--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0011.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0011.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Questless Knight, Diurnus Knight và Nocturnus Knight có thể tăng cường vũ khí, biểu hiện bằng hiệu ứng phát sáng. Hãy phản công chúng ba lần để loại bỏ hiệu ứng tăng cường, nếu không chúng sẽ liên tục nâng cấp vũ khí.</t>
+          <t>Hiệp Sĩ Không Nhiệm Vụ, Hiệp Sĩ Diurnus và Hiệp Sĩ Nocturnus có thể tăng cường vũ khí, biểu hiện bằng hiệu ứng phát sáng. Hãy phản công chúng ba lần để loại bỏ hiệu ứng tăng cường, nếu không chúng sẽ liên tục nâng cấp vũ khí.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Đối diện với Nightmare Cloud và dùng Công cụ để hóa thân thành Lottie Lost. &lt;color=#ffd12f&gt;Giữ nút&lt;/color&gt; để hấp thụ Nightmare Cloud bằng cuốn sách tranh của cô ấy!</t>
+          <t>Đối diện với Đám Mây Ác Mộng và dùng Tiện Ích để hóa thân thành Lottie Lost. &lt;color=#ffd12f&gt;Giữ nút&lt;/color&gt; để hấp thụ Đám Mây Ác Mộng bằng cuốn sách tranh của cô ấy!</t>
         </is>
       </c>
     </row>
@@ -705,8 +705,8 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Mỗi trong ba bàn thờ đều kết nối với các Bia Discipline xung quanh.
-Stand lên bệ bàn thờ để nạp năng lượng cho các bia, nhưng &lt;color=#ffd12f&gt;Tacet Discord sẽ xuất hiện&lt;/color&gt; để phá rối.</t>
+          <t>Mỗi trong ba bàn thờ đều kết nối với các Bia Kỷ Luật xung quanh.
+Đứng lên bệ bàn thờ để nạp năng lượng cho các bia, nhưng &lt;color=#ffd12f&gt;Tacet Discord sẽ xuất hiện&lt;/color&gt; để phá rối.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Trong vùng tối không được soi sáng bởi Ánh Đèn Ma Quái, các Tacet Discord được tăng cường, bước vào trạng thái Shadow khiến chúng &lt;color=#ffd12f&gt;miễn nhiễm với mọi đòn tấn công.&lt;/color&gt;</t>
+          <t>Trong vùng tối không được soi sáng bởi Ánh Đèn Ma Quái, các Tacet Discord được tăng cường, bước vào trạng thái Bóng Tối khiến chúng &lt;color=#ffd12f&gt;miễn nhiễm với mọi đòn tấn công.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Place các mảnh đã thu thập vào chỗ thiếu trên kính màu.
+          <t>Đặt các mảnh đã thu thập vào chỗ thiếu trên kính màu.
 Nếu mảnh ghép đúng, sẽ xuất hiện &lt;color=#ffd12f&gt;ánh sáng vàng&lt;/color&gt;.
 Nếu mảnh ghép sai, sẽ xuất hiện &lt;color=#ffd12f&gt;ánh sáng đỏ&lt;/color&gt;.</t>
         </is>
@@ -906,8 +906,8 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Mô-đun di động tích hợp cho chức năng Tổng hợp trong &lt;color=#ffd12f&gt;Pangu Terminal&lt;/color&gt;, do Huaxu Academy phát triển.
-Có thể truy cập nhanh qua &lt;color=#ffd12f&gt;Chi tiết vật phẩm&lt;/color&gt; trong Túi đồ.</t>
+          <t>Mô-đun di động tích hợp cho chức năng Tổng hợp trong &lt;color=#ffd12f&gt;Thiết bị đầu cuối Pangu&lt;/color&gt;, do Học viện Huaxu phát triển.
+Có thể truy cập nhanh qua &lt;color=#ffd12f&gt;Chi tiết Vật phẩm&lt;/color&gt; trong Hành trang.</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14.
 Quy tắc sự kiện
-Trong sự kiện, mỗi ngày bạn có thể mời một Đồng Hành tham gia cùng. Sau khi mời, bạn có thể nhận phần thưởng tương ứng trên trang sự kiện. Hoàn thành tất cả lượt mời để nhận Trang phục độc quyền của Sanhua, "Lệnh Bài Trừ Tà".
+Trong sự kiện, mỗi ngày bạn có thể mời một Đồng Hành tham gia cùng. Sau khi mời, bạn có thể nhận phần thưởng tương ứng trên trang sự kiện. Hoàn thành tất cả lượt mời để nhận Trang Phục độc quyền của Sanhua, "Lệnh Bài Trừ Tà".
 Số lần mời sẽ được làm mới hàng ngày vào lúc 4 giờ sáng, và các lượt mời chưa sử dụng sẽ hết hạn vào thời điểm đó. Hãy sử dụng hết lượt mời của bạn kịp thời.</t>
         </is>
       </c>
@@ -1050,8 +1050,8 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sau khi hoàn thành &lt;color=#ffd12f&gt;tất cả thử thách Dream Patrol trong một khu vực&lt;/color&gt;, những ý nghĩ đen tối ẩn sâu trong cõi mộng sẽ hiện hình thành Tacet Discord.
-Những Tacet Discord đặc biệt này là kẻ thù mạnh hơn. Đánh bại chúng để nhận được &lt;color=#ffd12f&gt;Echoes đặc biệt&lt;/color&gt;.</t>
+          <t>Sau khi hoàn thành &lt;color=#ffd12f&gt;tất cả thử thách Tuần Tra Giấc Mơ trong một khu vực&lt;/color&gt;, những ý nghĩ đen tối ẩn sâu trong cõi mộng sẽ hiện hình thành Tacet Discord.
+Những Tacet Discord đặc biệt này là kẻ thù mạnh hơn. Đánh bại chúng để nhận được &lt;color=#ffd12f&gt;Echo đặc biệt&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>[
-Event Rules]
-Trong sự kiện, ngươi có thể sử dụng Resonators thử nghiệm trong trang phục đặc biệt để thách đấu các giai đoạn cụ thể nhiều lần.
-Các Resonators thử nghiệm được cố định ở cấp độ và trang bị sẵn vũ khí cùng Echoes đã chọn. Trong các giai đoạn thử nghiệm, không thể thay đổi đội hình cũng như bộ vũ khí và Echoes.
-[Event Rewards]
+Quy Tắc Sự Kiện]
+Trong sự kiện, ngươi có thể sử dụng các Resonator thử nghiệm trong trang phục đặc biệt để thách đấu các giai đoạn cụ thể nhiều lần.
+Các Resonator thử nghiệm được cố định ở cấp độ và trang bị sẵn vũ khí cùng Echo đã chọn. Trong các giai đoạn thử nghiệm, không thể thay đổi đội hình cũng như bộ vũ khí và Echo.
+[Phần Thưởng Sự Kiện]
 Sau khi hoàn thành các giai đoạn sự kiện, ngươi có thể nhận phần thưởng giai đoạn trên trang sự kiện.
 Mỗi phần thưởng giai đoạn chỉ có thể nhận một lần duy nhất.
 Sau khi sự kiện kết thúc, phần thưởng cho các giai đoạn đã hoàn thành sẽ được gửi qua thư.</t>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>["Trang phục"]
-Trang phục là ngoại hình thay thế cho Resonators có thể chơi được.
+          <t>["Trang Phục"]
+Trang Phục là ngoại hình thay thế cho Resonator có thể chơi được.
 [Lưu ý]
-Một số Trang phục đi kèm với Weapon Projection đặc biệt, có thể thay đổi ngoại hình vũ khí.
-Một số Trang phục có thể mua với ưu đãi đặc biệt khi đang giảm giá. Sau khi giảm giá kết thúc, giá sẽ trở về ban đầu.
-Mỗi Trang phục độc đáo chỉ có thể mua một lần. Hãy đảm bảo bạn sở hữu Resonators trước khi mua Trang phục của họ. Bạn vẫn có thể mua Trang phục mà không sở hữu Resonators tương ứng, nhưng chỉ có thể sử dụng khi sở hữu Resonators đó.</t>
+Một số Trang Phục đi kèm với Hình Chiếu Vũ Khí đặc biệt, có thể thay đổi ngoại hình vũ khí.
+Một số Trang Phục có thể mua với ưu đãi đặc biệt khi đang giảm giá. Sau khi giảm giá kết thúc, giá sẽ trở về ban đầu.
+Mỗi Trang Phục độc đáo chỉ có thể mua một lần. Hãy đảm bảo bạn sở hữu Resonator trước khi mua Trang Phục của họ. Bạn vẫn có thể mua Trang Phục mà không sở hữu Resonator tương ứng, nhưng chỉ có thể sử dụng khi sở hữu Resonator đó.</t>
         </is>
       </c>
     </row>
@@ -1280,16 +1280,16 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>Về sự kiện
-Maji, người bạn cũ thân thiết của cậu, lại trở lại với "Kế hoạch Lollo Campaign New Toanh" của anh ấy. Như mọi khi, sự ủng hộ của cậu là điều anh rất trân trọng. Hoàn thành các chiến dịch để nhận Lollo Stamps—món quà tri ân từ Lollo Logistics.
+Maji, người bạn cũ thân thiết của cậu, lại trở lại với "Kế hoạch Chiến dịch Lollo Mới Toanh" của anh ấy. Như mọi khi, sự ủng hộ của cậu là điều anh rất trân trọng. Hoàn thành các chiến dịch để nhận Lollo Stamps—món quà tri ân từ Lollo Logistics.
 Lollo Stamps có thể đổi lấy các gói giao hàng đặc biệt từ Lollo Helper.
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14.
 Quy tắc sự kiện
-Trong thời gian diễn ra sự kiện, bạn có thể hoàn thành Lollo Campaign một lần mỗi ngày để nhận một số lượng Lollo Stamps nhất định.
+Trong thời gian diễn ra sự kiện, bạn có thể hoàn thành Chiến dịch Lollo một lần mỗi ngày để nhận một số lượng Lollo Stamps nhất định.
 Mỗi Lollo Stamp có thể đổi lấy một gói giao hàng đặc biệt từ Lollo Helper.
 Có 3 đợt hàng tồn kho cho các gói giao hàng đặc biệt của Lollo Helper. Khi bạn thu thập đủ tất cả các gói trong một đợt hàng, đợt hàng tiếp theo sẽ được mở khóa.
 Nếu bạn giành được dịch vụ giao hàng đặc biệt Lollo Express, bạn có thể nhận tất cả các gói hàng trong đợt hàng hiện tại.
-Sau khi sự kiện kết thúc, các Lollo Campaign chưa hoàn thành sẽ không còn hiệu lực, và tất cả Lollo Stamps còn lại sẽ bị thu hồi.</t>
+Sau khi sự kiện kết thúc, các Chiến dịch Lollo chưa hoàn thành sẽ không còn hiệu lực, và tất cả Lollo Stamps còn lại sẽ bị thu hồi.</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1. Sau khi mở khóa Bán Nhanh, mỗi lần mở giao diện Dock, một khu vực Bán Nhanh (Dodget đứt) sẽ tự động xuất hiện trong Khoang Hàng. Place thu hoạch của bạn vào khu vực này khi đang di chuyển để Bán Nhanh.
+          <t>1. Sau khi mở khóa Bán Nhanh, mỗi lần mở giao diện Bến Tàu, một khu vực Bán Nhanh (nét đứt) sẽ tự động xuất hiện trong Khoang Hàng. Đặt thu hoạch của bạn vào khu vực này khi đang di chuyển để Bán Nhanh.
 2. Khi khu vực Bán Nhanh đầy, bạn có thể bán ngay lập tức tất cả thu hoạch trong hoặc chạm vào khu vực đó.
 3. Thu hoạch bán qua Bán Nhanh sẽ có giá cao hơn so với bán tại bến tàu.
 4. Bán Nhanh chỉ khả dụng khi đang di chuyển.</t>
@@ -1640,13 +1640,13 @@
         <is>
           <t>[
 Thuộc Tính Đề Xuất]
-Tại trang Lựa Chọn Echoes, sử dụng "Đề Xuất" để mở bộ lọc. Điều này cho phép bạn kiểm tra các Mainstats và Chỉ Số Phụ được sử dụng phổ biến nhất cho Resonator hiện tại và nhanh chóng lọc ra các Echoes phù hợp.
-Khi chuyển đổi giữa các Echoes "Tất Cả", "COST 1", "COST 3" và "COST 4" trong Danh Sách Echoes bên trái, các thuộc tính đề xuất sẽ tự động điều chỉnh theo.
-[Sonata Effect Đề Xuất]
-Tại trang Resonator - Echoes, sử dụng "Đề Xuất" để kiểm tra Sonata Effect được sử dụng phổ biến nhất cho Resonator hiện tại.
-Sử dụng "Tự Động Equip" để trang bị tất cả các Echoes phù hợp nhất với Sonata Effect đã chọn.
-Tại trang Lựa Chọn Sonata và Thư viện Sonata, Sonata Effect được sử dụng phổ biến nhất cho Resonator hiện tại sẽ được đánh dấu bằng biểu tượng ngón tay cái.
-[Cập Nhật Data]
+Tại trang Lựa Chọn Echo, sử dụng "Đề Xuất" để mở bộ lọc. Điều này cho phép bạn kiểm tra các Chỉ Số Chính và Chỉ Số Phụ được sử dụng phổ biến nhất cho Resonator hiện tại và nhanh chóng lọc ra các Echo phù hợp.
+Khi chuyển đổi giữa các Echo "Tất Cả", "COST 1", "COST 3" và "COST 4" trong Danh Sách Echo bên trái, các thuộc tính đề xuất sẽ tự động điều chỉnh theo.
+[Hiệu Ứng Sonata Đề Xuất]
+Tại trang Resonator - Echo, sử dụng "Đề Xuất" để kiểm tra Hiệu Ứng Sonata được sử dụng phổ biến nhất cho Resonator hiện tại.
+Sử dụng "Tự Động Trang Bị" để trang bị tất cả các Echo phù hợp nhất với Hiệu Ứng Sonata đã chọn.
+Tại trang Lựa Chọn Sonata và Bộ Sưu Tập Sonata, Hiệu Ứng Sonata được sử dụng phổ biến nhất cho Resonator hiện tại sẽ được đánh dấu bằng biểu tượng ngón tay cái.
+[Cập Nhật Dữ Liệu]
 Các đề xuất dựa trên dữ liệu thu thập từ những người chơi hoạt động gần đây và được làm mới vào thứ Tư hàng tuần lúc 00:00 (giờ máy chủ). Thời gian làm mới thực tế có thể bị trễ đôi chút.
 Nếu không đủ dữ liệu, các đề xuất mặc định do hệ thống tạo ra sẽ được hiển thị thay thế.</t>
         </is>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bản Save Tần Số giúp bạn dễ dàng lưu và áp dụng các đội hình Tần Số đã tùy chỉnh cho Resonator.
-[Save Bản Save]
-Chọn cột "Current Setup" và sử dụng "Save Thành Bản Save" để lưu đội hình Tần Số đang trang bị cho Resonator.
+          <t>Bản Lưu Tần Số giúp bạn dễ dàng lưu và áp dụng các đội hình Tần Số đã tùy chỉnh cho Resonator.
+[Lưu Bản Lưu]
+Chọn cột "Thiết Lập Hiện Tại" và sử dụng "Lưu Thành Bản Lưu" để lưu đội hình Tần Số đang trang bị cho Resonator.
 Mỗi bản lưu có thể được đặt tên theo ý thích. Hãy đảm bảo tên tuân thủ luật pháp và quy định địa phương.
-Bạn có thể lưu tối đa 20 Bản Save Tần Số. Nếu đạt giới hạn, bạn cần xóa một bản lưu hiện có để tạo bản mới.
-[Áp Dụng Bản Save]
+Bạn có thể lưu tối đa 20 Bản Lưu Tần Số. Nếu đạt giới hạn, bạn cần xóa một bản lưu hiện có để tạo bản mới.
+[Áp Dụng Bản Lưu]
 Chọn bất kỳ bản lưu đã lưu và sử dụng "Áp Dụng" để trang bị bản lưu cho Resonator hiện tại.</t>
         </is>
       </c>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>["Event Rules"]
-Pioneer Association đã chọn Nimbus Sanctum làm chủ đề cho số tiếp theo của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Nimbus Sanctum.
-Hoàn thành Survey Tasks và tích lũy Points Khảo Sát để nhận những phần thưởng giá trị từ Pioneer Association.
+          <t>["Quy Tắc Sự Kiện"]
+Hiệp Hội Tiên Phong đã chọn Nimbus Sanctum làm chủ đề cho số tiếp theo của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Nimbus Sanctum.
+Hoàn thành Nhiệm Vụ Khảo Sát và tích lũy Điểm Khảo Sát để nhận những phần thưởng giá trị từ Hiệp Hội Tiên Phong.
 [Đặt Lại Nhiệm Vụ]
-Survey Tasks sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Points Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
-Nếu bạn còn phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.</t>
+Nhiệm Vụ Khảo Sát sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Điểm Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
+Nếu bạn còn phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Khi Tần số của Discord này giảm xuống, nó sẽ chuyển sang trạng thái phòng thủ. Hãy tấn công vào lúc đó để &lt;color=#ffd12f&gt;phá vỡ lớp phòng thủ tay&lt;/color&gt; và &lt;color=#ffd12f&gt;khóa chặt&lt;/color&gt; nó lại.</t>
+          <t>Khi Tần số của Tacet Discord này giảm xuống, nó sẽ chuyển sang trạng thái phòng thủ. Hãy tấn công vào lúc đó để &lt;color=#ffd12f&gt;phá vỡ lớp phòng thủ tay&lt;/color&gt; và &lt;color=#ffd12f&gt;khóa chặt&lt;/color&gt; nó lại.</t>
         </is>
       </c>
     </row>
@@ -1931,8 +1931,8 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Tương tác với Fishing Spots Cá để câu cá.
-Một số Fishing Spots Cá yêu cầu Kỹ Năng Fishing cụ thể. Hãy sở hữu các Kỹ Năng Fishing tương ứng để mở khóa những điểm này.</t>
+          <t>Tương tác với Điểm Câu Cá để câu cá.
+Một số Điểm Câu Cá yêu cầu Kỹ Năng Câu Cá cụ thể. Hãy sở hữu các Kỹ Năng Câu Cá tương ứng để mở khóa những điểm này.</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Trong chuyến hành trình, ngươi có thể dùng bánh lái để chuyển đổi Kỹ Năng Fishing.
+          <t>Trong chuyến hành trình, ngươi có thể dùng bánh lái để chuyển đổi Kỹ Năng Câu Cá.
 Sử dụng tính năng này một cách thông minh sẽ giúp chuyến câu của ngươi hiệu quả và đáng giá hơn.</t>
         </is>
       </c>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Một số tuyến đường trong Averardo Vault đang bảo trì. Sử dụng các công tắc để đảm bảo tàu di chuyển trên &lt;color=#ffd12f&gt;tuyến đường cho phép thông hành&lt;/color&gt;.
+          <t>Một số tuyến đường trong Hầm Averardo đang bảo trì. Sử dụng các công tắc để đảm bảo tàu di chuyển trên &lt;color=#ffd12f&gt;tuyến đường cho phép thông hành&lt;/color&gt;.
 Nếu tàu đi sai đường, nó sẽ tự động quay lại.</t>
         </is>
       </c>
@@ -2265,9 +2265,9 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Dùng Thiết Bị Giải Mã để biến các Echoes an ninh thù địch trong kho thành đồng minh. Ở trạng thái này, chúng sẽ ưu tiên bảo vệ người giữ Thiết Bị Giải Mã hơn tất cả.
-Nếu một Echoes đồng minh ở quá xa Thiết Bị Giải Mã hoặc thiết bị không được trang bị, nó sẽ trở lại trạng thái thù địch.
-*Các Echoes có thể điều khiển được đánh dấu bằng quầng sáng vàng.</t>
+          <t>Dùng Thiết Bị Giải Mã để biến các Echo an ninh thù địch trong kho thành đồng minh. Ở trạng thái này, chúng sẽ ưu tiên bảo vệ người giữ Thiết Bị Giải Mã hơn tất cả.
+Nếu một Echo đồng minh ở quá xa Thiết Bị Giải Mã hoặc thiết bị không được trang bị, nó sẽ trở lại trạng thái thù địch.
+*Các Echo có thể điều khiển được đánh dấu bằng quầng sáng vàng.</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Thực hiện &lt;color=#ffd12f&gt;Đòn Lao Xuống&lt;/color&gt; trên bệ tay cầm sẽ khiến Tượng Công Lý Hạ Giới hạ xuống, kích hoạt một phần di tích di chuyển.</t>
+          <t>Thực hiện &lt;color=#ffd12f&gt;Tấn Công Lao Xuống&lt;/color&gt; trên bệ tay cầm sẽ khiến Tượng Công Lý Hạ Giới hạ xuống, kích hoạt một phần di tích di chuyển.</t>
         </is>
       </c>
     </row>
@@ -2535,11 +2535,11 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>[Quy Định Sự Kiện]
-Pioneer Association đã chọn Whisperwind Haven làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Whisperwind Haven.
-Hoàn thành Survey Tasks và tích lũy Points Khảo Sát để nhận những phần thưởng giá trị từ Pioneer Association.
+Hiệp Hội Tiên Phong đã chọn Whisperwind Haven làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Whisperwind Haven.
+Hoàn thành Nhiệm Vụ Khảo Sát và tích lũy Điểm Khảo Sát để nhận những phần thưởng giá trị từ Hiệp Hội Tiên Phong.
 [Đặt Lại Nhiệm Vụ]
-Survey Tasks sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Points Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
-Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.</t>
+Nhiệm Vụ Khảo Sát sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Điểm Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
+Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.</t>
         </is>
       </c>
     </row>
@@ -2616,10 +2616,10 @@
           <t>Về sự kiện
 Phía bắc Thành phố Ragunna là ngư trường lớn nhất của Rinascita: quần đảo Riccioli, một điểm đến hấp dẫn cho cuộc phiêu lưu đầy thú vị. Chuẩn bị buồm và sẵn sàng chinh phục đại dương xanh thẳm nào, Thuyền trưởng!
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Vượt Biển Mở Đường" để mở khóa (nên hoàn thành nhiệm vụ "Silent as a Falling Leaf" để có trải nghiệm tốt nhất).
+Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Vượt Biển Mở Đường" để mở khóa (nên hoàn thành nhiệm vụ "Lặng Như Lá Rơi" để có trải nghiệm tốt nhất).
 Quy tắc sự kiện
-Trong sự kiện, cùng Phoebe thực hiện chuyến hải trình quyến rũ tại quần đảo Riccioli. Steer thuyền gondola "Rachel" và câu những loài cá độc đáo ở địa phương để tăng Fame và trở thành bậc thầy câu cá đích thực!
-Trong thời gian nhận thưởng giới hạn, hoàn thành các mục tiêu đặc biệt để kiếm Xu Không Tên. Thu thập đủ Xu Không Tên để đổi lấy Bộ Chỉnh Lưu "Món Quà Ocean" (bao gồm cả hình chiếu vũ khí).
+Trong sự kiện, cùng Phoebe thực hiện chuyến hải trình quyến rũ tại quần đảo Riccioli. Điều khiển thuyền gondola "Rachel" và câu những loài cá độc đáo ở địa phương để tăng Danh Vọng và trở thành bậc thầy câu cá đích thực!
+Trong thời gian nhận thưởng giới hạn, hoàn thành các mục tiêu đặc biệt để kiếm Xu Không Tên. Thu thập đủ Xu Không Tên để đổi lấy Bộ Chỉnh Lưu "Món Quà Đại Dương" (bao gồm cả hình chiếu vũ khí).
 Xu Không Tên có thể dùng để đổi thưởng tại cửa hàng sự kiện giới hạn. Hãy đảm bảo nhận thưởng trước khi sự kiện kết thúc.
 Nếu đăng nhập trong vòng 30 ngày sau thời gian nhận thưởng, phần thưởng chưa nhận sẽ tự động gửi vào hộp thư của bạn. Tuy nhiên, phần thưởng chưa đổi sẽ không được gửi vào hộp thư.
 Sau thời gian nhận thưởng giới hạn, bạn vẫn có thể tham gia sự kiện và nhận phần thưởng tiêu chuẩn Chanty Bounty.</t>
@@ -2689,7 +2689,7 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>1. Bạn có thể bán các vật phẩm trong Hàng Hóa tại cửa hàng bến tàu của Planck để kiếm Xu Công Ty Ngư Nghiệp Riccioli.
-2. Bạn có thể sử dụng Xu Công Ty Ngư Nghiệp Riccioli để mua nhiều loại vật phẩm khác nhau tại Dock Shop. Lưu ý rằng các vật phẩm có thể thay đổi tùy theo bến tàu bạn ghé thăm.</t>
+2. Bạn có thể dùng Xu Công Ty Ngư Nghiệp Riccioli để mua nhiều loại vật phẩm khác nhau tại Cửa Hàng Bến Tàu. Lưu ý rằng các vật phẩm có thể thay đổi tùy theo bến tàu bạn ghé thăm.</t>
         </is>
       </c>
     </row>
@@ -2768,11 +2768,11 @@
 Giờ đây, cánh cửa dẫn vào sâu thẳm Somnoire đã mở—nơi tĩnh lặng không gió, không ánh sáng, một nhân vật bí ẩn gửi đến cậu lời mời tham dự liên hoan phim.
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 30.
-Event Rules
-Somnoire đang rung động bởi sức mạnh bí ẩn. Khi bước vào, mọi Synergy Giả sẽ bị tước đi Echoes, nhưng thay vào đó là Illusive Echoes, Metaphor và những hiệu ứng đặc biệt khác chờ khám phá.
+Quy Tắc Sự Kiện
+Somnoire đang rung động bởi sức mạnh bí ẩn. Khi bước vào, mọi Resonator sẽ bị tước đi Echo, nhưng thay vào đó là Illusive Echo, Metaphor và những hiệu ứng đặc biệt khác chờ khám phá.
 Thử nghiệm các đội hình và tổ hợp khác nhau để trải nghiệm chiến đấu đa dạng.
-Event lần này có hệ thống Bond mới. Các Synergy Giả giờ đây có thể hình thành những mối Bond độc đáo với nhau, và khi cấp Bond tăng lên, sẽ mang lại nhiều hiệu ứng chiến đấu cùng kỹ năng Synergy Burst mạnh mẽ.
-Explore Illusive Realm để nhận những phần thưởng hậu hĩnh.</t>
+Sự kiện lần này có hệ thống Bond mới. Các Resonator giờ đây có thể hình thành những mối Bond độc đáo với nhau, và khi cấp Bond tăng lên, sẽ mang lại nhiều hiệu ứng chiến đấu cùng kỹ năng Synergy Burst mạnh mẽ.
+Khám phá Illusive Realm để nhận những phần thưởng hậu hĩnh.</t>
         </is>
       </c>
     </row>
@@ -2853,11 +2853,11 @@
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14.
 Quy tắc sự kiện
-Trong thời gian diễn ra sự kiện, bạn có thể hoàn thành Lollo Campaign một lần mỗi ngày để nhận một số lượng Lollo Stamps nhất định.
+Trong thời gian diễn ra sự kiện, bạn có thể hoàn thành Chiến dịch Lollo một lần mỗi ngày để nhận một số lượng Lollo Stamps nhất định.
 Mỗi Lollo Stamp có thể đổi lấy một gói giao hàng đặc biệt từ Lollo Helper.
 Có 3 đợt hàng tồn kho cho các gói giao hàng đặc biệt của Lollo Helper. Khi bạn thu thập đủ tất cả các gói trong một đợt hàng, đợt hàng tiếp theo sẽ được mở khóa.
 Nếu bạn giành được dịch vụ giao hàng đặc biệt Lollo Express, bạn có thể nhận tất cả các gói hàng trong đợt hàng hiện tại.
-Sau khi sự kiện kết thúc, các Lollo Campaign chưa hoàn thành sẽ không còn hiệu lực, và tất cả Lollo Stamps còn lại sẽ bị thu hồi.</t>
+Sau khi sự kiện kết thúc, các Chiến dịch Lollo chưa hoàn thành sẽ không còn hiệu lực, và tất cả Lollo Stamps còn lại sẽ bị thu hồi.</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>Về sự kiện
-Những khung cảnh quen thuộc giờ đây đã phai nhạt, mất đi sắc màu từng rực rỡ. A picture book đang chờ bàn tay bạn khôi phục lại vẻ đẹp nguyên bản.
+Những khung cảnh quen thuộc giờ đây đã phai nhạt, mất đi sắc màu từng rực rỡ. Một cuốn sách tranh đang chờ bàn tay bạn khôi phục lại vẻ đẹp nguyên bản.
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14 và hoàn thành Chương II Prologue.
 Nội quy sự kiện
@@ -3078,12 +3078,12 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>Về sự kiện
-KU-Ryan, một robot của Black Shores, hiện đang cần sự trợ giúp để thu thập Surveillance Dataset về Hiện Tượng Nhiễu Sóng tại Ragunna. Những ai quan tâm, hãy đến nói chuyện với cậu ấy.
+KU-Ryan, một robot của Black Shores, hiện đang cần sự trợ giúp để thu thập Bộ Dữ Liệu Giám Sát về Hiện Tượng Nhiễu Sóng tại Ragunna. Những ai quan tâm, hãy đến nói chuyện với cậu ấy.
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14 và hoàn thành Chương II Prologue của Nhiệm Vụ Chính.
 Quy tắc sự kiện
 1. Trong sự kiện, bạn cần kích hoạt thử thách ở các khu vực khác nhau. Bạn có thể tham gia bất kỳ thử thách nào đã kích hoạt bao nhiêu lần tùy thích.
-2. Sau khi thử thách bắt đầu, các Surveillance Dataset sẽ xuất hiện. Cố gắng thu thập càng nhiều càng tốt trong thời gian giới hạn. Khi tất cả dữ liệu đã được thu thập hoặc hết thời gian, bạn sẽ nhận thưởng dựa trên điểm số đạt được.
+2. Sau khi thử thách bắt đầu, các Bộ Dữ Liệu Giám Sát sẽ xuất hiện. Cố gắng thu thập càng nhiều càng tốt trong thời gian giới hạn. Khi tất cả dữ liệu đã được thu thập hoặc hết thời gian, bạn sẽ nhận thưởng dựa trên điểm số đạt được.
 3. Trong thử thách có nhiều mô-đun khác nhau. Hãy sử dụng chúng một cách chiến lược để tăng tốc độ thu thập dữ liệu.
 4. Nếu có phần thưởng nào chưa nhận sau khi sự kiện kết thúc, chúng sẽ được tự động gửi vào hộp thư của bạn khi đăng nhập lại trong vòng 30 ngày.</t>
         </is>
@@ -3165,11 +3165,11 @@
 Bước vào vùng đất bị bỏ hoang và cấm kỵ này để tìm kiếm sự thật đằng sau đức tin.
 Hoàn thành sự kiện để nhận những phần thưởng hậu hĩnh.
 Điều Kiện Tham Gia
-Đạt Cấp Liên Minh 14 và đến Chủng Viện Thần Học Avinoleum trong Nhiệm Vụ Chính Chương II Act III "Thiếu Nữ, Kẻ Nổi Loạn, Kẻ Rao Tin Tử Thần".
+Đạt Cấp Liên Minh 14 và đến Chủng Viện Thần Học Avinoleum trong Nhiệm Vụ Chính Chương II Hồi III "Thiếu Nữ, Kẻ Nổi Loạn, Kẻ Rao Tin Tử Thần".
 Nội Quy Sự Kiện
-Event được chia thành ba giai đoạn, mở khóa theo tiến độ Nhiệm Vụ Chính.
-Hoàn thành Event Quests để nhận phần thưởng phong phú.
-Unclaimed reward sẽ được giữ trong 30 ngày sau khi sự kiện kết thúc và sẽ được gửi qua Mail khi đăng nhập trong thời gian này.
+Sự kiện được chia thành ba giai đoạn, mở khóa theo tiến độ Nhiệm Vụ Chính.
+Hoàn thành Nhiệm Vụ Sự Kiện để nhận phần thưởng phong phú.
+Phần thưởng chưa nhận sẽ được giữ trong 30 ngày sau khi sự kiện kết thúc và sẽ được gửi qua Thư khi đăng nhập trong thời gian này.
 Lưu ý, một số nhiệm vụ trong sự kiện không thể hoàn thành ở Chế Độ Hợp Tác, và Theo Dõi Nhiệm Vụ sẽ không khả dụng ở một số khu vực trong game.</t>
         </is>
       </c>
@@ -3245,7 +3245,7 @@
 1. Tất cả tiến độ lưu đều có thời hạn. Khi hết hạn, tiến độ sẽ bị mất.
 2. Tiến độ lưu sẽ bị xóa khi cập nhật phiên bản. Hãy chú ý thông báo cập nhật và hoàn thành các thử thách đang dang dở.
 3. Bạn có thể lưu tối đa 10 tiến độ thử thách cùng lúc. Khi vượt quá giới hạn, bản lưu cũ nhất sẽ bị ghi đè.
-4. Nếu Rover thay đổi giới tính, tất cả tiến độ lưu giữa chừng sẽ bị mất.</t>
+4. Nếu Vận Mệnh Giả thay đổi giới tính, tất cả tiến độ lưu giữa chừng sẽ bị mất.</t>
         </is>
       </c>
     </row>
@@ -3378,8 +3378,8 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Cartethyia truyền năng lượng đặc biệt vào Gravity Calibrator. 
-Dùng Gravity Calibrator để &lt;color=#ffd12f&gt;thay đổi hướng trọng lực&lt;/color&gt;, từ đó tiếp cận những nơi trước đây không thể với tới.</t>
+          <t>Cartethyia truyền năng lượng đặc biệt vào Bộ Điều Chỉnh Trọng Lực. 
+Dùng Bộ Điều Chỉnh Trọng Lực để &lt;color=#ffd12f&gt;thay đổi hướng trọng lực&lt;/color&gt;, từ đó tiếp cận những nơi trước đây không thể với tới.</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=Ấn} vào chỉ báo hướng dọc theo bánh xe để thay đổi trọng lực. &lt;color=#ffd12f&gt;Mũi tên màu vàng chỉ hướng dẫn của Cartethyia&lt;/color&gt;.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào chỉ báo hướng dọc theo bánh xe để thay đổi trọng lực. &lt;color=#ffd12f&gt;Mũi tên màu vàng chỉ hướng dẫn của Cartethyia&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Attack liên tục vào Cơ chế Trình tự để nạp đầy năng lượng và mở khóa một số cơ chế cũng như lối vào.
+          <t>Tấn công liên tục vào Cơ chế Trình tự để nạp đầy năng lượng và mở khóa một số cơ chế cũng như lối vào.
 Tiến trình nạp được hiển thị bằng &lt;color=yellow&gt;phần sáng&lt;/color&gt;. Năng lượng sẽ bắt đầu giảm nếu ngừng tấn công.</t>
         </is>
       </c>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Xoay Tượng Messenger về hướng chính xác để kích hoạt cơ chế. Mỗi cơ chế sẽ yêu cầu xoay tượng theo cách và hướng khác nhau. Hãy tìm &lt;color=yellow&gt;gợi ý&lt;/color&gt; gần đó để giải câu đố.</t>
+          <t>Xoay Tượng Sứ Giả về hướng chính xác để kích hoạt cơ chế. Mỗi cơ chế sẽ yêu cầu xoay tượng theo cách và hướng khác nhau. Hãy tìm &lt;color=yellow&gt;gợi ý&lt;/color&gt; gần đó để giải câu đố.</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Sau mỗi vòng đua, bạn sẽ thấy bản Tóm Tắt, nơi bạn có thể xem các Khối Lập Phương đã gặp, phần thưởng nhận được và các dữ liệu khác của cuộc đua. Close bản Tóm Tắt để tiếp tục vòng đua tiếp theo!</t>
+          <t>Sau mỗi vòng đua, bạn sẽ thấy bản Tóm Tắt, nơi bạn có thể xem các Khối Lập Phương đã gặp, phần thưởng nhận được và các dữ liệu khác của cuộc đua. Đóng bản Tóm Tắt để tiếp tục vòng đua tiếp theo!</t>
         </is>
       </c>
     </row>
@@ -4378,9 +4378,9 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Những Cube cậu giải cứu từ Lâu đài Abbowser sẽ giúp chuẩn bị cho Lễ Anniversary.
-Khi công tác chuẩn bị tiến triển, Bánh Anniversary sẽ thay đổi qua từng giai đoạn.
-Các Cube được giải phóng sẽ ở lại Thế giới Cube. Biết đâu chúng sẽ có câu chuyện nào đó để kể?</t>
+          <t>Những Khối Lập Phương cậu giải cứu từ Lâu đài Abbowser sẽ giúp chuẩn bị cho Lễ Kỷ niệm.
+Khi công tác chuẩn bị tiến triển, Bánh Kỷ niệm sẽ thay đổi qua từng giai đoạn.
+Các Khối Lập Phương được giải phóng sẽ ở lại Thế giới Khối Lập Phương. Biết đâu chúng sẽ có câu chuyện nào đó để kể?</t>
         </is>
       </c>
     </row>
@@ -4447,9 +4447,9 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Các Cube đồng hành sẽ chiến đấu bên cạnh Resonators của cậu tại Abbowser Castle. 
-Hãy sử dụng Skills Echo để kích hoạt &lt;color=#ffd12f&gt;các đòn tấn công mạnh mẽ&lt;/color&gt; từ Cube.
-Một số Cube thậm chí có thể tự kích hoạt để tạo Hợp Kích với Resonators hoặc các Cube khác.</t>
+          <t>Các Khối Lập Phương đồng hành sẽ chiến đấu bên cạnh Resonator của cậu tại Lâu Đài Abbowser. 
+Hãy sử dụng Kỹ Năng Echo để kích hoạt &lt;color=#ffd12f&gt;các đòn tấn công mạnh mẽ&lt;/color&gt; từ Khối Lập Phương.
+Một số Khối Lập Phương thậm chí có thể tự kích hoạt để tạo Hợp Kích với Resonator hoặc các Khối Lập Phương khác.</t>
         </is>
       </c>
     </row>
@@ -4515,8 +4515,8 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Khối Lập Phương có thể trang bị Mô-đun Data để tăng sức mạnh trong chiến đấu.
-Mô-đun Data có nhiều loại. Hãy nhớ &lt;color=#ffd12f&gt;trang bị chúng vào khe tương ứng&lt;/color&gt;.</t>
+          <t>Khối Lập Phương có thể trang bị Mô-đun Dữ Liệu để tăng sức mạnh trong chiến đấu.
+Mô-đun Dữ Liệu có nhiều loại. Hãy nhớ &lt;color=#ffd12f&gt;trang bị chúng vào khe tương ứng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>Có 3 loại Mô-đun Dữ liệu cho Khối Lập Phương của cậu. 
-Ngoài Abbowser Castle, Abbowser's Shop cũng có những Mô-đun Dữ liệu mạnh mẽ. Để mua sắm ở đó, hãy thu thập xu bằng cách chinh phục Abbowser Castle.</t>
+Ngoài Lâu Đài Abbowser, Cửa Hàng Abbowser cũng có những Mô-đun Dữ liệu mạnh mẽ. Để mua sắm ở đó, hãy thu thập xu bằng cách chinh phục Lâu Đài Abbowser.</t>
         </is>
       </c>
     </row>
@@ -4649,8 +4649,8 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Gắn Ability Mô-đun để Trao cho Cube khả năng của các Khối khác. 
-Cube &lt;color=#ffd12f&gt;không thể gắn&lt;/color&gt; Ability Mô-đun nếu đã sở hữu &lt;color=#ffd12f&gt;khả năng tương tự&lt;/color&gt;.</t>
+          <t>Gắn Mô-đun Kỹ Năng để Trao cho Khối Lập Phương khả năng của các Khối khác. 
+Khối Lập Phương &lt;color=#ffd12f&gt;không thể gắn&lt;/color&gt; Mô-đun Kỹ Năng nếu đã sở hữu &lt;color=#ffd12f&gt;khả năng tương tự&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Người chơi có thể &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; một &lt;color=#ffd12f&gt;Cube&lt;/color&gt; bằng cách &lt;color=#ffd12f&gt;dự đoán&lt;/color&gt; rằng nó sẽ là &lt;color=#ffd12f&gt;Quán Quân&lt;/color&gt; của trận đấu.</t>
+          <t>Người chơi có thể &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; một &lt;color=#ffd12f&gt;Khối Lập Phương&lt;/color&gt; bằng cách &lt;color=#ffd12f&gt;dự đoán&lt;/color&gt; rằng nó sẽ là &lt;color=#ffd12f&gt;Quán Quân&lt;/color&gt; của trận đấu.</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Mỗi ngày từ 8:00 đến 19:30, người chơi có thể ủng hộ Cube yêu thích bằng cách dự đoán nó sẽ thắng trận. Mỗi ngày, trận đấu bắt đầu lúc 20:00 và kết quả sẽ được công bố trong ngày.</t>
+          <t>Mỗi ngày từ 8:00 đến 19:30, người chơi có thể ủng hộ Khối Lập Phương yêu thích bằng cách dự đoán nó sẽ thắng trận. Mỗi ngày, trận đấu bắt đầu lúc 20:00 và kết quả sẽ được công bố trong ngày.</t>
         </is>
       </c>
     </row>
@@ -4846,8 +4846,8 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Trong mỗi trận đấu, Cube &lt;color=#ffd12f&gt;xếp hạng số 1&lt;/color&gt; sẽ chiến thắng. Những người chơi &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; Cube thắng sẽ &lt;color=#ffd12f&gt;nhận&lt;/color&gt; Phần Thưởng Popularity.
-Phần Thưởng Popularity được xác định bởi Popularity đã tiêu hao khi ủng hộ và &lt;color=#ffd12f&gt;Tỷ Lệ Thua Cược&lt;/color&gt; của Cube. Tỷ lệ này &lt;color=#ffd12f&gt;cập nhật định kỳ&lt;/color&gt; dựa trên lượng ủng hộ mà Cube nhận được.</t>
+          <t>Trong mỗi trận đấu, Cube &lt;color=#ffd12f&gt;xếp hạng số 1&lt;/color&gt; sẽ chiến thắng. Những người chơi &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; Cube thắng sẽ &lt;color=#ffd12f&gt;nhận&lt;/color&gt; Phần Thưởng Độ Phổ Biến.
+Phần Thưởng Độ Phổ Biến được xác định bởi Độ Phổ Biến đã tiêu hao khi ủng hộ và &lt;color=#ffd12f&gt;Tỷ Lệ Thua Cược&lt;/color&gt; của Cube. Tỷ lệ này &lt;color=#ffd12f&gt;cập nhật định kỳ&lt;/color&gt; dựa trên lượng ủng hộ mà Cube nhận được.</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Mỗi trận đấu được chia thành Hiệp 1 và Hiệp 2. Xếp hạng ở Hiệp 2 sẽ quyết định liệu một Cube có &lt;color=#ffd12f&gt;tiến vào&lt;/color&gt; trận tiếp theo hay không.</t>
+          <t>Mỗi trận đấu được chia thành Hiệp 1 và Hiệp 2. Xếp hạng ở Hiệp 2 sẽ quyết định liệu một Khối Lập Phương có &lt;color=#ffd12f&gt;tiến vào&lt;/color&gt; trận tiếp theo hay không.</t>
         </is>
       </c>
     </row>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Khi các Cube xếp chồng lên nhau, nếu khối dưới cùng di chuyển trước, nó sẽ kéo theo tất cả các khối xếp phía trên. Trong số các khối xếp chồng, khối càng cao thì cấp bậc càng lớn.</t>
+          <t>Khi các Khối Lập Phương xếp chồng lên nhau, nếu khối dưới cùng di chuyển trước, nó sẽ kéo theo tất cả các khối xếp phía trên. Trong số các khối xếp chồng, khối càng cao thì cấp bậc càng lớn.</t>
         </is>
       </c>
     </row>
@@ -5045,9 +5045,9 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Trong Giai Đoạn Hỗ Trợ, người chơi có thể &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; Cube yêu thích bằng cách &lt;color=#ffd12f&gt;dự đoán&lt;/color&gt; rằng nó sẽ là &lt;color=#ffd12f&gt;Quán Quân Trận Đấu&lt;/color&gt;.
-&lt;color=#ffd12f&gt;Ủng hộ&lt;/color&gt; một Cube sẽ tiêu tốn Điểm Phổ Biến của người chơi. &lt;color=#ffd12f&gt;Điểm Phổ Biến&lt;/color&gt; có thể kiếm được bằng cách hoàn thành &lt;color=#ffd12f&gt;Daily Tasks&lt;/color&gt; của sự kiện.
-Nếu Cube mà bạn ủng hộ chiến thắng, bạn sẽ &lt;color=#ffd12f&gt;nhận được Phần Thưởng Điểm Phổ Biến&lt;/color&gt; dựa trên [Điểm Phổ Biến Đã Dành] x [Tỷ Lệ Thua Lợi].
+          <t>Trong Giai Đoạn Hỗ Trợ, người chơi có thể &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; Khối Lập Phương yêu thích bằng cách &lt;color=#ffd12f&gt;dự đoán&lt;/color&gt; rằng nó sẽ là &lt;color=#ffd12f&gt;Quán Quân Trận Đấu&lt;/color&gt;.
+&lt;color=#ffd12f&gt;Ủng hộ&lt;/color&gt; một Khối Lập Phương sẽ tiêu tốn Điểm Phổ Biến của người chơi. &lt;color=#ffd12f&gt;Điểm Phổ Biến&lt;/color&gt; có thể kiếm được bằng cách hoàn thành &lt;color=#ffd12f&gt;Nhiệm Vụ Hằng Ngày&lt;/color&gt; của sự kiện.
+Nếu Khối Lập Phương mà bạn ủng hộ chiến thắng, bạn sẽ &lt;color=#ffd12f&gt;nhận được Phần Thưởng Điểm Phổ Biến&lt;/color&gt; dựa trên [Điểm Phổ Biến Đã Dành] x [Tỷ Lệ Thua Lợi].
 Đừng lo, bạn sẽ nhận lại 80% Điểm Phổ Biến đã dùng để ủng hộ nếu dự đoán của bạn sai!</t>
         </is>
       </c>
@@ -5116,8 +5116,8 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>Giai đoạn Hỗ Trợ diễn ra từ 08:00 đến 19:30 hàng ngày.
-Dựa trên lượng Hỗ Trợ mà một Cube nhận được và vị trí xuất phát của nó, &lt;color=#ffd12f&gt;Tỷ Lệ Thua Lợi&lt;/color&gt; của Cube sẽ được &lt;color=#ffd12f&gt;cập nhật&lt;/color&gt; vào 12:00 và 18:00 hàng ngày.
-Rewards Danh Tiếng của cậu khi dự đoán đúng kẻ thắng cuộc sẽ phụ thuộc vào Tỷ Lệ Thua Lợi của Cube. Nhớ để mắt đến những thay đổi của tỷ lệ này nhé!</t>
+Dựa trên lượng Hỗ Trợ mà một Khối Lập Phương nhận được và vị trí xuất phát của nó, &lt;color=#ffd12f&gt;Tỷ Lệ Thua Lợi&lt;/color&gt; của Khối Lập Phương sẽ được &lt;color=#ffd12f&gt;cập nhật&lt;/color&gt; vào 12:00 và 18:00 hàng ngày.
+Phần thưởng Danh Tiếng của cậu khi dự đoán đúng kẻ thắng cuộc sẽ phụ thuộc vào Tỷ Lệ Thua Lợi của Khối Lập Phương. Nhớ để mắt đến những thay đổi của tỷ lệ này nhé!</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Page Race Hiện Thể hiện tất cả các giai đoạn của cuộc đua và ai sẽ tiến vào vòng tiếp theo.
+          <t>Trang Đua Hiện Thể hiện tất cả các giai đoạn của cuộc đua và ai sẽ tiến vào vòng tiếp theo.
 Cuộc đua gồm 5 giai đoạn: Bảng A, Bảng B, Tứ kết A, Tứ kết B và Chung kết, tổng cộng 10 trận đấu.
 Trong Giai đoạn Hỗ trợ, các Đấu thủ và trận đấu hiện tại sẽ được làm nổi bật. Sau khi mỗi trận kết thúc, trang sẽ cập nhật Đấu thủ cho trận đấu tiếp theo.</t>
         </is>
@@ -5255,9 +5255,9 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>Mỗi Giai Đoạn Bảng sẽ chia thành Nửa Đầu và Nửa Sau.
-Vị trí của một Cube trong Nửa Đầu sẽ quyết định điểm xuất phát của nó trong Nửa Sau.
-Sau khi Nửa Sau kết thúc, chỉ những &lt;color=#ffd12f&gt;Cube dẫn đầu&lt;/color&gt; mới được &lt;color=#ffd12f&gt;tiến vào Giai Đoạn tiếp theo&lt;/color&gt;.
-4 Cube đứng đầu mỗi Giai Đoạn Bảng sẽ tiến vào Vòng Tứ Kết. Hai đội đứng đầu Vòng Tứ Kết sẽ bước vào Trận Chung Kết, nơi nhà vô địch được quyết định.</t>
+Vị trí của một Khối Lập Phương trong Nửa Đầu sẽ quyết định điểm xuất phát của nó trong Nửa Sau.
+Sau khi Nửa Sau kết thúc, chỉ những &lt;color=#ffd12f&gt;Khối Lập Phương dẫn đầu&lt;/color&gt; mới được &lt;color=#ffd12f&gt;tiến vào Giai Đoạn tiếp theo&lt;/color&gt;.
+4 Khối Lập Phương đứng đầu mỗi Giai Đoạn Bảng sẽ tiến vào Vòng Tứ Kết. Hai đội đứng đầu Vòng Tứ Kết sẽ bước vào Trận Chung Kết, nơi nhà vô địch được quyết định.</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>Sau khi mỗi trận đấu kết thúc, trang Tóm Tắt Trận Đấu sẽ cho phép bạn xem lại trận đấu.
-Nếu trận đấu vừa kết thúc là Hiệp 1, nút "Vị Trí Xuất Phát Hiệp 2" sẽ xuất hiện trên trang chính. {Cus:Ipt,Touch=Touch PC=press Gamepad=Ấn} để xem vị trí xuất phát của các Khối Lập Phương trong Hiệp 2.</t>
+Nếu trận đấu vừa kết thúc là Hiệp 1, nút "Vị Trí Xuất Phát Hiệp 2" sẽ xuất hiện trên trang chính. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem vị trí xuất phát của các Khối Lập Phương trong Hiệp 2.</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
         <is>
           <t>[Ủng hộ]
 1. Trang Ủng hộ hiển thị các trận đấu mà bạn đã ủng hộ một Cube. Mỗi mục sẽ hiển thị thông tin trận đấu, Cube được ủng hộ, vị trí về đích của Cube và Lượng ủng hộ bạn nhận được.
-2. Nếu trận đấu đã kết thúc, bạn cũng có thể {Cus:Ipt,Touch=tap PC=bấm Gamepad=press} nút Xem lại ở bên phải để xem lại trận đấu.</t>
+2. Nếu trận đấu đã kết thúc, bạn cũng có thể {Cus:Ipt,Touch=tap PC=click Gamepad=press} nút Xem lại ở bên phải để xem lại trận đấu.</t>
         </is>
       </c>
     </row>
@@ -5476,13 +5476,13 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>[Bảng Bảo Trợ]
-1. Bảng Bảo Trợ được thành lập dựa trên kết quả ủng hộ Cube. 100 người chơi hàng đầu máy chủ của bạn sẽ được hiển thị trên Bảng Bảo Trợ.
-2. Thứ hạng của bạn cũng sẽ xuất hiện trên Bảng Bảo Trợ. Thông tin của bạn sẽ không được hiển thị nếu bạn chưa ủng hộ Cube hoặc kết quả của bạn thấp hơn 50% số người tham gia.
-3. Thứ hạng trên Bảng Bảo Trợ được xác định bởi Tổng Popularity. Hai hoặc nhiều người chơi có cùng Popularity sẽ có cùng thứ hạng, thứ tự trong Bảng Bảo Trợ sẽ được quyết định bởi số dự đoán chính xác và thời điểm dự đoán.
-4. Chỉ Popularity từ việc ủng hộ Cube mới được tính vào Ranking Tổng Popularity. Popularity từ việc hoàn thành Nhiệm Vụ Sự Kiện Hằng Ngày sẽ không được tính.
-5. Bạn cần ủng hộ Cube ít nhất một lần để được xếp hạng.
-6. Bảng Bảo Trợ sẽ hiển thị avatar và tên của bạn như lúc bạn ủng hộ Cube.
-7. Bạn sẽ bị loại khỏi Bảng Bảo Trợ hiện tại nếu tên của bạn chứa ký tự nhạy cảm vi phạm Thỏa Thuận Người Dùng. Nếu phát hiện bất thường trong quá trình ủng hộ Cube, dữ liệu xếp hạng của người chơi vi phạm sẽ bị xóa và họ sẽ bị cấm tham gia xếp hạng hiện tại. Đội ngũ Phát Triển bảo lưu quyền giải thích cuối cùng.
+1. Bảng Bảo Trợ được thành lập dựa trên kết quả ủng hộ Khối Lập Phương. 100 người chơi hàng đầu máy chủ của bạn sẽ được hiển thị trên Bảng Bảo Trợ.
+2. Thứ hạng của bạn cũng sẽ xuất hiện trên Bảng Bảo Trợ. Thông tin của bạn sẽ không được hiển thị nếu bạn chưa ủng hộ Khối Lập Phương hoặc kết quả của bạn thấp hơn 50% số người tham gia.
+3. Thứ hạng trên Bảng Bảo Trợ được xác định bởi Tổng Độ Phổ Biến. Hai hoặc nhiều người chơi có cùng Độ Phổ Biến sẽ có cùng thứ hạng, thứ tự trong Bảng Bảo Trợ sẽ được quyết định bởi số dự đoán chính xác và thời điểm dự đoán.
+4. Chỉ Độ Phổ Biến từ việc ủng hộ Khối Lập Phương mới được tính vào Bảng Xếp Hạng Tổng Độ Phổ Biến. Độ Phổ Biến từ việc hoàn thành Nhiệm Vụ Sự Kiện Hằng Ngày sẽ không được tính.
+5. Bạn cần ủng hộ Khối Lập Phương ít nhất một lần để được xếp hạng.
+6. Bảng Bảo Trợ sẽ hiển thị avatar và tên của bạn như lúc bạn ủng hộ Khối Lập Phương.
+7. Bạn sẽ bị loại khỏi Bảng Bảo Trợ hiện tại nếu tên của bạn chứa ký tự nhạy cảm vi phạm Thỏa Thuận Người Dùng. Nếu phát hiện bất thường trong quá trình ủng hộ Khối Lập Phương, dữ liệu xếp hạng của người chơi vi phạm sẽ bị xóa và họ sẽ bị cấm tham gia xếp hạng hiện tại. Đội ngũ Phát Triển bảo lưu quyền giải thích cuối cùng.
 [Cập Nhật Bảng Bảo Trợ]
 Bảng Bảo Trợ được cập nhật vào các khung giờ cố định. Thời gian cập nhật cho từng máy chủ:
 Trung Quốc Đại Lục: 04:00 (UTC+8)
@@ -5562,11 +5562,11 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>[Diện Mạo Echo]
-Bằng cách chuyển đổi Diện Mạo, bạn có thể thay đổi ngoại hình của Đôi Cánh Echo và Dù Lượn.
+          <t>[Diện Mạo Tiếng Vọng]
+Bằng cách chuyển đổi Diện Mạo, bạn có thể thay đổi ngoại hình của Đôi Cánh Tiếng Vọng và Dù Lượn.
 [Lưu ý quan trọng]
-Mỗi Diện Mạo Echo chỉ có thể mua một lần và có thể sử dụng cho tất cả Resonators mà bạn sở hữu.
-Diện Mạo Echo có yêu cầu sử dụng. Bạn phải hoàn thành Chương I Prologue của Nhiệm Vụ Chính để mở khóa Diện Mạo Dù Lượn, và Chương II Act II để mở khóa Diện Mạo Đôi Cánh Echo.
+Mỗi Diện Mạo Tiếng Vọng chỉ có thể mua một lần và có thể sử dụng cho tất cả Resonator mà bạn sở hữu.
+Diện Mạo Tiếng Vọng có yêu cầu sử dụng. Bạn phải hoàn thành Chương I Prologue của Nhiệm Vụ Chính để mở khóa Diện Mạo Dù Lượn, và Chương II Act II để mở khóa Diện Mạo Đôi Cánh Tiếng Vọng.
 Bạn có thể mua Diện Mạo ngay cả khi chưa đáp ứng yêu cầu. Khi đủ điều kiện, Diện Mạo sẽ tự động kích hoạt.</t>
         </is>
       </c>
@@ -5645,9 +5645,9 @@
 Đường phố Septimont đang tràn ngập sức sống. Du khách từ khắp nơi đổ về, diện những bộ trang phục lộng lẫy nhất để tham dự Đại Hội Agon.
 Hãy khám phá Septimont trong thời khắc lễ hội này, nếm trải vị đắng của thất bại và niềm vui chiến thắng trong cuộc tranh tài, và cảm nhận vinh quang của đấu trường giữa khung cảnh hùng vĩ.
 Điều Kiện Tham Gia
-Đến Septimont trong Nhiệm Vụ Chính "Shadow Glory".
-Event Rules
-Event gồm bốn giai đoạn, mỗi giai đoạn sẽ mở khóa dần khi bạn hoàn thành Nhiệm Vụ Chính.
+Đến Septimont trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang".
+Quy Tắc Sự Kiện
+Sự kiện gồm bốn giai đoạn, mỗi giai đoạn sẽ mở khóa dần khi bạn hoàn thành Nhiệm Vụ Chính.
 Hoàn thành nhiệm vụ sự kiện để nhận những phần thưởng hấp dẫn.
 Nếu có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận qua thư.
 Lưu ý: Một số nội dung sự kiện không khả dụng trong Chế Độ Hợp Tác, và Theo Dõi Nhiệm Vụ Sự Kiện sẽ không khả dụng ở một số khu vực.</t>
@@ -5716,8 +5716,8 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Sau khi hoàn thành tất cả thử thách trong sự kiện "Lá Cờ Không Bao Giờ Ngã", việc hồi sinh TD trong Khu Vực Challenge sẽ trở lại trạng thái bình thường, và các BUFF Special vẫn sẽ được giữ nguyên trong khu vực đó.
-Các lá cờ trong Khu Vực Challenge đã hoàn thành sẽ không còn tương tác được, nhưng các Rương Giải Thưởng chưa mở vẫn sẽ còn ở đó.</t>
+          <t>Sau khi hoàn thành tất cả thử thách trong sự kiện "Lá Cờ Không Bao Giờ Ngã", việc hồi sinh TD trong Khu Vực Thử Thách sẽ trở lại trạng thái bình thường, và các BUFF Đặc Biệt vẫn sẽ được giữ nguyên trong khu vực đó.
+Các lá cờ trong Khu Vực Thử Thách đã hoàn thành sẽ không còn tương tác được, nhưng các Rương Giải Thưởng chưa mở vẫn sẽ còn ở đó.</t>
         </is>
       </c>
     </row>
@@ -5788,11 +5788,11 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>[Quy Định Sự Kiện]
-Pioneer Association đã chọn Dãy Border Mountains làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Dãy Border Mountains.
-Hoàn thành Survey Tasks và tích lũy Points Khảo Sát để nhận những phần thưởng giá trị từ Pioneer Association.
+Hiệp Hội Tiên Phong đã chọn Dãy Núi Biên Giới làm chủ đề cho một số phát hành sắp tới của &lt;i&gt;Wutherium Geographic&lt;/i&gt;. Vì vậy, hiệp hội đã tổ chức một cuộc khảo sát đặc biệt tại Dãy Núi Biên Giới.
+Hoàn thành Nhiệm Vụ Khảo Sát và tích lũy Điểm Khảo Sát để nhận những phần thưởng giá trị từ Hiệp Hội Tiên Phong.
 [Đặt Lại Nhiệm Vụ]
-Survey Tasks sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Points Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
-Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.</t>
+Nhiệm Vụ Khảo Sát sẽ được đặt lại hàng ngày vào lúc 04:00. Khi đặt lại, mọi Điểm Khảo Sát chưa nhận sẽ được tự động thu thập, và các nhiệm vụ chưa hoàn thành sẽ hết hạn.
+Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.</t>
         </is>
       </c>
     </row>
@@ -5932,13 +5932,13 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>[Quản Lý Echo]
-- Bạn có thể tạo nhiều kế hoạch quản lý Echo dựa trên chất lượng, COST, Sonata Effect và Mainstats.
-- Nhiều kế hoạch có thể được kích hoạt cùng lúc. Khi nhận được Echo mới, nó sẽ tự động bị khóa hoặc đánh dấu để loại bỏ theo các kế hoạch đang kích hoạt.
-[Tự Động Loại Bỏ Echo]
-Nếu một Echo đáp ứng cả tiêu chí khóa và loại bỏ, nó sẽ được khóa thay vì bị loại bỏ.
+          <t>[Quản Lý Tiếng Vọng]
+- Bạn có thể tạo nhiều kế hoạch quản lý Tiếng Vọng dựa trên chất lượng, COST, Hiệu Ứng Sonata và Chỉ Số Chính.
+- Nhiều kế hoạch có thể được kích hoạt cùng lúc. Khi nhận được Tiếng Vọng mới, nó sẽ tự động bị khóa hoặc đánh dấu để loại bỏ theo các kế hoạch đang kích hoạt.
+[Tự Động Loại Bỏ Tiếng Vọng]
+Nếu một Tiếng Vọng đáp ứng cả tiêu chí khóa và loại bỏ, nó sẽ được khóa thay vì bị loại bỏ.
 [Kế Hoạch Gợi Ý]
-Bạn có thể trực tiếp nhập nhiều kế hoạch gợi ý. Các kế hoạch gợi ý không bao gồm tất cả Sonata Effect và phải được kích hoạt thủ công.</t>
+Bạn có thể trực tiếp nhập nhiều kế hoạch gợi ý. Các kế hoạch gợi ý không bao gồm tất cả Hiệu Ứng Sonata và phải được kích hoạt thủ công.</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
         <is>
           <t>Fenrico có thể sử dụng Holy Summon để triệu hồi các Divine Envoys theo lệnh và bắt đầu tập trung Retribution.
 Khi Fenrico thi triển Holy Summon, Phrolova sẽ tích lũy năng lượng để phản đòn Retribution.
-Đánh bại các Divine Envoys sẽ đảm bảo quá trình tích lũy của Phrolova không bị gián đoạn và cho phép cô tạo ra Remnant Field bảo vệ Resonators bên trong khỏi Retribution. Sau khi Retribution kết thúc, Phrolova sẽ phản công Fenrico, làm giảm sức mạnh rung động của hắn.</t>
+Đánh bại các Divine Envoys sẽ đảm bảo quá trình tích lũy của Phrolova không bị gián đoạn và cho phép cô tạo ra Remnant Field bảo vệ Resonator bên trong khỏi Retribution. Sau khi Retribution kết thúc, Phrolova sẽ phản công Fenrico, làm giảm sức mạnh rung động của hắn.</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Lồng ấp Echo Vi mô được lưu trữ tập trung và chiếm không gian đáng kể. Để tiết kiệm diện tích sàn sản xuất quý giá, chúng thường được giấu trong các vách cấu trúc.
+          <t>Lồng ấp Tiếng Vọng Vi mô được lưu trữ tập trung và chiếm không gian đáng kể. Để tiết kiệm diện tích sàn sản xuất quý giá, chúng thường được giấu trong các vách cấu trúc.
 Các đơn vị này triển khai nhanh chóng khi kích hoạt và có thể va chạm vào vật thể xung quanh. Bạn có thể điều khiển chúng thông qua Orchestration.</t>
         </is>
       </c>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Ống dẫn năng lượng cung cấp lượng lớn năng lượng cho nhiều khu vực và kết nối với hệ thống van đóng mở. Vận hành các van bằng cách truyền năng lượng qua ống đến đúng vị trí.</t>
+          <t>Ống dẫn năng lượng cung cấp lượng lớn năng lượng cho nhiều khu vực và kết nối với hệ thống van đóng mở. Điều khiển các van bằng cách truyền năng lượng qua ống đến đúng vị trí.</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Nghi thức Cầu Nguyện phải được tiến hành chính xác theo quy định của Giáo Đoàn Deep mới được coi là biểu hiện của lòng thành kính. Nếu không, các ngươi sẽ bị trục xuất khỏi nhóm.</t>
+          <t>Nghi thức Cầu Nguyện phải được tiến hành chính xác theo quy định của Giáo Đoàn Sâu Thẳm mới được coi là biểu hiện của lòng thành kính. Nếu không, các ngươi sẽ bị trục xuất khỏi nhóm.</t>
         </is>
       </c>
     </row>
@@ -6402,10 +6402,10 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy &lt;color=#ffd12f&gt;Sự Nuốt Chửng&lt;/color&gt; làm khả năng cốt lõi.
-Một số Resonator sẽ trở nên mạnh mẽ hơn trong Thế Giới Giấc Mơ bằng cách Nuốt Chửng. &lt;color=#ffd12f&gt;Khi một Resonator mạnh hấp thụ kẻ yếu hơn, sản lượng Daily Coupon của nó sẽ tăng lên.&lt;/color&gt;
-Một số Resonator sẽ mang lại hiệu ứng tăng cường bổ sung khi bị Nuốt Chửng.
-Để tối đa hóa lợi ích, &lt;color=#ffd12f&gt;hãy đảm bảo có đủ Resonator trên chiến trường có thể bị Nuốt Chửng&lt;/color&gt; nếu bạn chọn Giấc Mơ Nuốt Chửng.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy &lt;color=#ffd12f&gt;Sự Nuốt Chửng&lt;/color&gt; làm khả năng cốt lõi.
+Một số Cộng Hưởng Giả sẽ trở nên mạnh mẽ hơn trong Thế Giới Giấc Mơ bằng cách Nuốt Chửng. &lt;color=#ffd12f&gt;Khi một Cộng Hưởng Giả mạnh hấp thụ kẻ yếu hơn, sản lượng Phiếu Hằng Ngày của nó sẽ tăng lên.&lt;/color&gt;
+Một số Cộng Hưởng Giả sẽ mang lại hiệu ứng tăng cường bổ sung khi bị Nuốt Chửng.
+Để tối đa hóa lợi ích, &lt;color=#ffd12f&gt;hãy đảm bảo có đủ Cộng Hưởng Giả trên chiến trường có thể bị Nuốt Chửng&lt;/color&gt; nếu bạn chọn Giấc Mơ Nuốt Chửng.</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Các Echoes thuộc thuộc tính Giấc Mộng này không có khả năng cốt lõi. &lt;color=#ffd12f&gt;Chúng rất phù hợp để kết hợp với các Echoes thuộc thuộc tính Giấc Mộng khác.&lt;/color&gt; Những Echoes này sẽ tự động được thêm vào Tuyển Dụng Echoes sau khi mở khóa, không cần phải chọn thuộc tính Giấc Mộng này.</t>
+          <t>Các Echo thuộc thuộc tính Giấc Mộng này không có khả năng cốt lõi. &lt;color=#ffd12f&gt;Chúng rất phù hợp để kết hợp với các Echo thuộc thuộc tính Giấc Mộng khác.&lt;/color&gt; Những Echo này sẽ tự động được thêm vào Tuyển Dụng Echo sau khi mở khóa, không cần phải chọn thuộc tính Giấc Mộng này.</t>
         </is>
       </c>
     </row>
@@ -6546,12 +6546,12 @@
           <t>Về sự kiện
 Vua ý tưởng Maji lại trở lại với một chiến dịch mới toanh—
 Lần này, hắn đang lướt trên làn sóng công nghệ và cố tạo ra trợ lý thông minh riêng của mình, Lollo Genie.
-Tương tác với những Echoes đáng yêu và gửi dữ liệu hành vi của chúng cho Maji để thu thập Lollo Stamp và tham gia xổ số gay cấn!
+Tương tác với những Echo đáng yêu và gửi dữ liệu hành vi của chúng cho Maji để thu thập Lollo Stamp và tham gia xổ số gay cấn!
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14 và hoàn thành Chương II Prologue của Nhiệm Vụ Chính.
 Quy tắc sự kiện
-Trong sự kiện, bạn có thể hoàn thành các Lollo Campaign để nhận một số lượng Lollo Stamp nhất định. Mỗi Lollo Stamp cho phép bạn bóc một vé xổ số Lollo Campaign.
-Sau khi sự kiện kết thúc, các Lollo Campaign chưa hoàn thành sẽ không còn khả dụng, và tất cả Lollo Stamp còn lại sẽ bị thu hồi.</t>
+Trong sự kiện, bạn có thể hoàn thành các Chiến dịch Lollo để nhận một số lượng Lollo Stamp nhất định. Mỗi Lollo Stamp cho phép bạn bóc một vé xổ số Chiến dịch Lollo.
+Sau khi sự kiện kết thúc, các Chiến dịch Lollo chưa hoàn thành sẽ không còn khả dụng, và tất cả Lollo Stamp còn lại sẽ bị thu hồi.</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Hãy đặt &lt;color=#ffd12f&gt;Đá Neo&lt;/color&gt; vào &lt;color=#ffd12f&gt;Cột Đá Neo&lt;/color&gt; để kích hoạt. Khi được kích hoạt, nó sẽ đẩy lùi sương mù Thủy Triều Hắc Ám và tiếp sức cho Ngọn Sacred Flame tại Rừng Đỏ Thẫm.</t>
+          <t>Hãy đặt &lt;color=#ffd12f&gt;Đá Neo&lt;/color&gt; vào &lt;color=#ffd12f&gt;Cột Đá Neo&lt;/color&gt; để kích hoạt. Khi được kích hoạt, nó sẽ đẩy lùi sương mù Thủy Triều Hắc Ám và tiếp sức cho Ngọn Lửa Thiêng tại Rừng Đỏ Thẫm.</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Hollow Figure đã thức tỉnh có thể bị &lt;color=#ffd12f&gt;phá vỡ&lt;/color&gt;. Khi lại gần Hollow Figure, nó sẽ &lt;color=#ffd12f&gt;tích trữ năng lượng&lt;/color&gt; và phát nổ, triệu hồi Tacet Discord. &lt;color=#ffd12f&gt;Phá vỡ&lt;/color&gt; Hollow Figure trước khi nó hoàn tất &lt;color=#ffd12f&gt;tích trữ năng lượng&lt;/color&gt; có thể ngăn chặn việc triệu hồi.</t>
+          <t>Hình Nhân Rỗng đã thức tỉnh có thể bị &lt;color=#ffd12f&gt;phá vỡ&lt;/color&gt;. Khi lại gần Hình Nhân Rỗng, nó sẽ &lt;color=#ffd12f&gt;tích trữ năng lượng&lt;/color&gt; và phát nổ, triệu hồi Tacet Discord. &lt;color=#ffd12f&gt;Phá vỡ&lt;/color&gt; Hình Nhân Rỗng trước khi nó hoàn tất &lt;color=#ffd12f&gt;tích trữ năng lượng&lt;/color&gt; có thể ngăn chặn việc triệu hồi.</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Tương tác với Các Nút Mộng Ảo tại Sanguis Plateaus để mở khóa thử thách và xóa bỏ Những Cơn Nightmares bị phong ấn bên trong.
+          <t>Tương tác với Các Nút Mộng Ảo tại Cao Nguyên Sanguis để mở khóa thử thách và xóa bỏ Những Cơn Ác Mộng bị phong ấn bên trong.
 Mỗi Nút có ba thử thách. Hoàn thành một thử thách sẽ mở khóa thử thách tiếp theo. Hoàn thành tất cả để nhận phần thưởng.</t>
         </is>
       </c>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Trong Tidal Defense Simulator có ba loại địa hình: mặt đất, tường và trần. Combat Machines chỉ có thể triển khai trên địa hình phù hợp với loại của chúng.
+          <t>Trong Mô Phỏng Phòng Thủ Thủy Triều có ba loại địa hình: mặt đất, tường và trần. Máy Chiến Đấu chỉ có thể triển khai trên địa hình phù hợp với loại của chúng.
 Trong mỗi giai đoạn Chuẩn Bị, cậu sẽ nhận được một số Tín Dụng Mô Phỏng nhất định. Cậu cũng sẽ kiếm được thêm một ít Tín Dụng Mô Phỏng khi đánh bại Tacet Discord.</t>
         </is>
       </c>
@@ -7012,7 +7012,7 @@
       <c r="M94" t="inlineStr">
         <is>
           <t>Tacet Discord xâm nhập qua các điểm đột kích. Trong quá trình mô phỏng, chúng sẽ không tấn công cậu trực tiếp mà di chuyển theo lộ trình đã định. Cậu có thể thấy các lộ trình này dưới dạng đường đánh dấu trong giai đoạn Chuẩn Bị.
-Ngoài ra, giai đoạn Chuẩn Bị sẽ hiển thị trước chuyển động của Tacet Discord dọc theo các tuyến đường này. Hãy dùng thông tin này để triển khai Combat Machines một cách chiến lược dựa trên mô hình di chuyển của chúng.</t>
+Ngoài ra, giai đoạn Chuẩn Bị sẽ hiển thị trước chuyển động của Tacet Discord dọc theo các tuyến đường này. Hãy dùng thông tin này để triển khai Máy Chiến Đấu một cách chiến lược dựa trên mô hình di chuyển của chúng.</t>
         </is>
       </c>
     </row>
@@ -7078,8 +7078,8 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Sau khi hoàn thành một mô phỏng, cậu sẽ được trao Sao Đánh Giá dựa trên Độ Bền còn lại của Energy Matrix.
-Sao Đánh Giá có thể dùng để mở khóa Overwatch Protocols, mang lại lợi thế chiến thuật cho các mô phỏng sau này.</t>
+          <t>Sau khi hoàn thành một mô phỏng, cậu sẽ được trao Sao Đánh Giá dựa trên Độ Bền còn lại của Ma Trận Năng Lượng.
+Sao Đánh Giá có thể dùng để mở khóa Giao Thức Overwatch, mang lại lợi thế chiến thuật cho các mô phỏng sau này.</t>
         </is>
       </c>
     </row>
@@ -7145,8 +7145,8 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Trong Chế Độ Bẫy Chết, bạn có thể chọn một Tactics trong giai đoạn Chuẩn Bị trước mỗi đợt tấn công. Tactics sẽ mang lại những hiệu ứng tăng cường chiến đấu mạnh mẽ.
-Mỗi Tactics thuộc về một Tactic Set cụ thể, nơi bạn có thể xem mô tả và hiệu ứng chi tiết.</t>
+          <t>Trong Chế Độ Bẫy Chết, bạn có thể chọn một Chiến Thuật trong giai đoạn Chuẩn Bị trước mỗi đợt tấn công. Chiến Thuật sẽ mang lại những hiệu ứng tăng cường chiến đấu mạnh mẽ.
+Mỗi Chiến Thuật thuộc về một Bộ Chiến Thuật cụ thể, nơi bạn có thể xem mô tả và hiệu ứng chi tiết.</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Khi các mẫu cùng Attribute được kết nối, tất cả các mẫu đơn lẻ khác của Attribute đó sẽ bị cố định. Kéo các mẫu đã kết nối để liên kết với những mẫu cố định.</t>
+          <t>Khi các mẫu cùng Thuộc tính được kết nối, tất cả các mẫu đơn lẻ khác của Thuộc tính đó sẽ bị cố định. Kéo các mẫu đã kết nối để liên kết với những mẫu cố định.</t>
         </is>
       </c>
     </row>
@@ -7345,9 +7345,9 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Hoán Swap [Thiết Bị Đầu Cuối]
+          <t>Hoán Đổi [Thiết Bị Đầu Cuối]
 Khi có được Thiết Bị Đầu Cuối mới, bạn có thể hoán đổi chúng trong trang Thiết Bị Đầu Cuối. Các Thiết Bị chưa sở hữu sẽ không hiển thị.
-Terminal Swap chỉ áp dụng cho Rover và không khả dụng với Resonators khác. Thay đổi giới tính của Rover sẽ không ảnh hưởng đến cấu hình Thiết Bị Đầu Cuối hiện tại.</t>
+Hoán Đổi Thiết Bị Đầu Cuối chỉ áp dụng cho Rover và không khả dụng với các Resonator khác. Thay đổi giới tính của Rover sẽ không ảnh hưởng đến cấu hình Thiết Bị Đầu Cuối hiện tại.</t>
         </is>
       </c>
     </row>
@@ -7418,8 +7418,8 @@
         <is>
           <t>[Chế độ Chăm sóc Mắt]
 Chế độ Chăm sóc Mắt điều chỉnh hiển thị màn hình để dễ quan sát hơn, trừ các đoạn cắt cảnh và thành phần giao diện.
-Chế độ này có ba tùy chọn: [Low Light], [Ánh sáng mạnh] và [Custom], có thể lựa chọn phù hợp với môi trường hiện tại của người dùng.
-Trong chế độ Custom, bạn có thể điều chỉnh nhiệt độ màu, cường độ màu, độ sáng và cường độ họa tiết.
+Chế độ này có ba tùy chọn: [Ánh sáng yếu], [Ánh sáng mạnh] và [Tùy chỉnh], có thể lựa chọn phù hợp với môi trường hiện tại của người dùng.
+Trong chế độ Tùy chỉnh, bạn có thể điều chỉnh nhiệt độ màu, cường độ màu, độ sáng và cường độ họa tiết.
 Lưu ý rằng tính năng Chăm sóc Mắt không tương thích với Bộ lọc Toàn cầu.</t>
         </is>
       </c>
@@ -7487,7 +7487,7 @@
       <c r="M101" t="inlineStr">
         <is>
           <t>Trong mô phỏng này, một số Tacet Discord được bảo vệ bởi Khiên. Tacet Discord có Khiên sẽ miễn nhiễm với hiệu ứng Làm Chậm.
-Hãy sử dụng các loại Combat Machines hút vào (Máy Tạo Lốc Xoáy và Thiết Bị Xoáy Nước) để loại bỏ Khiên của Tacet Discord.</t>
+Hãy sử dụng các loại Máy Chiến Đấu hút vào (Máy Tạo Lốc Xoáy và Thiết Bị Xoáy Nước) để loại bỏ Khiên của Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord mang Âm Thanh Tử Thần - Ô Nhiễm bị &lt;color=#ffd12f&gt;hạ gục&lt;/color&gt;, chúng sẽ giải phóng Ô Nhiễm Tần Số ngay tại chỗ. Không thể triển khai Combat Machines trong khu vực bị ô nhiễm, và những máy đã triển khai &lt;color=#ffd12f&gt;sẽ bị vô hiệu hóa&lt;/color&gt;.</t>
+          <t>Khi Tacet Discord mang Âm Thanh Tử Thần - Ô Nhiễm bị &lt;color=#ffd12f&gt;hạ gục&lt;/color&gt;, chúng sẽ giải phóng Ô Nhiễm Tần Số ngay tại chỗ. Không thể triển khai Máy Chiến Đấu trong khu vực bị ô nhiễm, và những máy đã triển khai &lt;color=#ffd12f&gt;sẽ bị vô hiệu hóa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14 và hoàn thành cuộc săn đầu tiên trong Nhiệm Vụ Chính "By Sun's Burning Hand".
 Quy tắc sự kiện
-1. Event sẽ mở khóa một bộ mẫu mới mỗi ngày. Mỗi bộ gồm các mẫu với độ khó Dễ, Thường và Expert. Hoàn thành phân tích mẫu tương ứng để mở khóa phần thưởng.
+1. Sự kiện sẽ mở khóa một bộ mẫu mới mỗi ngày. Mỗi bộ gồm các mẫu với độ khó Dễ, Thường và Chuyên Gia. Hoàn thành phân tích mẫu tương ứng để mở khóa phần thưởng.
 2. Để thử thách các mẫu khó hơn trong cùng một bộ, bạn cần hoàn thành phân tích mẫu trước đó.</t>
         </is>
       </c>
@@ -7704,16 +7704,16 @@
       <c r="M104" t="inlineStr">
         <is>
           <t>Về nhiệm vụ
-Lollo Campaign lại gặp khủng hoảng bất ngờ! Để cứu đôi chân giao hàng đáng tin cậy của Maji và duy trì dịch vụ tiện lợi này, hãy giúp cậu ấy hoàn thành chương trình mới: Lollo Đồ Uống Mát Lạnh!
+Chiến dịch Lollo lại gặp khủng hoảng bất ngờ! Để cứu đôi chân giao hàng đáng tin cậy của Maji và duy trì dịch vụ tiện lợi này, hãy giúp cậu ấy hoàn thành chương trình mới: Lollo Đồ Uống Mát Lạnh!
 Hoàn thành các chiến dịch để nhận Tem Lollo – món quà tri ân từ Lollo Logistics. Tem Lollo có thể đổi lấy các kiện hàng đặc biệt từ Lollo Helper.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và hoàn thành Chương II Act V "Shadow of Glory" trong Nhiệm vụ Main.
+Đạt Cấp Liên Minh 14 và hoàn thành Chương II Hồi V "Shadow of Glory" trong Nhiệm vụ Chính.
 Quy tắc sự kiện
-Trong sự kiện, cậu có thể hoàn thành Lollo Campaign để nhận một số lượng Tem Lollo nhất định.
+Trong sự kiện, cậu có thể hoàn thành Chiến dịch Lollo để nhận một số lượng Tem Lollo nhất định.
 Mỗi Tem Lollo có thể đổi lấy một kiện hàng đặc biệt từ Lollo Helper.
 Có 3 Kho hàng cho kiện hàng đặc biệt của Lollo Helper. Khi thu thập đủ tất cả kiện hàng trong một Kho, Kho tiếp theo sẽ được mở.
 Nếu giành được dịch vụ giao hàng đặc biệt Lollo Express, cậu có thể nhận tất cả kiện hàng trong Kho hiện tại.
-Sau khi sự kiện kết thúc, các Lollo Campaign chưa hoàn thành sẽ không còn khả dụng, và tất cả Tem Lollo còn lại sẽ bị thu hồi.</t>
+Sau khi sự kiện kết thúc, các Chiến dịch Lollo chưa hoàn thành sẽ không còn khả dụng, và tất cả Tem Lollo còn lại sẽ bị thu hồi.</t>
         </is>
       </c>
     </row>
@@ -7851,9 +7851,9 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>1. Bạn có thể xem chỉ số và hiệu ứng của tất cả Combat Machines và Vũ Khí của KU-Roro trên trang này.
+          <t>1. Bạn có thể xem chỉ số và hiệu ứng của tất cả Máy Chiến Đấu và Vũ Khí của KU-Roro trên trang này.
 2. Bạn có thể nâng cấp và tăng cường chúng bằng Sim Ingot kiếm được sau khi hoàn thành một giai đoạn. 
-Đạt Cấp 3 sẽ mở khóa Mô-đun Tùy Chọn cho Combat Machines, cho phép bạn tùy chỉnh và cải thiện hiệu quả chiến đấu theo chiến thuật của mình.
+Đạt Cấp 3 sẽ mở khóa Mô-đun Tùy Chọn cho Máy Chiến Đấu, cho phép bạn tùy chỉnh và cải thiện hiệu quả chiến đấu theo chiến thuật của mình.
 3. Tất cả các nâng cấp đều có thể đặt lại để hoàn trả toàn bộ Sim Ingot.
 4. Lưu ý rằng không thể thực hiện nâng cấp hoặc thay đổi mô-đun trong khi đang diễn ra một đợt tấn công.</t>
         </is>
@@ -7929,12 +7929,12 @@
       <c r="M107" t="inlineStr">
         <is>
           <t>Giới thiệu
-KU-Ryan, một robot của Black Shores, hiện đang tìm kiếm sự hỗ trợ thu thập Surveillance Dataset về Hiện Tượng Nhiễu Sóng tại Septimont. Những ai quan tâm có thể trò chuyện với hắn.
+KU-Ryan, một robot của Black Shores, hiện đang tìm kiếm sự hỗ trợ thu thập Bộ Dữ Liệu Giám Sát về Hiện Tượng Nhiễu Sóng tại Septimont. Những ai quan tâm có thể trò chuyện với hắn.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và hoàn thành phá hủy đơn vị thử nghiệm trong Nhiệm Vụ Chính "Shadow Glory".
+Đạt Cấp Liên Minh 14 và hoàn thành phá hủy đơn vị thử nghiệm trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang".
 Quy tắc sự kiện
 1. Trong sự kiện, bạn cần kích hoạt các thử thách tại nhiều địa điểm khác nhau. Bạn có thể tham gia bất kỳ thử thách nào đã kích hoạt bao nhiêu lần tùy thích.
-2. Khi thử thách bắt đầu, Surveillance Dataset sẽ xuất hiện. Hãy cố gắng thu thập càng nhiều càng tốt trong thời gian giới hạn. Khi tất cả dữ liệu đã được thu thập hoặc hết thời gian, bạn sẽ nhận phần thưởng dựa trên điểm số đạt được.
+2. Khi thử thách bắt đầu, Bộ Dữ Liệu Giám Sát sẽ xuất hiện. Hãy cố gắng thu thập càng nhiều càng tốt trong thời gian giới hạn. Khi tất cả dữ liệu đã được thu thập hoặc hết thời gian, bạn sẽ nhận phần thưởng dựa trên điểm số đạt được.
 3. Trong thử thách có nhiều mô-đun khác nhau. Hãy tận dụng chúng một cách chiến lược để tăng tốc độ thu thập dữ liệu.
 4. Nếu có phần thưởng chưa nhận sau khi sự kiện kết thúc, chúng sẽ tự động gửi đến hộp thư của bạn khi đăng nhập lại trong vòng 30 ngày.</t>
         </is>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Trong buổi diễn tập, đánh bại Tacet Discord sẽ nhận được Mô-đun Tăng Cường. Bạn có thể sử dụng chúng tại Shop giữa các đợt để nâng cấp Resonators, Vũ Khí hoặc mua Vật Phẩm.
+          <t>Trong buổi diễn tập, đánh bại Tacet Discord sẽ nhận được Mô-đun Tăng Cường. Bạn có thể dùng chúng tại Cửa Hàng giữa các đợt để nâng cấp Resonator, Vũ Khí hoặc mua Vật Phẩm.
 Hoàn thành đủ số đợt yêu cầu để vượt qua thử thách.</t>
         </is>
       </c>
@@ -8343,11 +8343,11 @@
         <is>
           <t>Về sự kiện
 Dù có xanh mướt hay mờ ảo đến đâu, những ngày tháng học trò vẫn luôn lấp lánh như viên ngọc trong dòng sông ký ức. Những câu chuyện ấy trôi dạt giữa các vì sao, là người bạn đồng hành bên ta trong mỗi đêm tĩnh lặng.
-Khi New Solar Celebration bắt đầu, những câu chuyện nhỏ mới lại nở rộ giữa bạn và những người bạn của mình...
+Khi Lễ Hội Mặt Trời Mới bắt đầu, những câu chuyện nhỏ mới lại nở rộ giữa bạn và những người bạn của mình...
 Điều kiện tham gia
-Solve the first riddle cùng Sigrika trong Nhiệm Vụ Chính "Gold Suspended in Shadows" để mở khóa.
+Giải câu đố đầu tiên cùng Sigrika trong Nhiệm Vụ Chính "Gold Suspended in Shadows" để mở khóa.
 Quy tắc
-Tiến triển Nhiệm Vụ Chính để mở khóa các sự kiện của Resonators tương ứng. Một số sự kiện yêu cầu điều kiện đặc biệt để mở khóa. Hoàn thành "Whispers Between Stars" để nhận phần thưởng độc quyền, bao gồm Astrites và Livery.</t>
+Tiến triển Nhiệm Vụ Chính để mở khóa các sự kiện của Resonator tương ứng. Một số sự kiện yêu cầu điều kiện đặc biệt để mở khóa. Hoàn thành "Whispers Between Stars" để nhận phần thưởng độc quyền, bao gồm Astrites và Livery.</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Có thể nhận được sticker Namipon bằng cách tiêu diệt Tacet Discord, phá hủy các vật thể có thể phá hủy hoặc mở Supply Chest.
+          <t>Có thể nhận được sticker Namipon bằng cách tiêu diệt Tacet Discord, phá hủy các vật thể có thể phá hủy hoặc mở Rương Cung Cấp.
 Sticker có nhiều loại khác nhau, mỗi loại mang lại những hiệu ứng tăng cường và chỉ số cơ bản riêng.</t>
         </is>
       </c>
@@ -8480,8 +8480,8 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Dù cuộc khủng hoảng vòng lặp đã kết thúc, nhưng vẫn còn nhiều bí ẩn chưa được giải đáp ở Honami City.
-Cùng Namipon và Chisa khám phá Honami City để tìm kiếm chiến lợi phẩm, nâng cao sức chiến đấu và cải tiến Shashou Cafe. Hãy vén màn sự thật đằng sau những bất thường trong thành phố!</t>
+          <t>Dù cuộc khủng hoảng vòng lặp đã kết thúc, nhưng vẫn còn nhiều bí ẩn chưa được giải đáp ở Thành phố Honami.
+Cùng Namipon và Chisa khám phá Thành phố Honami để tìm kiếm chiến lợi phẩm, nâng cao sức chiến đấu và cải tiến Shashou Cafe. Hãy vén màn sự thật đằng sau những bất thường trong thành phố!</t>
         </is>
       </c>
     </row>
@@ -8547,8 +8547,8 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Mở khóa thêm Namipon Hỗ Trợ và Namipon Stickers khi bạn điều tra và khám phá những khu vực chưa được khám phá để tìm kiếm chiến lợi phẩm giá trị.
-Phát triển khả năng của đội khi bạn khám phá sâu hơn vào Honami City!</t>
+          <t>Mở khóa thêm Hỗ Trợ Namipon và Hình Dán Namipon khi khám phá và mạo hiểm vào những khu vực chưa được khai phá để tìm kiếm chiến lợi phẩm giá trị.
+Nâng cao sức mạnh đội ngũ của cậu khi dấn thân vào lòng thành phố Honami!</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Ngoài Sticker, Honami City còn tràn ngập những món đồ sưu tầm độc đáo. Tuy không có hiệu ứng thực tế, nhưng chúng lại rất có giá trị. Những món đồ này có thể bán cho Nhà vô địch Bán hàng để đổi lấy Rice Dango, dùng để nâng cao khả năng khám phá ở Honami.</t>
+          <t>Ngoài Sticker, Thành phố Honami còn tràn ngập những món đồ sưu tầm độc đáo. Tuy không có hiệu ứng thực tế, nhưng chúng lại rất có giá trị. Những món đồ này có thể bán cho Nhà vô địch Bán hàng để đổi lấy Bánh Dango Gạo, dùng để nâng cao khả năng khám phá ở Honami.</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Honami City hiện đã mở khám phá tự do. Ngoài Bốt Điện Thoại, cậu cũng có thể đặt xe đưa đón Namipon từ menu Preparations. Chọn tùy chọn này sẽ cho phép cậu rút lui bất cứ lúc nào.</t>
+          <t>Thành phố Honami hiện đã mở khám phá tự do. Ngoài Bốt Điện Thoại, cậu cũng có thể đặt xe đưa đón Namipon từ menu Chuẩn Bị. Chọn tùy chọn này sẽ cho phép cậu rút lui bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -8754,16 +8754,16 @@
       <c r="M119" t="inlineStr">
         <is>
           <t>Giới thiệu
-Mạng lưới tuyến đường của Lahai-Roi, cùng với Spacetrek Observatory từng giám sát địa hình, hệ sinh thái và khí hậu của khu vực, đã bị cơn Void Storm tàn phá. Đã đến lúc tái thiết tất cả!
-Hãy sử dụng vật liệu tái thiết thu thập tại Lahai-Roi để hỗ trợ Dhalifa khôi phục Mạng Lưới Tuyến Đường và Spacetrek Observatory.
+Mạng lưới tuyến đường của Lahai-Roi, cùng với Đài Quan Sát Spacetrek từng giám sát địa hình, hệ sinh thái và khí hậu của khu vực, đã bị cơn Bão Hư Không tàn phá. Đã đến lúc tái thiết tất cả!
+Hãy sử dụng vật liệu tái thiết thu thập tại Lahai-Roi để hỗ trợ Dhalifa khôi phục Mạng Lưới Tuyến Đường và Đài Quan Sát Spacetrek.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 8 và hoàn thành Nhiệm Vụ Guide "Chiến Dịch: Tái Thiết Biên Cương".
+Đạt Cấp Liên Minh 8 và hoàn thành Nhiệm Vụ Hướng Dẫn "Chiến Dịch: Tái Thiết Biên Cương".
 Quy tắc sự kiện
-Explore Lahai-Roi và sử dụng 3 loại vật liệu để tái thiết 10 tuyến đường.
-Khi tiếp cận một Bộ Xây Dựng Tuyến Đường, nó sẽ mở khóa thành điểm Di Chuyển Nhanh.
+Khám phá Lahai-Roi và sử dụng 3 loại vật liệu để tái thiết 10 tuyến đường.
+Khi tiếp cận một Bộ Xây Dựng Tuyến Đường, nó sẽ mở khóa thành điểm Dịch Chuyển Nhanh.
 Sau khi kích hoạt, Bộ Xây Dựng sẽ tự động hoàn thành tái thiết tuyến đường. Các tuyến đường được khôi phục sẽ hồi sinh khu vực xung quanh, mở khóa nhiều nhiệm vụ phụ và thử thách đa dạng.
-Mỗi tuyến đường hoàn thành sẽ tăng Network Activity. Đạt đến các mốc Activity nhất định sẽ thúc đẩy tiến độ tái thiết Spacetrek Observatory.
-Event này có sẵn vĩnh viễn. Từ Phiên Bản 3.0 trở đi, bạn có thể truy cập sự kiện này qua Guide Khu Vực trên bản đồ Lahai-Roi.</t>
+Mỗi tuyến đường hoàn thành sẽ tăng Hoạt Động Mạng. Đạt đến các mốc Hoạt Động nhất định sẽ thúc đẩy tiến độ tái thiết Đài Quan Sát Spacetrek.
+Sự kiện này có sẵn vĩnh viễn. Từ Phiên Bản 3.0 trở đi, bạn có thể truy cập sự kiện này qua Hướng Dẫn Khu Vực trên bản đồ Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -8908,8 +8908,8 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khi khám phá Honami City, sau khi mang bất kỳ vật phẩm không thể trang bị chất lượng Legendary về quán Shashou Cafe lần đầu, vật phẩm đó sẽ được trưng bày trong Thư viện.
-Ngay cả khi sau này bạn bán vật phẩm đó từ Warehouse, nó vẫn sẽ được giữ lại trong Thư viện.</t>
+          <t>Khi khám phá Thành Phố Honami, sau khi mang bất kỳ vật phẩm không thể trang bị chất lượng Huyền Thoại về quán Shashou Cafe lần đầu, vật phẩm đó sẽ được trưng bày trong Bộ Sưu Tập.
+Ngay cả khi sau này bạn bán vật phẩm đó từ Kho, nó vẫn sẽ được giữ lại trong Bộ Sưu Tập.</t>
         </is>
       </c>
     </row>
@@ -9050,14 +9050,14 @@
       <c r="M123" t="inlineStr">
         <is>
           <t>Về sự kiện
-Người chơi mới có thể nhận phần thưởng bonus và mở khóa Resonators Hỗ Trợ mới thông qua sự kiện này để hỗ trợ quá trình lên cấp.
+Người chơi mới có thể nhận phần thưởng bonus và mở khóa Resonator Hỗ Trợ mới thông qua sự kiện này để hỗ trợ quá trình lên cấp.
 Điều kiện tham gia
 Tạo nhân vật sau 04:00 ngày 12-12-2025 (giờ máy chủ) trong thời gian diễn ra sự kiện.
 Quy tắc
 Sự kiện Herald of New Tides kéo dài 30 ngày.
-Trong sự kiện, khi mở khóa các Giai đoạn SOL3 mới, người chơi mới có thể nhận phần thưởng Astrite và Kinh nghiệm Data Bank cùng Resonators Hỗ Trợ 5 sao: Yinlin, Jinhsi, Changli, Shorekeeper và Camellya.
-Trong sự kiện, để hỗ trợ người chơi mới lên cấp nhanh hơn, bạn sẽ được tiếp cận các địa điểm chứa vật liệu nâng cấp và Echoes được khuyến nghị của Resonators Đặc Trưng hiện tại và Resonators New Voyage.
-(Lưu ý: Resonators Hỗ Trợ chỉ có thể tham gia cùng bạn ở thế giới mở và một số Sonoro Spheres định kỳ)</t>
+Trong sự kiện, khi mở khóa các Giai đoạn SOL3 mới, người chơi mới có thể nhận phần thưởng Astrite và Kinh nghiệm Data Bank cùng các Resonator Hỗ Trợ 5 sao: Yinlin, Jinhsi, Changli, Shorekeeper và Camellya.
+Trong sự kiện, để hỗ trợ người chơi mới lên cấp nhanh hơn, bạn sẽ được tiếp cận các địa điểm chứa vật liệu nâng cấp và Echo được khuyến nghị của Resonator Đặc Trưng hiện tại và Resonator New Voyage.
+(Lưu ý: Resonator Hỗ Trợ chỉ có thể tham gia cùng bạn ở thế giới mở và một số Sonoro Spheres định kỳ)</t>
         </is>
       </c>
     </row>
@@ -9129,11 +9129,11 @@
       <c r="M124" t="inlineStr">
         <is>
           <t>Về sự kiện
-Tham gia Pioneer Project Lahai-Roi do Spacetrek Collective khởi xướng! Explore mọi ngóc ngách của Lahai-Roi, khám phá những điều kỳ diệu và nhận thưởng trên hành trình.
+Tham gia Dự Án Tiên Phong Lahai-Roi do Spacetrek Collective khởi xướng! Khám phá mọi ngóc ngách của Lahai-Roi, khám phá những điều kỳ diệu và nhận thưởng trên hành trình.
 Điều kiện tham gia
 Đạt Cấp Liên Minh 8 và đến Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nấp Dưới Băng Giá" để mở khóa.
 Quy tắc sự kiện
-Hoàn thành nhiệm vụ sự kiện để thu thập Exploration Data, sau đó sử dụng nó để nâng cấp Cấp Tiên Phong. Cấp càng cao, phần thưởng càng hấp dẫn.
+Hoàn thành nhiệm vụ sự kiện để thu thập Dữ Liệu Thám Hiểm, sau đó sử dụng nó để nâng cấp Cấp Tiên Phong. Cấp càng cao, phần thưởng càng hấp dẫn.
 Lưu ý rằng một số nhiệm vụ sự kiện không thể hoàn thành ở Chế Độ Hợp Tác, và tính năng theo dõi nhiệm vụ có thể bị vô hiệu hóa trong một số tình huống nhất định.</t>
         </is>
       </c>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>1. Guide Khu Vực hiển thị các lối chơi và tính năng độc quyền của từng khu vực. Tại đây, bạn có thể nhanh chóng xem, tìm kiếm và truy cập nội dung đặc biệt của các khu vực khác nhau.
+          <t>1. Hướng Dẫn Khu Vực hiển thị các lối chơi và tính năng độc quyền của từng khu vực. Tại đây, bạn có thể nhanh chóng xem, tìm kiếm và truy cập nội dung đặc biệt của các khu vực khác nhau.
 2. Các lối chơi hoặc tính năng cụ thể trong khu vực đã mở khóa có thể được ghim. Điều này sẽ đánh dấu lối chơi hoặc tính năng đã ghim trên giao diện bản đồ. Bạn có thể ghim tối đa 2 lối chơi và/hoặc tính năng.</t>
         </is>
       </c>
@@ -9268,9 +9268,9 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Cậu có thể nâng cấp Mô-đun Mở Rộng bằng Points Cải Tiến khi đáp ứng các điều kiện sau:
+          <t>Cậu có thể nâng cấp Mô-đun Mở Rộng bằng Điểm Cải Tiến khi đáp ứng các điều kiện sau:
 1. Mô-đun Chuyên Biệt có thể nâng cấp sau khi mô-đun trước đó đã đạt Cấp 1.
-2. Core Mô-đun có thể nâng cấp khi có đủ Points Cải Tiến.</t>
+2. Mô-đun Cốt Lõi có thể nâng cấp khi có đủ Điểm Cải Tiến.</t>
         </is>
       </c>
     </row>
@@ -9338,8 +9338,8 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Các Mô-đun Mở Rộng có Points Nâng Cấp và Nhiệm Vụ Nâng Cấp tương ứng.
-Nhiệm Vụ Nâng Cấp gồm có Permanent, Thời Hạn và Định Kỳ.
+          <t>Các Mô-đun Mở Rộng có Điểm Nâng Cấp và Nhiệm Vụ Nâng Cấp tương ứng.
+Nhiệm Vụ Nâng Cấp gồm có Vĩnh Viễn, Thời Hạn và Định Kỳ.
 Nhiệm Vụ Thời Hạn phải hoàn thành trong khoảng thời gian quy định. Khi hết thời gian, nhiệm vụ sẽ không thể tiếp tục và phần thưởng sẽ không được trao nếu chưa hoàn thành.
 Các Nhiệm Vụ Thời Hạn trong phiên bản này sẽ được thay thế bằng Nhiệm Vụ Định Kỳ sau bản cập nhật tiếp theo. Nhiệm Vụ Định Kỳ cũng là vĩnh viễn. Người chơi có thể hoàn thành chúng để kiếm đủ điểm cho Mô-đun Mở Rộng tương ứng.</t>
         </is>
@@ -9407,8 +9407,8 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Cậu có thể triển khai Echoes bằng cách trang bị các Echoes đã mở khóa từ Thư viện vào Máy Triển Khai thông qua bảng Wheel Công cụ. 
-Khi ở trong khu vực chỉ định, các Echoes được triển khai có thể thực hiện kỹ năng đặc biệt để giúp cậu giải đố.</t>
+          <t>Cậu có thể triển khai Echo bằng cách trang bị các Echo đã mở khóa từ Bộ Sưu Tập vào Máy Triển Khai thông qua bảng Bánh Xe Tiện Ích. 
+Khi ở trong khu vực chỉ định, các Echo được triển khai có thể thực hiện kỹ năng đặc biệt để giúp cậu giải đố.</t>
         </is>
       </c>
     </row>
@@ -9484,16 +9484,16 @@
       <c r="M129" t="inlineStr">
         <is>
           <t>Giới thiệu
-Mạng lưới tuyến đường của Lahai-Roi, cùng với Spacetrek Observatory từng giám sát địa hình, hệ sinh thái và khí hậu của khu vực, đã bị cơn Void Storm tàn phá. Đã đến lúc tái thiết tất cả!
-Hãy sử dụng vật liệu tái thiết thu thập tại Lahai-Roi để hỗ trợ Dhalifa khôi phục Mạng Lưới Tuyến Đường và Spacetrek Observatory.
+Mạng lưới tuyến đường của Lahai-Roi, cùng với Đài Quan Sát Spacetrek từng giám sát địa hình, hệ sinh thái và khí hậu của khu vực, đã bị cơn Bão Hư Không tàn phá. Đã đến lúc tái thiết tất cả!
+Hãy sử dụng vật liệu tái thiết thu thập tại Lahai-Roi để hỗ trợ Dhalifa khôi phục Mạng Lưới Tuyến Đường và Đài Quan Sát Spacetrek.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 8 và hoàn thành Nhiệm Vụ Guide "Chiến Dịch: Tái Thiết Biên Cương".
+Đạt Cấp Liên Minh 8 và hoàn thành Nhiệm Vụ Hướng Dẫn "Chiến Dịch: Tái Thiết Biên Cương".
 Quy tắc sự kiện
-Explore Lahai-Roi và sử dụng 3 loại vật liệu để tái thiết 10 tuyến đường.
-Khi tiếp cận một Bộ Xây Dựng Tuyến Đường, nó sẽ mở khóa thành điểm Di Chuyển Nhanh.
+Khám phá Lahai-Roi và sử dụng 3 loại vật liệu để tái thiết 10 tuyến đường.
+Khi tiếp cận một Bộ Xây Dựng Tuyến Đường, nó sẽ mở khóa thành điểm Dịch Chuyển Nhanh.
 Sau khi kích hoạt, Bộ Xây Dựng sẽ tự động hoàn thành tái thiết tuyến đường. Các tuyến đường được khôi phục sẽ hồi sinh khu vực xung quanh, mở khóa nhiều nhiệm vụ phụ và thử thách đa dạng.
-Mỗi tuyến đường hoàn thành sẽ tăng Network Activity. Đạt đến các mốc Activity nhất định sẽ thúc đẩy tiến độ tái thiết Spacetrek Observatory.
-Event này có sẵn vĩnh viễn. Từ Phiên Bản 3.0 trở đi, bạn có thể truy cập sự kiện này qua Guide Khu Vực trên bản đồ Lahai-Roi.</t>
+Mỗi tuyến đường hoàn thành sẽ tăng Hoạt Động Mạng. Đạt đến các mốc Hoạt Động nhất định sẽ thúc đẩy tiến độ tái thiết Đài Quan Sát Spacetrek.
+Sự kiện này có sẵn vĩnh viễn. Từ Phiên Bản 3.0 trở đi, bạn có thể truy cập sự kiện này qua Hướng Dẫn Khu Vực trên bản đồ Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Bạn có thể triệu hồi xe máy thám hiểm hoặc điều chỉnh cài đặt liên quan qua Wheel Công cụ. Xe máy không thể được triệu hồi trong trận chiến hoặc khi không đủ không gian.</t>
+          <t>Bạn có thể triệu hồi xe máy thám hiểm hoặc điều chỉnh cài đặt liên quan qua Bánh Xe Tiện Ích. Xe máy không thể được triệu hồi trong trận chiến hoặc khi không đủ không gian.</t>
         </is>
       </c>
     </row>
@@ -9624,8 +9624,8 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Nhấn nút Tự Lái để kích hoạt Autopilot Mode.
-Trong chế độ này, bạn có thể bật Cinematic Mode, tỷ lệ khung hình trò chơi sẽ thay đổi và camera sẽ tự động di chuyển.</t>
+          <t>Nhấn nút Tự Lái để kích hoạt Chế Độ Tự Lái.
+Trong chế độ này, bạn có thể bật Chế Độ Điện Ảnh, tỷ lệ khung hình trò chơi sẽ thay đổi và camera sẽ tự động di chuyển.</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Chế Độ Lái Tự Động cho phép di chuyển camera tự do và tự động tránh chướng ngại vật (như phương tiện giao thông) trên đường. Trong chế độ này, bạn có thể thoải mái điều khiển góc nhìn, nghe Kênh Radio Heart, chụp ảnh hoặc chuyển sang Cinematic Mode khi khả dụng.</t>
+          <t>Chế Độ Lái Tự Động cho phép di chuyển camera tự do và tự động tránh chướng ngại vật (như phương tiện giao thông) trên đường. Trong chế độ này, bạn có thể thoải mái điều khiển góc nhìn, nghe Kênh Radio Heart, chụp ảnh hoặc chuyển sang Chế Độ Điện Ảnh khi khả dụng.</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Cần ba nguyên liệu đặc biệt để kích hoạt Bộ Tạo Lộ Trình: &lt;color=#ffd12f&gt;Mechanite&lt;/color&gt;, &lt;color=#ffd12f&gt;Compressed Bedrock&lt;/color&gt;, và &lt;color=#ffd12f&gt;Core Bộ Tạo&lt;/color&gt;. Mỗi nguyên liệu có thể thu thập bằng các phương pháp khác nhau.</t>
+          <t>Cần ba nguyên liệu đặc biệt để kích hoạt Bộ Tạo Lộ Trình: &lt;color=#ffd12f&gt;Mechanite&lt;/color&gt;, &lt;color=#ffd12f&gt;Đá Nền Nén&lt;/color&gt;, và &lt;color=#ffd12f&gt;Lõi Bộ Tạo&lt;/color&gt;. Mỗi nguyên liệu có thể thu thập bằng các phương pháp khác nhau.</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Sau khi hoàn tất việc tái thiết mạng lưới tuyến đường, hãy sử dụng Autopilot Mode của xe máy thám hiểm để nhanh chóng di chuyển đến Trạm Xây Dựng Tuyến Đường tiếp theo và tiến hành công việc tái thiết tiếp theo.</t>
+          <t>Sau khi hoàn tất việc tái thiết mạng lưới tuyến đường, hãy sử dụng Chế Độ Tự Lái của xe máy thám hiểm để nhanh chóng di chuyển đến Trạm Xây Dựng Tuyến Đường tiếp theo và tiến hành công việc tái thiết tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -10150,8 +10150,8 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#ffd12f&gt;Hoạt động Mạng đạt đến một mức nhất định&lt;/color&gt;, các nhiệm vụ dự án sẽ mở ra để thúc đẩy &lt;color=#ffd12f&gt;giai đoạn tái thiết Spacetrek Observatory&lt;/color&gt;.
-Hoàn thành tái thiết Spacetrek Observatory sẽ mở khóa tính năng Weather Simulation, cho phép người chơi thay đổi thời tiết ở khu vực Lahai-Roi.</t>
+          <t>Khi &lt;color=#ffd12f&gt;Hoạt động Mạng đạt đến một mức nhất định&lt;/color&gt;, các nhiệm vụ dự án sẽ mở ra để thúc đẩy &lt;color=#ffd12f&gt;giai đoạn tái thiết Đài Thiên Văn Spacetrek&lt;/color&gt;.
+Hoàn thành tái thiết Đài Thiên Văn Spacetrek sẽ mở khóa tính năng Mô Phỏng Thời Tiết, cho phép người chơi thay đổi thời tiết ở khu vực Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -10217,8 +10217,8 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Khi Hyvatia mở Mắt Tiên Tri, nó sẽ quan sát và ghi lại các pha Dodge và Phản Đòn của Resonators.
-Sau đó, đòn tấn công tiếp theo của Hyvatia sẽ không thể Dodge hay Phản Đòn.</t>
+          <t>Khi Hyvatia mở Mắt Tiên Tri, nó sẽ quan sát và ghi lại các pha Né Tránh và Phản Đòn của Resonator.
+Sau đó, đòn tấn công tiếp theo của Hyvatia sẽ không thể Né Tránh hay Phản Đòn.</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Sau vài lần tấn công hoặc phản đòn, Vulnerable Core sẽ lộ ra trên cánh tay trái của Reactor Husk. Attack vào lõi lộ ra sẽ phá hủy giáp của Reactor Husk, khiến nó không thể tấn công được nữa.</t>
+          <t>Sau vài lần tấn công hoặc phản đòn, Lõi Dễ Tổn Thương sẽ lộ ra trên cánh tay trái của Reactor Husk. Tấn công vào lõi lộ ra sẽ phá hủy giáp của Reactor Husk, khiến nó không thể tấn công được nữa.</t>
         </is>
       </c>
     </row>
@@ -10349,8 +10349,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Bên trong Solisylum, Heliogyre đã bị vô hiệu hóa.
-Rotate sáu &lt;color=#ffd12f&gt;Stars&lt;/color&gt; để căn chỉnh chùm tia của chúng hướng về Heliogyre và kích hoạt lại nó.</t>
+          <t>Trong Solisylum, Heliogyre đã bị vô hiệu hóa.</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10414,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Trong Nhiệm Vụ Khám Phá "Nơi Light Hóa Hình", các Rover sẽ cần thu thập Soliskin, thứ sẽ đồng hành cùng các ngươi khi đi qua &lt;color=#ffd12f&gt;Bjartr Woods&lt;/color&gt;.</t>
+          <t>Trong Nhiệm Vụ Khám Phá "Nơi Ánh Sáng Hóa Hình", các Vận Mệnh Giả sẽ cần thu thập Soliskin, thứ sẽ đồng hành cùng các ngươi khi đi qua &lt;color=#ffd12f&gt;Bjartr Woods&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10611,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Ngươi có thể xem và trang bị tất cả Echoes có sẵn trong trang chỉnh sửa. Dùng Công cụ: Máy Chiếu để mở menu lựa chọn và chọn Echoes cần chiếu. Một số khu vực có câu đố yêu cầu tương tác đặc biệt. Hãy dùng Máy Chiếu để tạo ra Hình Ảnh Echoes phù hợp, hỗ trợ việc khám phá của ngươi.</t>
+          <t>Ngươi có thể xem và trang bị tất cả Echo có sẵn trong trang chỉnh sửa. Sử dụng Tiện Ích: Projector to call out the selection menu and choose the Echo to be projected. Some areas present puzzles that require special interactions. Use the Projector to create the appropriate Echo Projection to help your exploration.</t>
         </is>
       </c>
     </row>
@@ -10677,7 +10676,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Nhện Địa Chấn S4 ở Lahai-Roi thường bị hút về những nơi ngập tràn Ánh Sáng Lumi, nơi chúng thực hiện Lễ Revelation Ánh Sáng. Khi lễ kết thúc, Ánh Sáng Lumi dần tắt đi, để lộ những vật thể ẩn giấu bên trong.</t>
+          <t>Nhện Địa Chấn S4 ở Lahai-Roi thường bị hút về những nơi ngập tràn Ánh Sáng Lumi, nơi chúng thực hiện Lễ Khải Huyền Ánh Sáng. Khi lễ kết thúc, Ánh Sáng Lumi dần tắt đi, để lộ những vật thể ẩn giấu bên trong.</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10741,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Ở Lahai-Roi, Mining Reindeer có thể phát hiện Soliskin gần đó bị phong ấn trong các tinh thể Luxite đặc biệt. Chúng có thể bắn ra một chùm tia laser liên tục để phá vỡ lớp vỏ đá bên ngoài, giúp cậu giải phóng Soliskin bị mắc kẹt.</t>
+          <t>Ở Lahai-Roi, Tuần Lộc Khai Thác có thể phát hiện Soliskin gần đó bị phong ấn trong các tinh thể Luxite đặc biệt. Chúng có thể bắn ra một chùm tia laser liên tục để phá vỡ lớp vỏ đá bên ngoài, giúp cậu giải phóng Soliskin bị mắc kẹt.</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10806,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Khi di chuyển trên Cruise Conduit, bạn có thể nhảy sang các Cruise Conduit liền kề. Giữ phím điều hướng và nhấn Nhảy để nhảy khỏi conduit theo hướng tương ứng.</t>
+          <t>Khi di chuyển trên Cruise Conduit, bạn có thể nhảy sang các Cruise Conduit liền kề. Giữ phím điều hướng và nhấn Jump để nhảy khỏi conduit theo hướng tương ứng.</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10871,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Cậu kiếm được Points Lướt Ray bằng cách Lướt Ray. Sử dụng Drift Ray để thu thập điểm ở hai bên đường ray. Dùng Bật Nhảy để lấy điểm trên không. Kiếm đủ Points Lướt Ray để đổi lấy phần thưởng Shell Credit.</t>
+          <t>Cậu kiếm được Điểm Lướt Ray bằng cách Lướt Ray. Sử dụng Drift Ray để thu thập điểm ở hai bên đường ray. Dùng Nhảy Bật để lấy điểm trên không. Kiếm đủ Điểm Lướt Ray để đổi lấy phần thưởng Shell Credit.</t>
         </is>
       </c>
     </row>
@@ -10937,7 +10936,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Domain là loại thẻ mới được thêm vào phiên bản Lahai-Roi của *Peaks of Prestige*. Những thẻ này sở hữu sức mạnh cực kỳ đáng gờm, có thể xoay chuyển cục diện của bất kỳ trận đấu nào.</t>
+          <t>Tổ Tacet là loại thẻ mới được thêm vào phiên bản Lahai-Roi của *Peaks of Prestige*. Những thẻ này sở hữu sức mạnh cực kỳ đáng gờm, có thể xoay chuyển cục diện của bất kỳ trận đấu nào.</t>
         </is>
       </c>
     </row>
@@ -11003,8 +11002,8 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Cube Blocker Cube&lt;/color&gt; là thành phần cốt lõi của Smartprint Cube. Nó có thể di chuyển dọc theo mạch điện miễn là có đủ không gian an toàn trên đường đi.
-&lt;color=#ffd12f&gt;Cube Blocker Cube&lt;/color&gt; có hai dạng, mỗi dạng yêu cầu không gian an toàn khác nhau để di chuyển.</t>
+          <t>&lt;color=#ffd12f&gt;Khối Chặn Cube&lt;/color&gt; là thành phần cốt lõi của Smartprint Cube. Nó có thể di chuyển dọc theo mạch điện miễn là có đủ không gian an toàn trên đường đi.
+&lt;color=#ffd12f&gt;Khối Chặn Cube&lt;/color&gt; có hai dạng, mỗi dạng yêu cầu không gian an toàn khác nhau để di chuyển.</t>
         </is>
       </c>
     </row>
@@ -11070,8 +11069,8 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Một số quá trình biên dịch sẽ liên quan đến nhiều Cube Cản Trở. Tất cả các Cube Cản Trở phải đến được Mô-đun Điểm Kết để hoàn tất biên dịch.
-Bạn chỉ có thể điều khiển một Cube Cản Trở tại một thời điểm. Sử dụng nút &lt;color=#ffd12f&gt;Switch đổi&lt;/color&gt; để đổi giữa các Khối.</t>
+          <t>Một số quá trình biên dịch sẽ liên quan đến nhiều Khối Lập Phương Cản Trở. Tất cả các Khối Lập Phương Cản Trở phải đến được Mô-đun Điểm Kết để hoàn tất biên dịch.
+Bạn chỉ có thể điều khiển một Khối Lập Phương Cản Trở tại một thời điểm. Sử dụng nút &lt;color=#ffd12f&gt;Chuyển đổi&lt;/color&gt; để đổi giữa các Khối.</t>
         </is>
       </c>
     </row>
@@ -11140,11 +11139,11 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>[Customization Ngoại Hình]
+          <t>[Tùy Chỉnh Ngoại Hình]
 Bạn có thể gắn các mô-đun tùy chỉnh khác nhau lên xe máy thám hiểm để thay đổi diện mạo của nó.
 [Lưu Ý]
 Mỗi món đồ Ngoại Hình Xe chỉ có thể mua một lần và chỉ dùng được cho xe máy thám hiểm.
-Các món đồ Ngoại Hình Xe chỉ có thể sử dụng sau khi mở khóa xe máy ở Chương III Act I. Tuy nhiên, bạn vẫn có thể mua trước và chúng sẽ tự động kích hoạt sau khi mở khóa giấy phép.</t>
+Các món đồ Ngoại Hình Xe chỉ có thể sử dụng sau khi mở khóa xe máy ở Chương III Hồi I. Tuy nhiên, bạn vẫn có thể mua trước và chúng sẽ tự động kích hoạt sau khi mở khóa giấy phép.</t>
         </is>
       </c>
     </row>
@@ -11214,7 +11213,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>[Customization Ngoại Hình]
+          <t>[Tùy Chỉnh Ngoại Hình]
 Bạn có thể áp dụng nhiều món đồ ngoại hình khác nhau cho xe máy thám hiểm để thay đổi diện mạo của nó.
 [Nhập Cài Đặt Có Sẵn]
 Bạn có thể lưu và nhập các cài đặt tùy chỉnh để áp dụng nhanh chóng.
@@ -11357,9 +11356,9 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>- Một bộ bài gồm 22 lá, bao gồm một Domain, một Echoes Cốt Core và các Echoes Thường hoặc Vật Phẩm Đặc Biệt.
+          <t>- Một bộ bài gồm 22 lá, bao gồm một Miền, một Echo Cốt Lõi và các Echo Thường hoặc Vật Phẩm Đặc Biệt.
 - Số lượng lá bài trong bộ bài có giới hạn trên và yêu cầu tối thiểu để có thể tiến hành trận đấu.
-- Các lá bài có những Skills khác nhau. Một số Skills bổ trợ hoặc tăng cường cho các Skills khác. Hãy lưu ý điều này khi xây dựng bộ bài của bạn.</t>
+- Các lá bài có những Kỹ Năng khác nhau. Một số Kỹ Năng bổ trợ hoặc tăng cường cho các Kỹ Năng khác. Hãy lưu ý điều này khi xây dựng bộ bài của bạn.</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11424,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>- {Cus:Ipt,Touch=Touch PC=click Gamepad=Ấn} vào các lá bài trong danh sách bên trái để thêm vào bộ bài.
+          <t>- {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào các lá bài trong danh sách bên trái để thêm vào bộ bài.
 - Mỗi bộ bài chỉ có thể chứa lá bài của tối đa 2 Thuộc Tính. Để thay đổi Thuộc Tính, hãy xóa các lá bài có Thuộc Tính muốn thay thế khỏi bộ bài trước.</t>
         </is>
       </c>
@@ -11492,7 +11491,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>- &lt;color=#ffd12f&gt;Tâm Ảnh Cốt Core&lt;/color&gt; là những Tâm Ảnh cấp Overlord hoặc Calamity tại Solaris. Mỗi bộ bài phải chứa đúng một Tâm Ảnh Cốt Core. Sức mạnh áp đảo của nó biến nó thành nền tảng của một bộ bài mạnh. Hoàn thành các Thử Thách tương ứng để thêm Tâm Ảnh Cốt Core vào bộ bài của bạn.
+          <t>- &lt;color=#ffd12f&gt;Tâm Ảnh Cốt Lõi&lt;/color&gt; là những Tâm Ảnh cấp Overlord hoặc Calamity tại Solaris. Mỗi bộ bài phải chứa đúng một Tâm Ảnh Cốt Lõi. Sức mạnh áp đảo của nó biến nó thành nền tảng của một bộ bài mạnh. Hoàn thành các Thử Thách tương ứng để thêm Tâm Ảnh Cốt Lõi vào bộ bài của bạn.
 - &lt;color=#ffd12f&gt;Tâm Ảnh Thường&lt;/color&gt; có chi phí từ 1 đến 3 và thuộc cấp Common hoặc Elite tại Solaris. Một bộ bài phải chứa tổng cộng 20 Tâm Ảnh Thường hoặc Vật Phẩm Đặc Biệt để bắt đầu trận đấu.</t>
         </is>
       </c>
@@ -11560,9 +11559,9 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>1. Nhận được Dải Sóng của Resonators 5-Star sẽ cấp Journey Points. Resonators 5-Star được triệu hồi từ lần thứ 8 trở đi vẫn tính vào Journey Points.
-2. Weapons 5-Star tiêu hao trong Hợp Tần vẫn tính vào Journey Points.
-3. Nhận Rover, Dải Sóng của Rover và bất kỳ Weapons 5-Star nào thông qua nhiệm vụ sẽ không tính vào Journey Points.</t>
+          <t>1. Nhận được Dải Sóng của Resonator 5 Sao sẽ cấp Điểm Hành Trình. Resonator 5 Sao được triệu hồi từ lần thứ 8 trở đi vẫn tính vào Điểm Hành Trình.
+2. Vũ khí 5 Sao tiêu hao trong Hợp Tần vẫn tính vào Điểm Hành Trình.
+3. Nhận Rover, Dải Sóng của Rover và bất kỳ Vũ khí 5 Sao nào thông qua nhiệm vụ sẽ không tính vào Điểm Hành Trình.</t>
         </is>
       </c>
     </row>
@@ -11629,9 +11628,9 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>1. Hoàn thành Nhiệm Vụ Con Đường Sao để kiếm Journey Points. Đạt các mốc Journey Points để nhận Quà Con Đường Sao.
-2. Mỗi Nhiệm Vụ Con Đường Sao có giới hạn Journey Points. Khi đạt giới hạn, cậu sẽ không thể kiếm thêm điểm từ nhiệm vụ đó.
-3. Trong các bản cập nhật tương lai, sẽ có thêm nhiều quà tặng và giới hạn Journey Points cũng sẽ được tăng lên. Hãy đón chờ nhé.</t>
+          <t>1. Hoàn thành Nhiệm Vụ Con Đường Sao để kiếm Điểm Hành Trình. Đạt các mốc Điểm Hành Trình để nhận Quà Con Đường Sao.
+2. Mỗi Nhiệm Vụ Con Đường Sao có giới hạn Điểm Hành Trình. Khi đạt giới hạn, cậu sẽ không thể kiếm thêm điểm từ nhiệm vụ đó.
+3. Trong các bản cập nhật tương lai, sẽ có thêm nhiều quà tặng và giới hạn Điểm Hành Trình cũng sẽ được tăng lên. Hãy đón chờ nhé.</t>
         </is>
       </c>
     </row>
@@ -11698,9 +11697,9 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>[Rules]
-Hoàn thành Chương III Act III "The Star That Voyages Far" trong Nhiệm Vụ Chính để nhận Trang phục miễn phí "Perpetual Spark" cho Rover.
-Cả hai bộ Trang phục và Ảnh Đại Diện đều có thể nhận được khi xác nhận.</t>
+          <t>[Quy Tắc]
+Hoàn thành Chương III Hồi III "Ngôi Sao Viễn Du" trong Nhiệm Vụ Chính để nhận Trang Phục miễn phí "Tia Lửa Vĩnh Cửu" cho Rover.
+Cả hai bộ Trang Phục và Ảnh Đại Diện đều có thể nhận được khi xác nhận.</t>
         </is>
       </c>
     </row>
@@ -11780,7 +11779,7 @@
 [Thứ Tự Di Chuyển]
 Dễ: Người chơi và 1 Exoswarm thay phiên di chuyển, người chơi đi trước.
 Khó: Người chơi và 2 Exoswarm thay phiên di chuyển theo thứ tự: Người chơi → Exoswarm thứ nhất → Người chơi → Exoswarm thứ hai, lặp lại.
-[Game Rules]
+[Luật Chơi]
 - Điều Kiện Chiến Thắng: Hoàn thành màn chơi khi bao vây hoàn toàn tất cả Exoswarm, không để chúng thoát ra.
 - Điều Kiện Thất Bại: Thua màn chơi nếu bất kỳ Exoswarm nào trốn thoát khỏi khu vực băng giá hiện tại.
 [Yêu Cầu Hỗ Trợ]
@@ -11860,10 +11859,10 @@
           <t>Về sự kiện
 Vùng đất băng giá Lahai-Roi đang vẫy gọi những tâm hồn tò mò. Nhiều người bị mê hoặc bởi những khoảng trắng vô tận nơi đây. Những kẻ tìm kiếm chân lý bước từng bước trên vùng cực này, truy đuổi những tiếng vọng mơ hồ của sự thật trong thế giới băng tuyết lặng im. Giờ đây, hãy cùng họ khám phá vùng đất băng giá và đặt chân đến những nơi chưa ai từng đến.
 Điều kiện tham gia
-Lần đầu đặt chân đến Bề Mặt Vùng Đất Băng Giá trong Nhiệm Vụ Chính "The Star That Voyages Far".
+Lần đầu đặt chân đến Bề Mặt Vùng Đất Băng Giá trong Nhiệm Vụ Chính "Ngôi Sao Viễn Du".
 Thể lệ sự kiện
-- Event được chia thành bốn giai đoạn, mở khóa khi bạn tiến triển trong Nhiệm Vụ Chính. Hoàn thành nhiệm vụ sự kiện để nhận những phần thưởng hậu hĩnh.
-- Nếu có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận qua Mail.
+- Sự kiện được chia thành bốn giai đoạn, mở khóa khi bạn tiến triển trong Nhiệm Vụ Chính. Hoàn thành nhiệm vụ sự kiện để nhận những phần thưởng hậu hĩnh.
+- Nếu có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận qua Thư.
 - Lưu ý rằng một số nội dung sự kiện không khả dụng trong chế độ Đồng Đội, và Theo Dõi Nhiệm Vụ sẽ không hoạt động ở một số khu vực nhất định trong nhiệm vụ.</t>
         </is>
       </c>
@@ -11995,7 +11994,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Invite đồng đội tham gia trò chơi bài hai người trong sự kiện Lone Star. Hoàn thành một ván với một đồng đội để mở khóa đồng đội tiếp theo.</t>
+          <t>Mời đồng đội tham gia trò chơi bài hai người trong sự kiện Lone Star. Hoàn thành một ván với một đồng đội để mở khóa đồng đội tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12197,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Nhận thêm vật trang trí bằng cách tăng &lt;color=#ffd12f&gt;Cấp Độ Sôi Động&lt;/color&gt;, ghé thăm &lt;color=#ffd12f&gt;Shop Trang Trí&lt;/color&gt; và &lt;color=#ffd12f&gt;mời bạn bè&lt;/color&gt; đến chơi.</t>
+          <t>Nhận thêm vật trang trí bằng cách tăng &lt;color=#ffd12f&gt;Cấp Độ Sôi Động&lt;/color&gt;, ghé thăm &lt;color=#ffd12f&gt;Cửa Hàng Trang Trí&lt;/color&gt; và &lt;color=#ffd12f&gt;mời bạn bè&lt;/color&gt; đến chơi.</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12403,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Bạn đồng hành của cậu sẽ đánh giá từng ly dựa trên độ phù hợp của hương vị với đơn đặt và sở thích cá nhân của cô ấy. Để nhận thưởng, cậu phải đạt mức đánh giá "Satisfied" trở lên.
+          <t>Bạn đồng hành của cậu sẽ đánh giá từng ly dựa trên độ phù hợp của hương vị với đơn đặt và sở thích cá nhân của cô ấy. Để nhận thưởng, cậu phải đạt mức đánh giá "Hài lòng" trở lên.
 Đạt đánh giá "Rất hài lòng" để mở khóa đoạn hội thoại bonus.</t>
         </is>
       </c>
@@ -12472,7 +12471,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Trong mạch điện có hai dạng &lt;color=#ffd12f&gt;Mô-đun Shadow Kỹ Thuật Số&lt;/color&gt;:
+          <t>Trong mạch điện có hai dạng &lt;color=#ffd12f&gt;Mô-đun Bóng Tối Kỹ Thuật Số&lt;/color&gt;:
 - &lt;color=#ffd12f&gt;Mô-đun Hữu Hình&lt;/color&gt; có thể chặn Cube Blocker.
 - &lt;color=#ffd12f&gt;Mô-đun Vô Hình&lt;/color&gt; sẽ không chặn Cube Blocker.</t>
         </is>
@@ -12606,7 +12605,7 @@
       <c r="M175" t="inlineStr">
         <is>
           <t>Khi một Cube Blocker tiếp xúc với tia laser phát ra từ
-&lt;color=#ffd12f&gt;Laser Beam Mô-đun&lt;/color&gt;, nó sẽ bị nóng chảy tức thì, khiến Smartprint Cube phải khởi động lại.</t>
+&lt;color=#ffd12f&gt;Laser Beam Module&lt;/color&gt;, nó sẽ bị nóng chảy tức thì, khiến Smartprint Cube phải khởi động lại.</t>
         </is>
       </c>
     </row>
@@ -12739,8 +12738,8 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Cards Bất Định sẽ biến thành một thẻ ngẫu nhiên (trừ Cards Không Vương Miện) trong tay người chơi vào đầu mỗi lượt. Cards Bất Định sẽ không biến thành thẻ đã được sử dụng hoặc lặp lại biến hình trong cùng một lượt.
-Cards Bất Định có thể dùng để tạo cặp như các thẻ thông thường.</t>
+          <t>Thẻ Bất Định sẽ biến thành một thẻ ngẫu nhiên (trừ Thẻ Không Vương Miện) trong tay người chơi vào đầu mỗi lượt. Thẻ Bất Định sẽ không biến thành thẻ đã được sử dụng hoặc lặp lại biến hình trong cùng một lượt.
+Thẻ Bất Định có thể dùng để tạo cặp như các thẻ thông thường.</t>
         </is>
       </c>
     </row>
@@ -12806,8 +12805,8 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Các Exoswarm Containment Unit sẽ xuất hiện trên địa hình trong thử thách này. Khi Exoswarm di chuyển vào một Đơn vị Kiềm Chế, nó sẽ chuyển sang trạng thái Nghỉ và bỏ qua lượt tiếp theo.
-Nhỏ gọn và khó phát hiện, Exoswarm khó lòng nhận ra các Đơn vị Kiềm Chế. Do đó, nó sẽ không chủ động tránh Dodge chúng khi di chuyển.</t>
+          <t>Các Đơn vị Kiềm Chế Exoswarm sẽ xuất hiện trên địa hình trong thử thách này. Khi Exoswarm di chuyển vào một Đơn vị Kiềm Chế, nó sẽ chuyển sang trạng thái Nghỉ và bỏ qua lượt tiếp theo.
+Nhỏ gọn và khó phát hiện, Exoswarm khó lòng nhận ra các Đơn vị Kiềm Chế. Do đó, nó sẽ không chủ động tránh né chúng khi di chuyển.</t>
         </is>
       </c>
     </row>
@@ -12941,7 +12940,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Dùng Hỗ Trợ Mô-đun để phá băng và kích hoạt Lực Trường Vật Chất Hư Không, sau đó tiến vào bằng Điểm Móc.
+          <t>Dùng Mô-đun Hỗ Trợ để phá băng và kích hoạt Lực Trường Vật Chất Hư Không, sau đó tiến vào bằng Điểm Móc.
 Nếu tiến vào lực trường khi đang cưỡi mô-tô, năng lượng sẽ được nạp đầy, giúp bạn bật nhảy mạnh mẽ.
 Nếu tiến vào lực trường khi đi bộ, bạn sẽ tự động lướt và bay lên không trung.</t>
         </is>
@@ -13074,7 +13073,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Tại những khu vực có tín hiệu ổn định, cậu có thể tìm thấy Bộ Chuyển Đổi Mô-đun tại các căn cứ do Startorch Academy để lại. 
+          <t>Tại những khu vực có tín hiệu ổn định, cậu có thể tìm thấy Bộ Chuyển Đổi Mô-đun tại các căn cứ do Học viện Startorch để lại. 
 Những thiết bị này phát hiện các tần số bị nhiễu loạn bởi Voidmatter và biến chúng thành các Mô-đun Thích ứng.</t>
         </is>
       </c>
@@ -13208,8 +13207,8 @@
       <c r="M184" t="inlineStr">
         <is>
           <t>Một con đường hình thành từ các Mô-đun Thích ứng đã xuất hiện trên chiến trường.
-Bắn đạn vào &lt;color=#ffd12f&gt;Core Tần số Bất ổn&lt;/color&gt; để chuyển đổi trạng thái của các &lt;color=#ffd12f&gt;Mô-đun Thích ứng&lt;/color&gt; gần đó.
-Tuy nhiên, các &lt;color=#ffd12f&gt;Mô-đun Đông cứng&lt;/color&gt; (hiển thị màu xám) không thể bị thay đổi bởi &lt;color=#ffd12f&gt;Core Tần số Bất ổn&lt;/color&gt;.</t>
+Bắn đạn vào &lt;color=#ffd12f&gt;Lõi Tần số Bất ổn&lt;/color&gt; để chuyển đổi trạng thái của các &lt;color=#ffd12f&gt;Mô-đun Thích ứng&lt;/color&gt; gần đó.
+Tuy nhiên, các &lt;color=#ffd12f&gt;Mô-đun Đông cứng&lt;/color&gt; (hiển thị màu xám) không thể bị thay đổi bởi &lt;color=#ffd12f&gt;Lõi Tần số Bất ổn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13279,8 +13278,8 @@
         <is>
           <t>Soliskin có thể di chuyển dọc theo một đường liên tục của &lt;color=#ffd12f&gt;Mô-đun Thích Ứng&lt;/color&gt; được vật chất hóa.
 Chúng có thể nhảy lên một tầng và sẽ tự động nhảy xuống khi gặp khoảng trống.
-Khi một Soliskin xác định được rằng nó có thể đến được Giant Soliskin, nó sẽ tự di chuyển.
-Hãy điều chỉnh &lt;color=#ffd12f&gt;Mô-đun Thích Ứng&lt;/color&gt; trên chiến trường và dẫn dắt tất cả Soliskin an toàn đến Giant Soliskin.</t>
+Khi một Soliskin xác định được rằng nó có thể đến được Soliskin Khổng Lồ, nó sẽ tự di chuyển.
+Hãy điều chỉnh &lt;color=#ffd12f&gt;Mô-đun Thích Ứng&lt;/color&gt; trên chiến trường và dẫn dắt tất cả Soliskin an toàn đến Soliskin Khổng Lồ.</t>
         </is>
       </c>
     </row>
@@ -13346,8 +13345,8 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Trong thử thách này, Ice Wall sẽ xuất hiện trên địa hình như những chướng ngại vật tạm thời trên vùng đất băng giá. Sau một số lượt nhất định, chúng sẽ tan chảy và biến mất.
-Khi còn tồn tại, Ice Wall chặn đường di chuyển của Exoswarm. Chúng không thể bước vào ô có Ice Wall.</t>
+          <t>Trong thử thách này, Tường Băng sẽ xuất hiện trên địa hình như những chướng ngại vật tạm thời trên vùng đất băng giá. Sau một số lượt nhất định, chúng sẽ tan chảy và biến mất.
+Khi còn tồn tại, Tường Băng chặn đường di chuyển của Exoswarm. Chúng không thể bước vào ô có Tường Băng.</t>
         </is>
       </c>
     </row>
@@ -13412,7 +13411,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Sau khi tìm thấy Soliskin, cậu sẽ nhận được Soliseed của Essehalo từ chúng, có thể mang đến &lt;color=#ffd12f&gt;Giant Soliskin tại Monument of Returning Soliseeds&lt;/color&gt; để nhận thưởng.</t>
+          <t>Sau khi tìm thấy Soliskin, cậu sẽ nhận được Soliseed của Essehalo từ chúng, có thể mang đến &lt;color=#ffd12f&gt;Giant Soliskin tại Đài Tưởng Niệm Soliseed Trở Về&lt;/color&gt; để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13476,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Bạn có thể điều khiển xe thám hiểm ở cả góc nhìn thứ nhất và thứ ba. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} Switch đổi góc nhìn để thay đổi cách quan sát.</t>
+          <t>Bạn có thể điều khiển xe thám hiểm ở cả góc nhìn thứ nhất và thứ ba. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} Chuyển đổi góc nhìn để thay đổi cách quan sát.</t>
         </is>
       </c>
     </row>
@@ -13613,9 +13612,9 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Repair các Hiệp Sĩ để nâng GPA Level và kích hoạt buff mốc thưởng.
-Mở rương và thực hiện các hành động chiến đấu sẽ tạm thời tăng GPA Level Tạm Thời, kích hoạt buff.
-GPA Level Tạm Thời sẽ bị xóa khi bạn rời khỏi khu vực hoặc kết thúc trạng thái chiến đấu.</t>
+          <t>Sửa chữa các Hiệp Sĩ để nâng Cấp GPA và kích hoạt buff mốc thưởng.
+Mở rương và thực hiện các hành động chiến đấu sẽ tạm thời tăng Cấp GPA Tạm Thời, kích hoạt buff.
+Cấp GPA Tạm Thời sẽ bị xóa khi bạn rời khỏi khu vực hoặc kết thúc trạng thái chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13816,7 @@
       <c r="M193" t="inlineStr">
         <is>
           <t>Kéo các khối để lấp đầy khoảng trống. Hoàn thành một hàng hoặc cột đầy đủ để xóa khối.
-Clear các khối chứa Huy Hiệu để thu thập chúng.
+Xóa các khối chứa Huy Hiệu để thu thập chúng.
 Thu thập đủ số Huy Hiệu yêu cầu để vượt qua màn chơi.</t>
         </is>
       </c>
@@ -13950,7 +13949,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Để tăng điểm, hãy {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút tương ứng với màu của Nốt khi tàu vũ trụ đi qua Nốt (Nốt Xanh và Xanh Lá).</t>
+          <t>Để tăng điểm, hãy {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} nút tương ứng với màu của Nốt khi tàu vũ trụ đi qua Nốt (Nốt Xanh và Xanh Lá).</t>
         </is>
       </c>
     </row>
@@ -14015,7 +14014,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Cậu cũng có thể kiếm điểm bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Điều Hướng tương ứng khi tàu vũ trụ đi qua Nốt Điều Hướng. Làm vậy sẽ khiến tàu nghiêng trái hoặc phải trong Chế Độ Tuần Tiễu Tiêu Chuẩn.</t>
+          <t>Cậu cũng có thể kiếm điểm bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} nút Điều Hướng tương ứng khi tàu vũ trụ đi qua Nốt Điều Hướng. Làm vậy sẽ khiến tàu nghiêng trái hoặc phải trong Chế Độ Tuần Tiễu Tiêu Chuẩn.</t>
         </is>
       </c>
     </row>
@@ -14145,7 +14144,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Để tăng điểm, hãy {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút tương ứng với màu của Nốt khi tàu vũ trụ đi qua Nốt (Nốt Xanh và Xanh Lá).</t>
+          <t>Để tăng điểm, hãy {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} nút tương ứng với màu của Nốt khi tàu vũ trụ đi qua Nốt (Nốt Xanh và Xanh Lá).</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14209,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Cậu cũng có thể kiếm điểm bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Điều Hướng tương ứng khi tàu vũ trụ đi qua Nốt Điều Hướng. Làm vậy sẽ khiến tàu nghiêng trái hoặc phải trong Chế Độ Tuần Tiễu Tiêu Chuẩn.</t>
+          <t>Cậu cũng có thể kiếm điểm bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} nút Điều Hướng tương ứng khi tàu vũ trụ đi qua Nốt Điều Hướng. Làm vậy sẽ khiến tàu nghiêng trái hoặc phải trong Chế Độ Tuần Tiễu Tiêu Chuẩn.</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14339,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tích điểm sẽ nạp đầy Thanh Speed với tốc độ khác nhau tùy thuộc vào Đánh Giá hiện tại. Khi đầy, tàu vũ trụ sẽ tự động chuyển sang Full Speed Mode, di chuyển với vận tốc cực đại và tự động xóa mọi Nốt Nhạc trong thời gian giới hạn.</t>
+          <t>Tích điểm sẽ nạp đầy Thanh Tốc Độ với tốc độ khác nhau tùy thuộc vào Đánh Giá hiện tại. Khi đầy, tàu vũ trụ sẽ tự động chuyển sang Chế Độ Tốc Độ Tối Đa, di chuyển với vận tốc cực đại và tự động xóa mọi Nốt Nhạc trong thời gian giới hạn.</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14404,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Phi thuyền có nhiều chế độ bay khác nhau. Khi chuyển sang Triangle Mode, bạn không cần điều khiển và đường bay sẽ tự động xoay khi phi thuyền gặp Nốt Chuyển Hướng.</t>
+          <t>Phi thuyền có nhiều chế độ bay khác nhau. Khi chuyển sang Chế Độ Tam Giác, bạn không cần điều khiển và đường bay sẽ tự động xoay khi phi thuyền gặp Nốt Chuyển Hướng.</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14606,7 @@
       <c r="M205" t="inlineStr">
         <is>
           <t>Kéo các khối để lấp đầy khoảng trống. Hoàn thành một hàng hoặc cột đầy đủ để xóa khối.
-Clear các khối chứa Huy Hiệu để thu thập chúng.
+Xóa các khối chứa Huy Hiệu để thu thập chúng.
 Thu thập đủ số Huy Hiệu yêu cầu để vượt qua màn chơi.</t>
         </is>
       </c>
@@ -14740,7 +14739,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Những chiếc bàn phím bị vứt lung tung ở Dark Side, chia thành ba quãng tám. Resonators có thể kích hoạt Nốt nhạc hiển thị trong mỗi quãng bằng cách dẫm lên hai phím trong quãng đó. Kích hoạt ba Nốt sẽ tạo ra Ghi chú Windfield.</t>
+          <t>Những chiếc bàn phím bị vứt lung tung ở Dark Side, chia thành ba quãng tám. Resonator có thể kích hoạt Nốt nhạc hiển thị trong mỗi quãng bằng cách dẫm lên hai phím trong quãng đó. Kích hoạt ba Nốt sẽ tạo ra Note Windfield.</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14804,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Drum Set được cất giấu ngẫu nhiên ở Dark Side. Bạn có thể dẫm lên mặt trống, và khi di chuyển qua, rung động sẽ đẩy bạn lên cao đồng thời phát ra âm thanh nhịp nhàng.</t>
+          <t>Bộ trống được cất giấu ngẫu nhiên ở Dark Side. Bạn có thể dẫm lên mặt trống, và khi di chuyển qua, rung động sẽ đẩy bạn lên cao đồng thời phát ra âm thanh nhịp nhàng.</t>
         </is>
       </c>
     </row>
@@ -14940,12 +14939,12 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Gửi những Rover đã đồng hành cùng chúng ta trên chặng đường dài, ta cảm ơn các ngươi đã có mặt ở đây.
+          <t>Gửi những Vận Mệnh Giả đã đồng hành cùng chúng ta trên chặng đường dài, ta cảm ơn các ngươi đã có mặt ở đây.
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 8.
 [Quy tắc sự kiện]
 Đăng nhập trong thời gian diễn ra sự kiện để nhận thưởng.
-Rewards sẽ KHÔNG được gửi lại qua thư trong game sau khi sự kiện kết thúc. Hãy chú ý thời gian sự kiện và nhận thưởng trước đó.</t>
+Phần thưởng sẽ KHÔNG được gửi lại qua thư trong game sau khi sự kiện kết thúc. Hãy chú ý thời gian sự kiện và nhận thưởng trước đó.</t>
         </is>
       </c>
     </row>
@@ -15023,8 +15022,8 @@
 Giờ đây, dưới ánh mắt dõi theo của nó, một sinh viên vừa tốt nghiệp sắp bắt đầu hành trình vượt qua Dimmr Plains...
 Điều Kiện Mở Khóa
 Hoàn thành Chương III Màn V Nhiệm Vụ Chính "Starlights from Yesterdays" để mở khóa.
-Event Rules
-- Explore các khu vực theo manh mối để thu thập những Chrono Traces rải rác.
+Quy Tắc Sự Kiện
+- Khám phá các khu vực theo manh mối để thu thập những Chrono Traces rải rác.
 - Thu thập đủ tất cả Chrono Traces để nhận Astrites và các phần thưởng khác.
 - Trong tương lai, sẽ có thêm nhiều Chrono Traces để thu thập ở các khu vực khác.</t>
         </is>
@@ -15101,10 +15100,10 @@
           <t>Giới Thiệu
 Dưới bóng Lahai-Roi, Rừng Solvein Heartwood vươn cao như đang nâng đỡ những kỷ nguyên dài đằng đẵng chìm trong bóng tối. Vô số hạt bụi lơ lửng nơi đây như những dấu vết của quá khứ chưa tắt hẳn, cổ xưa và tĩnh lặng, chờ đợi một câu trả lời. Hãy đi theo ánh sáng xuống dưới, giữa những lớp bụi dày, lắng nghe những ngày tháng xa xưa bắt đầu thức tỉnh.
 [Điều kiện tham gia]
-Hoàn thành ảo ảnh của Đại Kiến Trúc Sư trong Nhiệm Vụ Chính "Wishes in the Bell" để mở khóa.
+Hoàn thành ảo ảnh của Đại Kiến Trúc Sư trong Nhiệm Vụ Chính "Điều Ước Trong Chuông" để mở khóa.
 [Quy tắc sự kiện]
-- Event được chia thành bốn giai đoạn, mỗi giai đoạn sẽ mở khóa khi bạn tiến triển trong Nhiệm Vụ Chính. Hoàn thành các nhiệm vụ sự kiện để nhận phần thưởng hậu hĩnh.
-- Nếu có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.
+- Sự kiện được chia thành bốn giai đoạn, mỗi giai đoạn sẽ mở khóa khi bạn tiến triển trong Nhiệm Vụ Chính. Hoàn thành các nhiệm vụ sự kiện để nhận phần thưởng hậu hĩnh.
+- Nếu có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.
 - Lưu ý rằng một số nội dung của sự kiện sẽ không khả dụng trong Chế Độ Đồng Đội, và Theo Dõi Nhiệm Vụ sẽ không hoạt động ở một số khu vực nhất định trong nhiệm vụ.</t>
         </is>
       </c>
@@ -15171,7 +15170,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ sẽ Dodgem cậu thẳng vào thử thách Boss!
+          <t>Hiệp Sĩ sẽ ném cậu thẳng vào thử thách Boss!
 Sửa chữa các Hiệp Sĩ sẽ làm Boss suy yếu đáng kể và tăng cường sức chiến đấu của cậu. Chúng tôi khuyên cậu nên sửa chữa tất cả các Hiệp Sĩ trước.</t>
         </is>
       </c>
@@ -15241,11 +15240,11 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>["Trang phục Accessory"]
-Gắn Phụ Kiện sẽ thay đổi ngoại hình của các bộ phận cụ thể trên Resonators.
-Một Resonators không thể trang bị nhiều Phụ Kiện cùng vị trí.
-Resonators sở hữu nhiều Trang phục có thể thiết lập Phụ Kiện khác nhau cho từng bộ. Mỗi Trang phục chỉ lưu được một thiết lập Phụ Kiện.
-Một số Phụ Kiện độc đáo chỉ có thể trang bị cho Trang phục được chỉ định của Resonators.</t>
+          <t>["Phụ Kiện Trang Phục"]
+Gắn Phụ Kiện sẽ thay đổi ngoại hình của các bộ phận cụ thể trên Resonator.
+Một Resonator không thể trang bị nhiều Phụ Kiện cùng vị trí.
+Resonator sở hữu nhiều Trang Phục có thể thiết lập Phụ Kiện khác nhau cho từng bộ. Mỗi Trang Phục chỉ lưu được một thiết lập Phụ Kiện.
+Một số Phụ Kiện độc đáo chỉ có thể trang bị cho Trang Phục được chỉ định của Resonator.</t>
         </is>
       </c>
     </row>
@@ -15318,9 +15317,9 @@
           <t>Khối Hư Không xuất hiện từ vùng chờ phía trên, di chuyển theo bạn và rơi xuống khi hết giờ. Tránh các khối rơi để không bị trúng.
 - Ngoài ra, điều khiển khối bằng cách di chuyển nhân vật để chúng rơi đúng vị trí mong muốn và ngăn chồng chất vượt quá vùng chờ.
 - Dùng nút xoay để điều chỉnh hướng khi đồng hồ đếm ngược đang chạy. Khi khối đã ở đúng vị trí và hướng, nhấn nút thả để kết thúc đếm ngược và khối sẽ rơi ngay lập tức.
-- Thử thách gồm hai chế độ: Thường Mode và Infinite Mode.
-- Thường Mode: Chiến thắng bằng cách hoàn thành đếm ngược.
-- Infinite Mode: Tích lũy đủ điểm để giành chiến thắng. Points có được khi xóa các hàng khối chồng chất hoặc thả khối thủ công.</t>
+- Thử thách gồm hai chế độ: Chế Độ Thường và Chế Độ Vô Tận.
+- Chế Độ Thường: Chiến thắng bằng cách hoàn thành đếm ngược.
+- Chế Độ Vô Tận: Tích lũy đủ điểm để giành chiến thắng. Điểm có được khi xóa các hàng khối chồng chất hoặc thả khối thủ công.</t>
         </is>
       </c>
     </row>
@@ -15386,7 +15385,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Bốn mẫu thực vật cổ quý hiếm mang tên Cổ Thụ Hư Không&lt;/color&gt; đang chờ được hồi sinh. Nhưng Void Storm quét qua Dimmr Plains quanh năm, khiến cây cối vẫn còi cọc vì ô nhiễm Vật Chất Hư Không và các dị thường khác.
+          <t>&lt;color=#ffd12f&gt;Bốn mẫu thực vật cổ quý hiếm mang tên Cổ Thụ Hư Không&lt;/color&gt; đang chờ được hồi sinh. Nhưng Bão Hư Không quét qua Đồng Bằng Dimmr quanh năm, khiến cây cối vẫn còi cọc vì ô nhiễm Vật Chất Hư Không và các dị thường khác.
 Trước tiên, ngươi phải hợp tác với các thành viên Đội Khảo Sát và Soliskin để dọn sạch &lt;color=#ffd12f&gt;ô nhiễm Vật Chất Hư Không và các dị thường&lt;/color&gt; xung quanh Cổ Thụ Hư Không.</t>
         </is>
       </c>
@@ -15455,8 +15454,8 @@
       <c r="M217" t="inlineStr">
         <is>
           <t>Bạn có thể thu thập số lượng lớn vật phẩm hồi phục từ &lt;color=#ffd12f&gt;nhiệm vụ và thử thách được đề xuất trong các khu vực tương ứng&lt;/color&gt;.
-Ngoài các nhiệm vụ đề xuất, bạn cũng có thể nhận được chúng từ &lt;color=#ffd12f&gt;nhiệm vụ, thử thách và Supply Chest&lt;/color&gt;.
-Bạn cũng có thể kiểm tra hoạt động nào rơi vật phẩm này trong trang &lt;color=#ffd12f&gt;Exploration Progress&lt;/color&gt;.</t>
+Ngoài các nhiệm vụ đề xuất, bạn cũng có thể nhận được chúng từ &lt;color=#ffd12f&gt;nhiệm vụ, thử thách và Rương Cung Cấp&lt;/color&gt;.
+Bạn cũng có thể kiểm tra hoạt động nào rơi vật phẩm này trong trang &lt;color=#ffd12f&gt;Tiến Độ Thám Hiểm&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15522,7 +15521,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Sau khi Restoration hoàn tất, các Cây Cổ Thụ Hư Không sẽ tiếp tục sinh trưởng, dùng năng lượng của chính mình để &lt;color=#ffd12f&gt;tạo thành những cây cầu nối liền các khu vực khảo sát lân cận&lt;/color&gt;.
+          <t>Sau khi Phục Hồi hoàn tất, các Cây Cổ Thụ Hư Không sẽ tiếp tục sinh trưởng, dùng năng lượng của chính mình để &lt;color=#ffd12f&gt;tạo thành những cây cầu nối liền các khu vực khảo sát lân cận&lt;/color&gt;.
 Nó cũng sẽ tạo ra &lt;color=#ffd12f&gt;cơ chế hỗ trợ&lt;/color&gt; trong các khu vực khảo sát tương ứng.</t>
         </is>
       </c>
@@ -15589,7 +15588,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Mỗi lần hoàn thành Restoration sẽ nhận được mẫu nghiên cứu quý hiếm: Quả Prism.
+          <t>Mỗi lần hoàn thành Phục Hồi sẽ nhận được mẫu nghiên cứu quý hiếm: Quả Lăng Kính.
 Hãy giao nó cho &lt;color=#ffd12f&gt;I.R.I.S. tại Trại Cơ Bản&lt;/color&gt; để phân tích, thúc đẩy khảo sát và &lt;color=#ffd12f&gt;mở rộng Trại Cơ Bản&lt;/color&gt;.</t>
         </is>
       </c>
@@ -15655,7 +15654,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Khi tất cả các Phục Hồi hoàn tất, mọi Quả Cầu Prism được chuyển giao, và &lt;color=#ffd12f&gt;Trại Cơ Bản được nâng cấp lên Cấp 5&lt;/color&gt;, năng lượng của Solvein Heartwood sẽ tràn đầy hơn, và hệ sinh thái Dimmr Plains sẽ hồi sinh một lần nữa.</t>
+          <t>Khi tất cả các Phục Hồi hoàn tất, mọi Quả Cầu Lăng Kính được chuyển giao, và &lt;color=#ffd12f&gt;Trại Cơ Bản được nâng cấp lên Cấp 5&lt;/color&gt;, năng lượng của Solvein Heartwood sẽ tràn đầy hơn, và hệ sinh thái Dimmr Plains sẽ hồi sinh một lần nữa.</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15784,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Các Bi Đánh tích lũy Points Bùng Nổ theo thời gian. Khi Thanh Bùng Nổ đầy, chúng sẽ bước vào trạng thái Bùng Nổ, tăng cường nhiều hiệu ứng cho tất cả Bi Đánh và tạo ra 4 cơ chế Bounce Hướng trong khu vực.</t>
+          <t>Các Bi Đánh tích lũy Điểm Bùng Nổ theo thời gian. Khi Thanh Bùng Nổ đầy, chúng sẽ bước vào trạng thái Bùng Nổ, tăng cường nhiều hiệu ứng cho tất cả Bi Đánh và tạo ra 4 cơ chế Nảy Hướng trong khu vực.</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15914,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Cơ chế Black Hole bắt đầu xuất hiện trong thử thách. Khi một quả Pinball đi vào Black Hole, nó sẽ được dịch chuyển ra khỏi Black Hole tương ứng khác, giữ nguyên tốc độ và hướng ban đầu.</t>
+          <t>Cơ chế Hố Đen bắt đầu xuất hiện trong thử thách. Khi một quả Pinball đi vào Hố Đen, nó sẽ được dịch chuyển ra khỏi Hố Đen tương ứng khác, giữ nguyên tốc độ và hướng ban đầu.</t>
         </is>
       </c>
     </row>
@@ -15980,7 +15979,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>S-Class Tactical ROM là ROM đặc biệt chỉ dành riêng cho Pinball, chỉ có thể trang bị cho các Persona Pinball tương ứng. Trang bị ROM này sẽ mang lại những bonus mạnh mẽ cho Pinball đó.</t>
+          <t>ROM Chiến Thuật Hạng S là ROM đặc biệt chỉ dành riêng cho Pinball, chỉ có thể trang bị cho các Persona Pinball tương ứng. Trang bị ROM này sẽ mang lại những bonus mạnh mẽ cho Pinball đó.</t>
         </is>
       </c>
     </row>
@@ -16113,7 +16112,7 @@
       <c r="M227" t="inlineStr">
         <is>
           <t>Mở khóa Mô-đun Mở Rộng sẽ kích hoạt Charged Leap.
-Sau khi mở khóa, giữ nút Bật Nhảy để sử dụng Charged Leap của xe máy, giúp tăng độ cao. Sử dụng Charged Leap từ mặt đất cũng sẽ tự động chuyển sang trạng thái lướt.
+Sau khi mở khóa, giữ nút Nhảy Bật để sử dụng Charged Leap của xe máy, giúp tăng độ cao. Sử dụng Charged Leap từ mặt đất cũng sẽ tự động chuyển sang trạng thái lướt.
 Charged Leap có tối đa 3 lần tích năng, sẽ hồi phục dần theo thời gian khi xe máy chạm đất. Không thể hồi phục khi đang ở trên không.</t>
         </is>
       </c>
@@ -16179,7 +16178,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Trên Dimmr Plains có rất nhiều hang động bí ẩn. Tương tác với Light Builder ở lối vào hang, sau đó xoay các bộ phận Exostrider bên trong cho đến khi hình chiếu khớp với hoa văn trên tường để mở hang.</t>
+          <t>Trên Đồng Bằng Dimmr có rất nhiều hang động bí ẩn. Tương tác với Light Builder ở lối vào hang, sau đó xoay các bộ phận Exostrider bên trong cho đến khi hình chiếu khớp với hoa văn trên tường để mở hang.</t>
         </is>
       </c>
     </row>
@@ -16245,8 +16244,8 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Lumescribe Component có thể ức chế Vật Chất Hư Không và thanh tẩy Quái Vật Hư Không. Những xúc tu của Quái Vật Hư Không tiếp xúc với ánh sáng sẽ co lại, và cơ thể chính của nó sẽ teo nhỏ rồi phát nổ sau khi tiếp xúc đủ lâu.
-Đứng trong phạm vi của Lumescribe Component sẽ bảo vệ bạn khỏi Quái Vật Hư Không. Các xúc tu của Quái Vật Hư Không trong khu vực chỉ biến mất sau khi tất cả Quái Vật Hư Không trong vùng đã bị tiêu diệt.</t>
+          <t>Bộ phận Ghi Âm Lumen có thể ức chế Vật Chất Hư Không và thanh tẩy Quái Vật Hư Không. Những xúc tu của Quái Vật Hư Không tiếp xúc với ánh sáng sẽ co lại, và cơ thể chính của nó sẽ teo nhỏ rồi phát nổ sau khi tiếp xúc đủ lâu.
+Đứng trong phạm vi của Bộ phận Ghi Âm Lumen sẽ bảo vệ bạn khỏi Quái Vật Hư Không. Các xúc tu của Quái Vật Hư Không trong khu vực chỉ biến mất sau khi tất cả Quái Vật Hư Không trong vùng đã bị tiêu diệt.</t>
         </is>
       </c>
     </row>
@@ -16312,7 +16311,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Attack hoặc dùng Hoverdroid bắn vào Nhánh Trái Tim Solvein để kích hoạt Bộ phận Lumescribe. Nó cũng có thể được kích hoạt bằng ánh sáng từ một Bộ phận Lumescribe khác.
+          <t>Tấn công hoặc dùng Hoverdroid bắn vào Nhánh Trái Tim Solvein để kích hoạt Bộ phận Lumescribe. Nó cũng có thể được kích hoạt bằng ánh sáng từ một Bộ phận Lumescribe khác.
 Tương tác với Bộ phận Lumescribe để di chuyển nó giữa các đường ray.</t>
         </is>
       </c>
@@ -16513,7 +16512,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Soliskin Platform hình thành khi năng lượng Soliskin được giải phóng thông qua một thiết bị khoa học từng bị Voidmatter ô nhiễm.
+          <t>Bệ Đỡ Soliskin hình thành khi năng lượng Soliskin được giải phóng thông qua một thiết bị khoa học từng bị Voidmatter ô nhiễm.
 Bệ đỡ này cấu thành từ năng lượng Soliskin bất ổn. Khi di chuyển trên đó, bệ đỡ sẽ nghiêng về phía vị trí của cậu.</t>
         </is>
       </c>
@@ -16650,7 +16649,7 @@
         <is>
           <t>Một nhánh cây Solvein Heartwood. Trên đó vẫn còn dấu vết của những tạo tác Exostrider và có thể lưu trữ một lượng nhỏ năng lượng Soliskin.
 Hãy đập vào nó để đánh thức năng lượng Soliskin bên trong, rồi dẫn năng lượng đó đến và kích hoạt lại các cỗ máy bị bỏ hoang gần nhất.
-Ở Dimmr Plains có rất nhiều loại máy móc bị bỏ hoang như vậy: Lumescribe Emitter, Lumescribe Component và Soliskin Platform.</t>
+Ở Đồng Bằng Dimmr có rất nhiều loại máy móc bị bỏ hoang như vậy: Lumescribe Emitter, Lumescribe Component và Soliskin Platform.</t>
         </is>
       </c>
     </row>
@@ -16716,7 +16715,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Trước khi khối gạch rơi xuống, nó sẽ di chuyển ngang trên đầu cậu trong một khoảng thời gian giới hạn. Cậu có thể xoay khối gạch 90 độ bằng nút Rotate.
+          <t>Trước khi khối gạch rơi xuống, nó sẽ di chuyển ngang trên đầu cậu trong một khoảng thời gian giới hạn. Cậu có thể xoay khối gạch 90 độ bằng nút Xoay.
 Khi đã ở đúng vị trí, cậu có thể thả khối gạch xuống thủ công.</t>
         </is>
       </c>
@@ -16782,7 +16781,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Trong Voidmatter Blocks: Infinite, con phải Dodge các khối rơi đồng thời điều chỉnh vị trí và hướng để kiếm điểm. Đạt các mốc nhất định để nhận thưởng.</t>
+          <t>Trong Voidmatter Blocks: Infinite, con phải né các khối rơi đồng thời điều chỉnh vị trí và hướng để kiếm điểm. Đạt các mốc nhất định để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16847,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Trước khi khối gạch rơi xuống, nó sẽ di chuyển ngang trên đầu cậu trong một khoảng thời gian giới hạn. Cậu có thể xoay khối gạch 90 độ bằng nút Rotate.
+          <t>Trước khi khối gạch rơi xuống, nó sẽ di chuyển ngang trên đầu cậu trong một khoảng thời gian giới hạn. Cậu có thể xoay khối gạch 90 độ bằng nút Xoay.
 Khi đã ở đúng vị trí, cậu có thể thả khối gạch xuống thủ công. Thả thủ công sẽ giúp cậu nhận được điểm thưởng.</t>
         </is>
       </c>
@@ -17046,7 +17045,7 @@
       <c r="M241" t="inlineStr">
         <is>
           <t>Tiến lên trên đường đua đã chọn, vượt qua mọi chướng ngại vật và kiếm đủ điểm để hoàn thành thử thách.
-Sử dụng Drift để trượt dưới rào chắn hoặc Bounce Nhảy để nhảy qua chướng ngại. Cậu cũng có thể dùng Drift để điều khiển xe máy lượn qua một số vị trí nhằm kiếm thêm điểm.</t>
+Sử dụng Drift để trượt dưới rào chắn hoặc Bounce Jump để nhảy qua chướng ngại. Cậu cũng có thể dùng Drift để điều khiển xe máy lượn qua một số vị trí nhằm kiếm thêm điểm.</t>
         </is>
       </c>
     </row>
@@ -17177,7 +17176,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Rover có thể &lt;color=#ffd12f&gt;hỗ trợ&lt;/color&gt; một &lt;color=#ffd12f&gt;Cube&lt;/color&gt; bằng cách &lt;color=#ffd12f&gt;dự đoán&lt;/color&gt; rằng nó sẽ là &lt;color=#ffd12f&gt;Quân Chiến Thắng&lt;/color&gt;.
+          <t>Vận Mệnh Giả có thể &lt;color=#ffd12f&gt;hỗ trợ&lt;/color&gt; một &lt;color=#ffd12f&gt;Khối Lập Phương&lt;/color&gt; bằng cách &lt;color=#ffd12f&gt;dự đoán&lt;/color&gt; rằng nó sẽ là &lt;color=#ffd12f&gt;Quân Chiến Thắng&lt;/color&gt;.
 Mỗi trận đấu bắt đầu lúc 21:00. Thời gian hỗ trợ mở từ khi trận trước kết thúc cho đến 30 phút trước khi trận tiếp theo bắt đầu (20:30).</t>
         </is>
       </c>
@@ -17245,8 +17244,8 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Trong mỗi trận đấu, Cube &lt;color=#ffd12f&gt;về nhất&lt;/color&gt; sẽ chiến thắng. Những Rover &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; Cube thắng sẽ &lt;color=#ffd12f&gt;nhận&lt;/color&gt; Phần Thưởng Popularity.
-Phần Thưởng Popularity được xác định bởi Popularity đã tiêu hao khi ủng hộ và &lt;color=#ffd12f&gt;Tỷ Lệ Thua Cược&lt;/color&gt; của Cube. Tỷ lệ này &lt;color=#ffd12f&gt;cập nhật vào các thời điểm cố định&lt;/color&gt; dựa trên lượng ủng hộ mà Cube nhận được.
+          <t>Trong mỗi trận đấu, Cube &lt;color=#ffd12f&gt;về nhất&lt;/color&gt; sẽ chiến thắng. Những Rover &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; Cube thắng sẽ &lt;color=#ffd12f&gt;nhận&lt;/color&gt; Phần Thưởng Độ Phổ Biến.
+Phần Thưởng Độ Phổ Biến được xác định bởi Độ Phổ Biến đã tiêu hao khi ủng hộ và &lt;color=#ffd12f&gt;Tỷ Lệ Thua Cược&lt;/color&gt; của Cube. Tỷ lệ này &lt;color=#ffd12f&gt;cập nhật vào các thời điểm cố định&lt;/color&gt; dựa trên lượng ủng hộ mà Cube nhận được.
 Diễn biến cuộc đua khác nhau tùy theo giai đoạn, và thứ hạng trận đấu sẽ quyết định liệu Cube có &lt;color=#ffd12f&gt;tiến vào&lt;/color&gt; trận tiếp theo hay không.</t>
         </is>
       </c>
@@ -17312,7 +17311,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Khi các Cube xếp chồng lên nhau, nếu khối dưới cùng di chuyển trước, nó sẽ kéo theo tất cả các khối xếp phía trên. Trong số các khối xếp chồng, khối càng cao thì cấp bậc càng lớn.</t>
+          <t>Khi các Khối Lập Phương xếp chồng lên nhau, nếu khối dưới cùng di chuyển trước, nó sẽ kéo theo tất cả các khối xếp phía trên. Trong số các khối xếp chồng, khối càng cao thì cấp bậc càng lớn.</t>
         </is>
       </c>
     </row>
@@ -17380,9 +17379,9 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Trong Giai Đoạn Hỗ Trợ, người chơi có thể &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; Cube yêu thích bằng cách &lt;color=#ffd12f&gt;dự đoán&lt;/color&gt; rằng nó sẽ là &lt;color=#ffd12f&gt;Quán Quân Trận Đấu&lt;/color&gt;.
-&lt;color=#ffd12f&gt;Ủng hộ&lt;/color&gt; một Cube sẽ tiêu tốn Điểm Phổ Biến của người chơi. &lt;color=#ffd12f&gt;Điểm Phổ Biến&lt;/color&gt; có thể kiếm được bằng cách hoàn thành &lt;color=#ffd12f&gt;Daily Tasks&lt;/color&gt; của sự kiện.
-Nếu Cube mà bạn ủng hộ chiến thắng, bạn sẽ &lt;color=#ffd12f&gt;nhận được Phần Thưởng Điểm Phổ Biến&lt;/color&gt; dựa trên [Điểm Phổ Biến Đã Dành] x [Tỷ Lệ Thua Lợi].
+          <t>Trong Giai Đoạn Hỗ Trợ, người chơi có thể &lt;color=#ffd12f&gt;ủng hộ&lt;/color&gt; Khối Lập Phương yêu thích bằng cách &lt;color=#ffd12f&gt;dự đoán&lt;/color&gt; rằng nó sẽ là &lt;color=#ffd12f&gt;Quán Quân Trận Đấu&lt;/color&gt;.
+&lt;color=#ffd12f&gt;Ủng hộ&lt;/color&gt; một Khối Lập Phương sẽ tiêu tốn Điểm Phổ Biến của người chơi. &lt;color=#ffd12f&gt;Điểm Phổ Biến&lt;/color&gt; có thể kiếm được bằng cách hoàn thành &lt;color=#ffd12f&gt;Nhiệm Vụ Hằng Ngày&lt;/color&gt; của sự kiện.
+Nếu Khối Lập Phương mà bạn ủng hộ chiến thắng, bạn sẽ &lt;color=#ffd12f&gt;nhận được Phần Thưởng Điểm Phổ Biến&lt;/color&gt; dựa trên [Điểm Phổ Biến Đã Dành] x [Tỷ Lệ Thua Lợi].
 Nếu dự đoán của bạn sai, 80% Điểm Phổ Biến đã dùng để ủng hộ sẽ được hoàn lại.</t>
         </is>
       </c>
@@ -17451,8 +17450,8 @@
       <c r="M247" t="inlineStr">
         <is>
           <t>Thời gian ủng hộ mở từ khi trận đấu trước kết thúc cho đến 30 phút trước khi trận đấu tiếp theo bắt đầu (20:30).
-Dựa trên lượng ủng hộ mà Cube nhận được và vị trí xuất phát của nó, &lt;color=#ffd12f&gt;Tỷ lệ Thua Lợi&lt;/color&gt; của Khối sẽ được &lt;color=#ffd12f&gt;cập nhật&lt;/color&gt; hàng ngày vào 4:00, 12:00 và 18:00.
-Rewards Popularity khi dự đoán đúng đội thắng sẽ phụ thuộc vào Tỷ lệ Thua Lợi của Khối. Hãy chú ý theo dõi những thay đổi về tỷ lệ này nhé!</t>
+Dựa trên lượng ủng hộ mà Khối Lập Phương nhận được và vị trí xuất phát của nó, &lt;color=#ffd12f&gt;Tỷ lệ Thua Lợi&lt;/color&gt; của Khối sẽ được &lt;color=#ffd12f&gt;cập nhật&lt;/color&gt; hàng ngày vào 4:00, 12:00 và 18:00.
+Phần thưởng Độ Phổ Biến khi dự đoán đúng đội thắng sẽ phụ thuộc vào Tỷ lệ Thua Lợi của Khối. Hãy chú ý theo dõi những thay đổi về tỷ lệ này nhé!</t>
         </is>
       </c>
     </row>
@@ -17519,8 +17518,8 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Page Race Hiện Thể hiện tất cả các giai đoạn của cuộc đua và ai sẽ tiến vào vòng tiếp theo.
-Cuộc đua gồm 3 giai đoạn: Vòng Sơ loại, Vòng Loại trực tiếp và Chung kết. Mỗi giai đoạn có lịch thi đấu khác nhau, bạn có thể xem chi tiết trên Page Race Hiện.
+          <t>Trang Đua Hiện Thể hiện tất cả các giai đoạn của cuộc đua và ai sẽ tiến vào vòng tiếp theo.
+Cuộc đua gồm 3 giai đoạn: Vòng Sơ loại, Vòng Loại trực tiếp và Chung kết. Mỗi giai đoạn có lịch thi đấu khác nhau, bạn có thể xem chi tiết trên Trang Đua Hiện.
 Trong Giai đoạn Hỗ trợ, các Đấu thủ và trận đấu hiện tại sẽ được làm nổi bật. Sau khi mỗi trận kết thúc, trang sẽ cập nhật để hiển thị Đấu thủ nào tiến vào vòng tiếp theo.</t>
         </is>
       </c>
@@ -17587,8 +17586,8 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Một số trận đấu có vòng 1 và vòng 2. Thứ hạng của Cube ở vòng 1 sẽ quyết định vị trí xuất phát ở vòng 2.
-Số suất đi tiếp sẽ thay đổi tùy trận. Các Cube không đi tiếp sẽ kết thúc hành trình sau khi thi đấu trong một trận Trận Trình Diễn.</t>
+          <t>Một số trận đấu có vòng 1 và vòng 2. Thứ hạng của Khối Lập Phương ở vòng 1 sẽ quyết định vị trí xuất phát ở vòng 2.
+Số suất đi tiếp sẽ thay đổi tùy trận. Các Khối Lập Phương không đi tiếp sẽ kết thúc hành trình sau khi thi đấu trong một trận Trận Trình Diễn.</t>
         </is>
       </c>
     </row>
@@ -17653,7 +17652,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Trong Vực Ảo Mộng, ngươi có thể thu thập nhiều loại tăng cường sức mạnh, bao gồm Ảo Ảnh, Ẩn Dụ và Resonator Enhancements. Hãy sử dụng những sức mạnh này để thách thức những tầng sâu hơn của giấc mơ.</t>
+          <t>Trong Vực Ảo Mộng, ngươi có thể thu thập nhiều loại tăng cường sức mạnh, bao gồm Ảo Ảnh, Ẩn Dụ và Tăng Cường Resonator. Hãy sử dụng những sức mạnh này để thách thức những tầng sâu hơn của giấc mơ.</t>
         </is>
       </c>
     </row>
@@ -17720,8 +17719,8 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Trong Vực Sâu Của Thế Giới Ảo Ảnh, bạn có thể điều chỉnh Tỷ Lệ Phần Thưởng thông qua Tuning Di Truyền.
-Thách thức ở Tỷ Lệ Phần Thưởng cao hơn sẽ mang lại nhiều Illusive Specimen và Memory Points hơn, đồng thời mở khóa nhiều Tuning Di Truyền hơn với những hạn chế trong chiến đấu.
+          <t>Trong Vực Sâu Của Thế Giới Ảo Ảnh, bạn có thể điều chỉnh Tỷ Lệ Phần Thưởng thông qua Điều Chỉnh Di Truyền.
+Thách thức ở Tỷ Lệ Phần Thưởng cao hơn sẽ mang lại nhiều Mẫu Vật Ảo Ảnh và Điểm Ký Ức hơn, đồng thời mở khóa nhiều Điều Chỉnh Di Truyền hơn với những hạn chế trong chiến đấu.
 Hoàn thành thử thách ở Tỷ Lệ Phần Thưởng cao nhất hiện có sẽ mở khóa Tỷ Lệ Phần Thưởng cao hơn nữa.</t>
         </is>
       </c>
@@ -17985,7 +17984,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Manh mối khả dụng: Thường xuất hiện ở Bãi Lầy Whining Aix.
+          <t>Manh mối khả dụng: Thường xuất hiện ở Whining Aix's Mire.
 Những con diệc lông lam cư ngụ ở rừng núi và bờ nước, khoe đôi cánh rộng màu lam biếc. Chúng chỉ xòe cánh khi gió mạnh thổi qua.</t>
         </is>
       </c>
@@ -18780,7 +18779,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade được trao cho các Chiến Binh xuất sắc nhất. Những hoa văn trên lưỡi kiếm lấy cảm hứng từ Griffrex – những thợ săn bẩm sinh và là đồng minh đầu tiên của người Septimontian trên mảnh đất này. Mối quan hệ của họ không cần lời nói, rạng ngời và thuần khiết như mặt trời rực cháy soi sáng vạn vật.</t>
+          <t>Lưỡi Kiếm Rộng được trao cho các Chiến Binh xuất sắc nhất. Những hoa văn trên lưỡi kiếm lấy cảm hứng từ Griffrex – những thợ săn bẩm sinh và là đồng minh đầu tiên của người Septimontian trên mảnh đất này. Mối quan hệ của họ không cần lời nói, rạng ngời và thuần khiết như mặt trời rực cháy soi sáng vạn vật.</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18844,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade được trao cho các Chiến Binh xuất sắc nhất. Những hoa văn trên lưỡi kiếm lấy cảm hứng từ Griffrex – những thợ săn bẩm sinh và là đồng minh đầu tiên của người Septimontian trên mảnh đất này. Mối quan hệ của họ không cần lời nói, rạng ngời và thuần khiết như mặt trời rực cháy soi sáng vạn vật.</t>
+          <t>Lưỡi Kiếm Rộng được trao cho các Chiến Binh xuất sắc nhất. Những hoa văn trên lưỡi kiếm lấy cảm hứng từ Griffrex – những thợ săn bẩm sinh và là đồng minh đầu tiên của người Septimontian trên mảnh đất này. Mối quan hệ của họ không cần lời nói, rạng ngời và thuần khiết như mặt trời rực cháy soi sáng vạn vật.</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19104,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Optical Sampling Stage&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}+{0}+{0} hoặc {1} để tích lũy &lt;color=Highlight&gt;Tràn Dòng&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Giai Đoạn Lấy Mẫu Quang Học&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}+{0}+{0} hoặc {1} để tích lũy &lt;color=Highlight&gt;Tràn Dòng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19169,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Va Chạm Lấp Lánh: Khi &lt;color=Highlight&gt;Overflow&lt;/color&gt; đạt tối đa, giữ {0} để liên tục chuyển hóa &lt;color=Highlight&gt;Overflow&lt;/color&gt; thành &lt;color=Highlight&gt;Ánh Sáng Dịu&lt;/color&gt;. Thả {0} để bước vào &lt;color=Highlight&gt;Diễu Hành Muôn Màu&lt;/color&gt;.</t>
+          <t>Va Chạm Lấp Lánh: Khi &lt;color=Highlight&gt;Tràn Đầy&lt;/color&gt; đạt tối đa, giữ {0} để liên tục chuyển hóa &lt;color=Highlight&gt;Tràn Đầy&lt;/color&gt; thành &lt;color=Highlight&gt;Ánh Sáng Dịu&lt;/color&gt;. Thả {0} để bước vào &lt;color=Highlight&gt;Diễu Hành Muôn Màu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19300,7 +19299,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Tư thế Iai: Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, với ít nhất 100 điểm &lt;color=Highlight&gt;Frostheart&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; hoặc giữ {0} sau khi thực hiện các đòn tấn công.</t>
+          <t>Tư thế Iai: Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, với ít nhất 100 điểm &lt;color=Highlight&gt;Frostheart&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Né tránh&lt;/color&gt; hoặc giữ {0} sau khi thực hiện các đòn tấn công.</t>
         </is>
       </c>
     </row>
@@ -19365,7 +19364,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Mid-air Attack: {Cus:Ipt,Touch=tap PC=Ấn Gamepad=Ấn} {0} giữa không trung để tấn công. Lật người sau mỗi giai đoạn và {Cus:Ipt,Touch=tap PC=ấn Gamepad=ấn} {0} để thực hiện giai đoạn tiếp theo. Giữ {0} ở Stage 1 hoặc 2 để tấn công liên tục.</t>
+          <t>Mid-air Attack: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} giữa không trung để tấn công. Lật người sau mỗi giai đoạn và {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thực hiện giai đoạn tiếp theo. Giữ {0} ở Giai Đoạn 1 hoặc 2 để tấn công liên tục.</t>
         </is>
       </c>
     </row>
@@ -19495,7 +19494,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Mid-air Attack - Dance Mưa Rào: {Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0} khi ở dưới đất để nhảy lên không rồi {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1}.</t>
+          <t>Tấn Công Giữa Không - Vũ Điệu Mưa Rào: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0} khi ở dưới đất để nhảy lên không rồi {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1}.</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19559,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Đòn Lao Xuống&lt;/color&gt; Được Tăng Cường: Khi &lt;color=Highlight&gt;Cartethyia&lt;/color&gt;, nếu có ít nhất 1 &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; trên chiến trường, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} khi đang ở trên không.</t>
+          <t>&lt;color=Highlight&gt;Tấn Công Lao Xuống&lt;/color&gt; Được Tăng Cường: Khi &lt;color=Highlight&gt;Cartethyia&lt;/color&gt;, nếu có ít nhất 1 &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; trên chiến trường, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} khi đang ở trên không.</t>
         </is>
       </c>
     </row>
@@ -19690,7 +19689,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Switch giữa &lt;color=Highlight&gt;Trăng Khuyết&lt;/color&gt; và &lt;color=Highlight&gt;New Moon&lt;/color&gt;: Trong &lt;color=Highlight&gt;Chu Kỳ Mặt Trăng&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy.</t>
+          <t>Chuyển giữa &lt;color=Highlight&gt;Trăng Khuyết&lt;/color&gt; và &lt;color=Highlight&gt;Trăng Non&lt;/color&gt;: Trong &lt;color=Highlight&gt;Chu Kỳ Mặt Trăng&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy.</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19756,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Death Snip có thể thực hiện theo cách sau:
+          <t>Cú Chém Tử Thần có thể thực hiện theo cách sau:
 {0}+{0}+{0}+{0}.
 Giữ {0} cho đến khi hạ cánh, sau đó {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}.</t>
         </is>
@@ -19828,11 +19827,11 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Lifethread - Glide có thể sử dụng theo các cách sau:
-Giữ {0} để nhảy, sau đó {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge trước khi tiếp đất.
-Khi đang ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1}, sau đó Dodge trước khi tiếp đất.
-Khi bị tung lên không trung, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge trước khi tiếp đất.
-Dodge về phía trước sau khi sử dụng Thu Hồi Sợi.</t>
+          <t>Sợi Sinh Mệnh - Lướt có thể sử dụng theo các cách sau:
+Giữ {0} để nhảy, sau đó {Cus:Ipt,Touch=tap PC=press Gamepad=press} né trước khi tiếp đất.
+Khi đang ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1}, sau đó né trước khi tiếp đất.
+Khi bị tung lên không trung, {Cus:Ipt,Touch=tap PC=press Gamepad=press} né trước khi tiếp đất.
+Né về phía trước sau khi sử dụng Thu Hồi Sợi.</t>
         </is>
       </c>
     </row>
@@ -19897,7 +19896,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Overflow&lt;/color&gt; đạt tối đa, có thể thi triển &lt;color=Highlight&gt;Va Chạm Tia Lửa&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, trong đó &lt;color=Highlight&gt;Overflow&lt;/color&gt; liên tục chuyển hóa thành &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Tràn Đầy&lt;/color&gt; đạt tối đa, có thể thi triển &lt;color=Highlight&gt;Va Chạm Tia Lửa&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, trong đó &lt;color=Highlight&gt;Tràn Đầy&lt;/color&gt; liên tục chuyển hóa thành &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20027,7 +20026,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade được trao cho các Chiến Binh xuất sắc nhất. Những hoa văn trên lưỡi kiếm lấy cảm hứng từ Griffrex – những thợ săn bẩm sinh và là đồng minh đầu tiên của người Septimontian trên mảnh đất này. Mối quan hệ của họ không cần lời nói, rạng ngời và thuần khiết như mặt trời rực cháy soi sáng vạn vật.</t>
+          <t>Lưỡi Kiếm Rộng được trao cho các Chiến Binh xuất sắc nhất. Những hoa văn trên lưỡi kiếm lấy cảm hứng từ Griffrex – những thợ săn bẩm sinh và là đồng minh đầu tiên của người Septimontian trên mảnh đất này. Mối quan hệ của họ không cần lời nói, rạng ngời và thuần khiết như mặt trời rực cháy soi sáng vạn vật.</t>
         </is>
       </c>
     </row>
@@ -20807,7 +20806,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế Thanh Đại Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế Thanh Đại Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -20872,7 +20871,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế Thanh Đại Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế Thanh Đại Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20936,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế Thanh Đại Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế Thanh Đại Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -21197,7 +21196,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của mẫu broadblade sản xuất hàng loạt tại Huanglong. Với hiệu năng đáng gờm và công nghệ đột phá, thanh broadblade này chỉ dành cho những chiến binh dày dạn kinh nghiệm mới có thể sử dụng.</t>
+          <t>Phiên bản cải tiến của mẫu đại kiếm sản xuất hàng loạt tại Huanglong. Với hiệu năng đáng gờm và công nghệ đột phá, thanh đại kiếm này chỉ dành cho những chiến binh dày dạn kinh nghiệm mới có thể sử dụng.</t>
         </is>
       </c>
     </row>
@@ -21262,7 +21261,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của mẫu broadblade sản xuất hàng loạt tại Huanglong. Với hiệu năng đáng gờm và công nghệ đột phá, thanh broadblade này chỉ dành cho những chiến binh dày dạn kinh nghiệm mới có thể sử dụng.</t>
+          <t>Phiên bản cải tiến của mẫu đại kiếm sản xuất hàng loạt tại Huanglong. Với hiệu năng đáng gờm và công nghệ đột phá, thanh đại kiếm này chỉ dành cho những chiến binh dày dạn kinh nghiệm mới có thể sử dụng.</t>
         </is>
       </c>
     </row>
@@ -21327,7 +21326,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Phiên bản cải tiến của mẫu broadblade sản xuất hàng loạt tại Huanglong. Với hiệu năng đáng gờm và công nghệ đột phá, thanh broadblade này chỉ dành cho những chiến binh dày dạn kinh nghiệm mới có thể sử dụng.</t>
+          <t>Phiên bản cải tiến của mẫu đại kiếm sản xuất hàng loạt tại Huanglong. Với hiệu năng đáng gờm và công nghệ đột phá, thanh đại kiếm này chỉ dành cho những chiến binh dày dạn kinh nghiệm mới có thể sử dụng.</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21598,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade do Pioneer Association cung cấp cho các nhà thám hiểm có màu sắc tươi sáng, khó mất, chất liệu cứng cáp, có thể đối phó với nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
+          <t>Lưỡi Kiếm Rộng do Hiệp Hội Tiên Phong cung cấp cho các nhà thám hiểm có màu sắc tươi sáng, khó mất, chất liệu cứng cáp, có thể đối phó với nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -21664,7 +21663,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade do Pioneer Association cung cấp cho các nhà thám hiểm có màu sắc tươi sáng, khó mất, chất liệu cứng cáp, có thể đối phó với nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
+          <t>Lưỡi Kiếm Rộng do Hiệp Hội Tiên Phong cung cấp cho các nhà thám hiểm có màu sắc tươi sáng, khó mất, chất liệu cứng cáp, có thể đối phó với nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21728,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade do Pioneer Association cung cấp cho các nhà thám hiểm có màu sắc tươi sáng, khó mất, chất liệu cứng cáp, có thể đối phó với nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
+          <t>Lưỡi Kiếm Rộng do Hiệp Hội Tiên Phong cung cấp cho các nhà thám hiểm có màu sắc tươi sáng, khó mất, chất liệu cứng cáp, có thể đối phó với nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -23644,7 +23643,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Một con dấu nghệ thuật được trang trí bằng những mầm cây phủ sương. Nó được đóng trên vô số bức tranh vẽ núi non và hẻm vực bằng những Dodget vẽ biểu cảm, mê hoặc. Những mầm cây mỏng manh tượng trưng cho sự nở rộ bất tận của những tuyệt tác nghệ thuật.</t>
+          <t>Một con dấu nghệ thuật được trang trí bằng những mầm cây phủ sương. Nó được đóng trên vô số bức tranh vẽ núi non và hẻm vực bằng những nét vẽ biểu cảm, mê hoặc. Những mầm cây mỏng manh tượng trưng cho sự nở rộ bất tận của những tuyệt tác nghệ thuật.</t>
         </is>
       </c>
     </row>
@@ -23709,7 +23708,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Một con dấu nghệ thuật được trang trí bằng những mầm cây phủ sương. Nó được đóng trên vô số bức tranh vẽ núi non và hẻm vực bằng những Dodget vẽ biểu cảm, mê hoặc. Những mầm cây mỏng manh tượng trưng cho sự nở rộ bất tận của những tuyệt tác nghệ thuật.</t>
+          <t>Một con dấu nghệ thuật được trang trí bằng những mầm cây phủ sương. Nó được đóng trên vô số bức tranh vẽ núi non và hẻm vực bằng những nét vẽ biểu cảm, mê hoặc. Những mầm cây mỏng manh tượng trưng cho sự nở rộ bất tận của những tuyệt tác nghệ thuật.</t>
         </is>
       </c>
     </row>
@@ -23774,7 +23773,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Một con dấu nghệ thuật được trang trí bằng những mầm cây phủ sương. Nó được đóng trên vô số bức tranh vẽ núi non và hẻm vực bằng những Dodget vẽ biểu cảm, mê hoặc. Những mầm cây mỏng manh tượng trưng cho sự nở rộ bất tận của những tuyệt tác nghệ thuật.</t>
+          <t>Một con dấu nghệ thuật được trang trí bằng những mầm cây phủ sương. Nó được đóng trên vô số bức tranh vẽ núi non và hẻm vực bằng những nét vẽ biểu cảm, mê hoặc. Những mầm cây mỏng manh tượng trưng cho sự nở rộ bất tận của những tuyệt tác nghệ thuật.</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24640,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade sinh ra từ hiện tượng trên không. Người thợ rèn đã gửi gắm cảm xúc khi chứng kiến ngôi sao xa lạ vào vũ khí, khiến nó trông rỗng và nhẹ, nhưng lại có thể phát huy sức hút vô địch của sao băng.</t>
+          <t>Lưỡi Kiếm Rộng sinh ra từ hiện tượng trên không. Người thợ rèn đã gửi gắm cảm xúc khi chứng kiến ngôi sao xa lạ vào vũ khí, khiến nó trông rỗng và nhẹ, nhưng lại có thể phát huy sức hút vô địch của sao băng.</t>
         </is>
       </c>
     </row>
@@ -24706,7 +24705,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade sinh ra từ hiện tượng trên không. Người thợ rèn đã gửi gắm cảm xúc khi chứng kiến ngôi sao xa lạ vào vũ khí, khiến nó trông rỗng và nhẹ, nhưng lại có thể phát huy sức hút vô địch của sao băng.</t>
+          <t>Lưỡi Kiếm Rộng sinh ra từ hiện tượng trên không. Người thợ rèn đã gửi gắm cảm xúc khi chứng kiến ngôi sao xa lạ vào vũ khí, khiến nó trông rỗng và nhẹ, nhưng lại có thể phát huy sức hút vô địch của sao băng.</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24770,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade sinh ra từ hiện tượng trên không. Người thợ rèn đã gửi gắm cảm xúc khi chứng kiến ngôi sao xa lạ vào vũ khí, khiến nó trông rỗng và nhẹ, nhưng lại có thể phát huy sức hút vô địch của sao băng.</t>
+          <t>Lưỡi Kiếm Rộng sinh ra từ hiện tượng trên không. Người thợ rèn đã gửi gắm cảm xúc khi chứng kiến ngôi sao xa lạ vào vũ khí, khiến nó trông rỗng và nhẹ, nhưng lại có thể phát huy sức hút vô địch của sao băng.</t>
         </is>
       </c>
     </row>
@@ -24836,7 +24835,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade này là vũ khí nghi lễ dùng trong Lễ Nhậm Chức Quan Phán Xét của Huanglong. Họa tiết lá bạch quả vàng tượng trưng cho sức sống bền bỉ của Huanglong, vươn lên trong thế giới đã bỏ rơi nó.</t>
+          <t>Lưỡi Đại kiếm này là vũ khí nghi lễ dùng trong Lễ Nhậm Chức Quan Phán Xét của Huanglong. Họa tiết lá bạch quả vàng tượng trưng cho sức sống bền bỉ của Huanglong, vươn lên trong thế giới đã bỏ rơi nó.</t>
         </is>
       </c>
     </row>
@@ -24901,7 +24900,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade này là vũ khí nghi lễ dùng trong Lễ Nhậm Chức Quan Phán Xét của Huanglong. Họa tiết lá bạch quả vàng tượng trưng cho sức sống bền bỉ của Huanglong, vươn lên trong thế giới đã bỏ rơi nó.</t>
+          <t>Lưỡi Đại kiếm này là vũ khí nghi lễ dùng trong Lễ Nhậm Chức Quan Phán Xét của Huanglong. Họa tiết lá bạch quả vàng tượng trưng cho sức sống bền bỉ của Huanglong, vươn lên trong thế giới đã bỏ rơi nó.</t>
         </is>
       </c>
     </row>
@@ -24966,7 +24965,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Lưỡi Broadblade này là vũ khí nghi lễ dùng trong Lễ Nhậm Chức Quan Phán Xét của Huanglong. Họa tiết lá bạch quả vàng tượng trưng cho sức sống bền bỉ của Huanglong, vươn lên trong thế giới đã bỏ rơi nó.</t>
+          <t>Lưỡi Đại kiếm này là vũ khí nghi lễ dùng trong Lễ Nhậm Chức Quan Phán Xét của Huanglong. Họa tiết lá bạch quả vàng tượng trưng cho sức sống bền bỉ của Huanglong, vươn lên trong thế giới đã bỏ rơi nó.</t>
         </is>
       </c>
     </row>
@@ -25356,7 +25355,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế Thanh Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế Thanh Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -25421,7 +25420,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế Thanh Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế Thanh Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -25486,7 +25485,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế Thanh Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế Thanh Kiếm thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -25746,7 +25745,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Kiếm do Pioneer Association cung cấp cho các nhà thám hiểm có màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, chịu đựng được nhiều môi trường khắc nghiệt trong thời gian dài, và rất được giới thám hiểm ưa chuộng.</t>
+          <t>Kiếm do Hiệp Hội Tiên Phong cung cấp cho các nhà thám hiểm có màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, chịu đựng được nhiều môi trường khắc nghiệt trong thời gian dài, và rất được giới thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -25811,7 +25810,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Kiếm do Pioneer Association cung cấp cho các nhà thám hiểm có màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, chịu đựng được nhiều môi trường khắc nghiệt trong thời gian dài, và rất được giới thám hiểm ưa chuộng.</t>
+          <t>Kiếm do Hiệp Hội Tiên Phong cung cấp cho các nhà thám hiểm có màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, chịu đựng được nhiều môi trường khắc nghiệt trong thời gian dài, và rất được giới thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -25876,7 +25875,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Kiếm do Pioneer Association cung cấp cho các nhà thám hiểm có màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, chịu đựng được nhiều môi trường khắc nghiệt trong thời gian dài, và rất được giới thám hiểm ưa chuộng.</t>
+          <t>Kiếm do Hiệp Hội Tiên Phong cung cấp cho các nhà thám hiểm có màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, chịu đựng được nhiều môi trường khắc nghiệt trong thời gian dài, và rất được giới thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -26721,7 +26720,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế những Khẩu Súng thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế những Khẩu Súng thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -26786,7 +26785,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế những Khẩu Súng thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế những Khẩu Súng thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -26851,7 +26850,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế những Khẩu Súng thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế những Khẩu Súng thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -26916,7 +26915,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Huaxu Academy đã phát triển những khẩu súng ngắn thực dụng, hiệu suất cao dựa trên các loại vũ khí năng lượng nguồn trước đây, thể hiện sự nghiên cứu tỉ mỉ và hướng đến sự hoàn hảo.</t>
+          <t>Học viện Huaxu đã phát triển những khẩu súng ngắn thực dụng, hiệu suất cao dựa trên các loại vũ khí năng lượng nguồn trước đây, thể hiện sự nghiên cứu tỉ mỉ và hướng đến sự hoàn hảo.</t>
         </is>
       </c>
     </row>
@@ -26981,7 +26980,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Huaxu Academy đã phát triển những khẩu súng ngắn thực dụng, hiệu suất cao dựa trên các loại vũ khí năng lượng nguồn trước đây, thể hiện sự nghiên cứu tỉ mỉ và hướng đến sự hoàn hảo.</t>
+          <t>Học viện Huaxu đã phát triển những khẩu súng ngắn thực dụng, hiệu suất cao dựa trên các loại vũ khí năng lượng nguồn trước đây, thể hiện sự nghiên cứu tỉ mỉ và hướng đến sự hoàn hảo.</t>
         </is>
       </c>
     </row>
@@ -27046,7 +27045,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Huaxu Academy đã phát triển những khẩu súng ngắn thực dụng, hiệu suất cao dựa trên các loại vũ khí năng lượng nguồn trước đây, thể hiện sự nghiên cứu tỉ mỉ và hướng đến sự hoàn hảo.</t>
+          <t>Học viện Huaxu đã phát triển những khẩu súng ngắn thực dụng, hiệu suất cao dựa trên các loại vũ khí năng lượng nguồn trước đây, thể hiện sự nghiên cứu tỉ mỉ và hướng đến sự hoàn hảo.</t>
         </is>
       </c>
     </row>
@@ -27111,7 +27110,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Những khẩu súng lục do Pioneer Association cung cấp cho các lữ khách xa xôi, với màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được giới thám hiểm ưa chuộng.</t>
+          <t>Những khẩu súng lục do Hiệp Hội Tiên Phong cung cấp cho các lữ khách xa xôi, với màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được giới thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -27176,7 +27175,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Những khẩu súng lục do Pioneer Association cung cấp cho các lữ khách xa xôi, với màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được giới thám hiểm ưa chuộng.</t>
+          <t>Những khẩu súng lục do Hiệp Hội Tiên Phong cung cấp cho các lữ khách xa xôi, với màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được giới thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -27241,7 +27240,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Những khẩu súng lục do Pioneer Association cung cấp cho các lữ khách xa xôi, với màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được giới thám hiểm ưa chuộng.</t>
+          <t>Những khẩu súng lục do Hiệp Hội Tiên Phong cung cấp cho các lữ khách xa xôi, với màu sắc nổi bật, khó thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được giới thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -28086,7 +28085,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế những Găng Tay thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế những Găng Tay thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -28151,7 +28150,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế những Găng Tay thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế những Găng Tay thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -28216,7 +28215,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế những Găng Tay thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế những Găng Tay thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của chúng là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28280,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Huaxu Academy đã tự cải tiến và phát triển thành công bộ Găng Tay hiệu suất cao thực tiễn đầu tiên dựa trên các vũ khí năng lượng nguồn trước đây, đại diện cho sự quan tâm và tình thương của Học viện, vững bền và trường tồn.</t>
+          <t>Học viện Huaxu đã tự cải tiến và phát triển thành công bộ Găng Tay hiệu suất cao thực tiễn đầu tiên dựa trên các vũ khí năng lượng nguồn trước đây, đại diện cho sự quan tâm và tình thương của Học viện, vững bền và trường tồn.</t>
         </is>
       </c>
     </row>
@@ -28346,7 +28345,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Huaxu Academy đã tự cải tiến và phát triển thành công bộ Găng Tay hiệu suất cao thực tiễn đầu tiên dựa trên các vũ khí năng lượng nguồn trước đây, đại diện cho sự quan tâm và tình thương của Học viện, vững bền và trường tồn.</t>
+          <t>Học viện Huaxu đã tự cải tiến và phát triển thành công bộ Găng Tay hiệu suất cao thực tiễn đầu tiên dựa trên các vũ khí năng lượng nguồn trước đây, đại diện cho sự quan tâm và tình thương của Học viện, vững bền và trường tồn.</t>
         </is>
       </c>
     </row>
@@ -28411,7 +28410,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Huaxu Academy đã tự cải tiến và phát triển thành công bộ Găng Tay hiệu suất cao thực tiễn đầu tiên dựa trên các vũ khí năng lượng nguồn trước đây, đại diện cho sự quan tâm và tình thương của Học viện, vững bền và trường tồn.</t>
+          <t>Học viện Huaxu đã tự cải tiến và phát triển thành công bộ Găng Tay hiệu suất cao thực tiễn đầu tiên dựa trên các vũ khí năng lượng nguồn trước đây, đại diện cho sự quan tâm và tình thương của Học viện, vững bền và trường tồn.</t>
         </is>
       </c>
     </row>
@@ -28476,7 +28475,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Bao tay do Pioneer Association cung cấp cho những người du hành xa, với màu sắc tươi sáng, khó bị thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, và rất được nhóm thám hiểm ưa chuộng.</t>
+          <t>Bao tay do Hiệp Hội Tiên Phong cung cấp cho những người du hành xa, với màu sắc tươi sáng, khó bị thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, và rất được nhóm thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -28541,7 +28540,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Bao tay do Pioneer Association cung cấp cho những người du hành xa, với màu sắc tươi sáng, khó bị thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, và rất được nhóm thám hiểm ưa chuộng.</t>
+          <t>Bao tay do Hiệp Hội Tiên Phong cung cấp cho những người du hành xa, với màu sắc tươi sáng, khó bị thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, và rất được nhóm thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -28606,7 +28605,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Bao tay do Pioneer Association cung cấp cho những người du hành xa, với màu sắc tươi sáng, khó bị thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, và rất được nhóm thám hiểm ưa chuộng.</t>
+          <t>Bao tay do Hiệp Hội Tiên Phong cung cấp cho những người du hành xa, với màu sắc tươi sáng, khó bị thất lạc, chất liệu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, và rất được nhóm thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -29841,7 +29840,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế Thiết bị Rectifier thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế Thiết bị Pháp khí thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -29906,7 +29905,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế Thiết bị Rectifier thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế Thiết bị Pháp khí thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -29971,7 +29970,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Để chế tạo vũ khí Tacetite mới, Huaxu Academy đã thiết kế Thiết bị Rectifier thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonators trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
+          <t>Để chế tạo vũ khí Tacetite mới, Học viện Huaxu đã thiết kế Thiết bị Pháp khí thử nghiệm này nhằm xác minh kỹ thuật. Đặc điểm chính của nó là hồi phục thông qua tấn công, tăng cường thể chất cho Resonator trong khi thể hiện hiệu suất vũ khí ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -30426,7 +30425,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Thiết bị Chỉnh Lưu do Pioneer Association cung cấp cho các nhà thám hiểm, với màu sắc tươi sáng, khó bị thất lạc, kết cấu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
+          <t>Thiết bị Chỉnh Lưu do Hiệp Hội Tiên Phong cung cấp cho các nhà thám hiểm, với màu sắc tươi sáng, khó bị thất lạc, kết cấu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -30491,7 +30490,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Thiết bị Chỉnh Lưu do Pioneer Association cung cấp cho các nhà thám hiểm, với màu sắc tươi sáng, khó bị thất lạc, kết cấu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
+          <t>Thiết bị Chỉnh Lưu do Hiệp Hội Tiên Phong cung cấp cho các nhà thám hiểm, với màu sắc tươi sáng, khó bị thất lạc, kết cấu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -30556,7 +30555,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Thiết bị Chỉnh Lưu do Pioneer Association cung cấp cho các nhà thám hiểm, với màu sắc tươi sáng, khó bị thất lạc, kết cấu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
+          <t>Thiết bị Chỉnh Lưu do Hiệp Hội Tiên Phong cung cấp cho các nhà thám hiểm, với màu sắc tươi sáng, khó bị thất lạc, kết cấu cứng cáp, có thể chịu đựng nhiều môi trường khắc nghiệt trong thời gian dài, rất được các nhà thám hiểm ưa chuộng.</t>
         </is>
       </c>
     </row>
@@ -32207,7 +32206,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Mỗi lần sử dụng &lt;color=Highlight&gt;Basic Attack - Iai&lt;/color&gt;, sẽ nhận được một điểm cộng dồn &lt;color=Highlight&gt;Whiteout Bitter Frost&lt;/color&gt;. Khi tích đủ 3 điểm &lt;color=Highlight&gt;Whiteout Bitter Frost&lt;/color&gt;, Hiyuki có thể thi triển &lt;color=Highlight&gt;Đòn tấn công hạng nặng - Bitter Frost: Foreclaimed Self&lt;/color&gt;, nhận 1 điểm &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt;. Hiyuki có thể chọn tiêu hao bất kỳ điểm &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; nào bằng cách sạc để tăng Sát Thương của Resonance Liberation &lt;color=Highlight&gt;Báo Trước: Giải Phóng Blade&lt;/color&gt;. Điểm &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; chưa dùng sẽ được giữ lại.</t>
+          <t>Mỗi lần sử dụng &lt;color=Highlight&gt;Đòn tấn công cơ bản - Iai&lt;/color&gt;, sẽ nhận được một điểm cộng dồn &lt;color=Highlight&gt;Whiteout Bitter Frost&lt;/color&gt;. Khi tích đủ 3 điểm &lt;color=Highlight&gt;Whiteout Bitter Frost&lt;/color&gt;, Hiyuki có thể thi triển &lt;color=Highlight&gt;Đòn tấn công hạng nặng - Bitter Frost: Foreclaimed Self&lt;/color&gt;, nhận 1 điểm &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt;. Hiyuki có thể chọn tiêu hao bất kỳ điểm &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; nào bằng cách sạc để tăng Sát Thương của Giải Phóng Cộng Hưởng &lt;color=Highlight&gt;Báo Trước: Giải Phóng Blade&lt;/color&gt;. Điểm &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; chưa dùng sẽ được giữ lại.</t>
         </is>
       </c>
     </row>
@@ -32817,7 +32816,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Hình chiếu của Broadblade - Ages of Harvest, đẹp như hoa đào nở rộ.
+          <t>Hình chiếu của Đại kiếm - Ages of Harvest, đẹp như hoa đào nở rộ.
 Khi xuân về, viên ngọc thời gian trên chuôi chuyển sang hồng, nhuốm màu cánh hoa, như trái tim thiếu nữ đang độ xuân thì.</t>
         </is>
       </c>
@@ -32883,7 +32882,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Khi Nameless Explorer chịu ảnh hưởng của &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;, mức Giảm Sức Vibration mà nó phải chịu tăng thêm 30%.</t>
+          <t>Khi Nhà Thám Hiểm Vô Danh chịu ảnh hưởng của &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;, mức Giảm Sức Rung động mà nó phải chịu tăng thêm 30%.</t>
         </is>
       </c>
     </row>
@@ -32949,7 +32948,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Môi trường trong khu vực này rất nguy hiểm. Khuyến nghị nâng Cấp Glory bằng cách nhận nhiệm vụ biểu ngữ phù hợp với cấp hiện tại trước.
+          <t>Môi trường trong khu vực này rất nguy hiểm. Khuyến nghị nâng Cấp Vinh Quang bằng cách nhận nhiệm vụ biểu ngữ phù hợp với cấp hiện tại trước.
 Phước lành từ chúng sẽ giúp cậu lấy lại vinh quang trước đây nhanh hơn.</t>
         </is>
       </c>
@@ -33149,7 +33148,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>"Chào buổi sáng quý vị. Cảm ơn vì đã theo dõi Megalopolis Hôm nay. Tin tức sáng nay bắt đầu với bản tin về vụ tấn công của những sinh vật lạ tại Công viên Memorial vào khoảng 9h30 tối qua. Chính quyền địa phương xác nhận tất cả nạn nhân đã được chuyển đến Bệnh viện Trung ương để điều trị, và đáng ngạc nhiên là không có trường hợp tử vong nào. Nhân chứng cho biết đã nhìn thấy một sinh vật lạ thứ hai dùng lửa để tiêu diệt những kẻ tấn công. Bây giờ, chúng ta sẽ chuyển đến phóng viên trực tiếp tại hiện trường." Trên màn hình sáng, một người phụ nữ ngồi trong văn phòng rộng rãi, nói chuyện trực tiếp với máy quay.</t>
+          <t>"Chào buổi sáng quý vị. Cảm ơn vì đã theo dõi Megalopolis Today. Tin tức sáng nay bắt đầu với bản tin về vụ tấn công của những sinh vật lạ tại Công viên Memorial vào khoảng 9h30 tối qua. Chính quyền địa phương xác nhận tất cả nạn nhân đã được chuyển đến Bệnh viện Trung ương để điều trị, và đáng ngạc nhiên là không có trường hợp tử vong nào. Nhân chứng cho biết đã nhìn thấy một sinh vật lạ thứ hai dùng lửa để tiêu diệt những kẻ tấn công. Bây giờ, chúng ta sẽ chuyển đến phóng viên trực tiếp tại hiện trường." Trên màn hình sáng, một người phụ nữ ngồi trong văn phòng rộng rãi, nói chuyện trực tiếp với máy quay.</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33213,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>"Cảm ơn. Đằng sau tôi là hiện trường vụ tấn công đêm qua. Ngay cả từ khoảng cách này, sự tàn phá do những sinh vật không xác định gây ra cũng rất khủng khiếp. Như các bạn thấy, các công trình bê tông bị hư hại và..." Cảnh quay chuyển sang khu vực ngoài trời đầy cây cối, khi người phóng viên tiếp tục tường thuật. Cậu nhanh chóng nhận ra đây là một buổi phát sóng trực tiếp qua thiết bị giống như Terminal.</t>
+          <t>"Cảm ơn. Đằng sau tôi là hiện trường vụ tấn công đêm qua. Ngay cả từ khoảng cách này, sự tàn phá do những sinh vật không xác định gây ra cũng rất khủng khiếp. Như các bạn thấy, các công trình bê tông bị hư hại và..." Cảnh quay chuyển sang khu vực ngoài trời đầy cây cối, khi người phóng viên tiếp tục tường thuật. Cậu nhanh chóng nhận ra đây là một buổi phát sóng trực tiếp qua thiết bị giống như Thiết bị đầu cuối.</t>
         </is>
       </c>
     </row>
@@ -33344,7 +33343,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>"Có vẻ như chúng ta gặp trục trặc với tín hiệu từ phóng viên. Tiếp theo trong Megalopolis Hôm nay, sự kiện ký tặng gặp gỡ họa sĩ truyện tranh Danqing dự kiến sáng nay đã bị hủy do ban tổ chức không liên lạc được với họa sĩ. Hiện tại, địa điểm đã chật kín người hâm mộ xếp hàng từ đêm qua..."</t>
+          <t>"Có vẻ như chúng ta gặp trục trặc với tín hiệu từ phóng viên. Tiếp theo trong Megalopolis Today, sự kiện ký tặng gặp gỡ họa sĩ truyện tranh Danqing dự kiến sáng nay đã bị hủy do ban tổ chức không liên lạc được với họa sĩ. Hiện tại, địa điểm đã chật kín người hâm mộ xếp hàng từ đêm qua..."</t>
         </is>
       </c>
     </row>
@@ -33474,7 +33473,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>"Tacet... Discord á? Chưa nghe bao giờ. Dù chúng là gì đi nữa, nếu dám lộ mặt lần nữa, ta sẽ tống chúng về nơi chúng đến..."</t>
+          <t>"Tacet... Discord á? Chưa nghe bao giờ. Dù chúng là gì đi nữa, nếu dám lộ mặt lần nữa, tao sẽ tống chúng về nơi chúng đến..."</t>
         </is>
       </c>
     </row>
@@ -33539,7 +33538,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>"Này, đừng nhìn ta như thế chứ! Ta hiểu mà, được chưa? Ta ổn. Ta trở thành Flame Ranger là để bảo vệ nụ cười của mọi người, chứ không phải để ai phải khóc vì ta. Ngươi nghĩ ta để chuyện đó xảy ra à?"</t>
+          <t>"Này, đừng nhìn tao như thế chứ! Tao hiểu mà, được chưa? Tao ổn. Tao trở thành Flame Ranger là để bảo vệ nụ cười của mọi người, chứ không phải để ai phải khóc vì tao. Mày nghĩ tao để chuyện đó xảy ra à?"</t>
         </is>
       </c>
     </row>
@@ -33800,7 +33799,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>"Yes. Chúng tôi vẫn chưa tìm ra quy luật hay logic nào trong cách di chuyển của chúng. Tất cả những gì chúng tôi biết là chúng tấn công bất cứ thứ gì nhìn thấy." Viên sĩ quan nhíu cậu như đang nhớ lại những sự việc xảy ra mấy ngày qua.</t>
+          <t>"Đúng vậy. Chúng tôi vẫn chưa tìm ra quy luật hay logic nào trong cách di chuyển của chúng. Tất cả những gì chúng tôi biết là chúng tấn công bất cứ thứ gì nhìn thấy." Viên sĩ quan nhíu mày như đang nhớ lại những sự việc xảy ra mấy ngày qua.</t>
         </is>
       </c>
     </row>
@@ -33865,7 +33864,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>"Ta phải hết sức thận trọng với tình huống này. Những nơi như ga tàu, khu thương mại và Bệnh viện Trung ương đông đúc người qua lại. Nếu có chuyện gì xảy ra, lực lượng An ninh Public như chúng ta chính là tuyến phòng thủ đầu tiên."</t>
+          <t>"Ta phải hết sức thận trọng với tình huống này. Những nơi như ga tàu, khu thương mại và Bệnh viện Trung ương đông đúc người qua lại. Nếu có chuyện gì xảy ra, lực lượng An ninh Công cộng như chúng ta chính là tuyến phòng thủ đầu tiên."</t>
         </is>
       </c>
     </row>
@@ -34125,7 +34124,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Bạn và Abby đến khoa nghiên cứu lâm sàng của Bệnh viện Trung ương, nơi không khí nặng mùi thuốc và chất khử trùng. Không khí nhộn nhịp ở đây chẳng kém gì Huaxu Academy.</t>
+          <t>Bạn và Abby đến khoa nghiên cứu lâm sàng của Bệnh viện Trung ương, nơi không khí nặng mùi thuốc và chất khử trùng. Không khí nhộn nhịp ở đây chẳng kém gì Học viện Huaxu.</t>
         </is>
       </c>
     </row>
